--- a/Data/processed/books.xlsx
+++ b/Data/processed/books.xlsx
@@ -985,7 +985,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/in-her-wake_980/index.html</t>
+          <t>https://books.toscrape.com/catalogue/in-her-wake_980/index.html</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/how-music-works_979/index.html</t>
+          <t>https://books.toscrape.com/catalogue/how-music-works_979/index.html</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/foolproof-preserving-a-guide-to-small-batch-jams-jellies-pickles-condiments-and-more-a-foolproof-guide-to-making-small-batch-jams-jellies-pickles-condiments-and-more_978/index.html</t>
+          <t>https://books.toscrape.com/catalogue/foolproof-preserving-a-guide-to-small-batch-jams-jellies-pickles-condiments-and-more-a-foolproof-guide-to-making-small-batch-jams-jellies-pickles-condiments-and-more_978/index.html</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/chase-me-paris-nights-2_977/index.html</t>
+          <t>https://books.toscrape.com/catalogue/chase-me-paris-nights-2_977/index.html</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/black-dust_976/index.html</t>
+          <t>https://books.toscrape.com/catalogue/black-dust_976/index.html</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/birdsong-a-story-in-pictures_975/index.html</t>
+          <t>https://books.toscrape.com/catalogue/birdsong-a-story-in-pictures_975/index.html</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/americas-cradle-of-quarterbacks-western-pennsylvanias-football-factory-from-johnny-unitas-to-joe-montana_974/index.html</t>
+          <t>https://books.toscrape.com/catalogue/americas-cradle-of-quarterbacks-western-pennsylvanias-football-factory-from-johnny-unitas-to-joe-montana_974/index.html</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/aladdin-and-his-wonderful-lamp_973/index.html</t>
+          <t>https://books.toscrape.com/catalogue/aladdin-and-his-wonderful-lamp_973/index.html</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/worlds-elsewhere-journeys-around-shakespeares-globe_972/index.html</t>
+          <t>https://books.toscrape.com/catalogue/worlds-elsewhere-journeys-around-shakespeares-globe_972/index.html</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/wall-and-piece_971/index.html</t>
+          <t>https://books.toscrape.com/catalogue/wall-and-piece_971/index.html</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-four-agreements-a-practical-guide-to-personal-freedom_970/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-four-agreements-a-practical-guide-to-personal-freedom_970/index.html</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-five-love-languages-how-to-express-heartfelt-commitment-to-your-mate_969/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-five-love-languages-how-to-express-heartfelt-commitment-to-your-mate_969/index.html</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-elephant-tree_968/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-elephant-tree_968/index.html</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-bear-and-the-piano_967/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-bear-and-the-piano_967/index.html</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/sophies-world_966/index.html</t>
+          <t>https://books.toscrape.com/catalogue/sophies-world_966/index.html</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/penny-maybe_965/index.html</t>
+          <t>https://books.toscrape.com/catalogue/penny-maybe_965/index.html</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/maude-1883-1993she-grew-up-with-the-country_964/index.html</t>
+          <t>https://books.toscrape.com/catalogue/maude-1883-1993she-grew-up-with-the-country_964/index.html</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/in-a-dark-dark-wood_963/index.html</t>
+          <t>https://books.toscrape.com/catalogue/in-a-dark-dark-wood_963/index.html</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/behind-closed-doors_962/index.html</t>
+          <t>https://books.toscrape.com/catalogue/behind-closed-doors_962/index.html</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/you-cant-bury-them-all-poems_961/index.html</t>
+          <t>https://books.toscrape.com/catalogue/you-cant-bury-them-all-poems_961/index.html</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/slow-states-of-collapse-poems_960/index.html</t>
+          <t>https://books.toscrape.com/catalogue/slow-states-of-collapse-poems_960/index.html</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/reasons-to-stay-alive_959/index.html</t>
+          <t>https://books.toscrape.com/catalogue/reasons-to-stay-alive_959/index.html</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/private-paris-private-10_958/index.html</t>
+          <t>https://books.toscrape.com/catalogue/private-paris-private-10_958/index.html</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/higherselfie-wake-up-your-life-free-your-soul-find-your-tribe_957/index.html</t>
+          <t>https://books.toscrape.com/catalogue/higherselfie-wake-up-your-life-free-your-soul-find-your-tribe_957/index.html</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/without-borders-wanderlove-1_956/index.html</t>
+          <t>https://books.toscrape.com/catalogue/without-borders-wanderlove-1_956/index.html</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/when-we-collided_955/index.html</t>
+          <t>https://books.toscrape.com/catalogue/when-we-collided_955/index.html</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/we-love-you-charlie-freeman_954/index.html</t>
+          <t>https://books.toscrape.com/catalogue/we-love-you-charlie-freeman_954/index.html</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/untitled-collection-sabbath-poems-2014_953/index.html</t>
+          <t>https://books.toscrape.com/catalogue/untitled-collection-sabbath-poems-2014_953/index.html</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/unseen-city-the-majesty-of-pigeons-the-discreet-charm-of-snails-other-wonders-of-the-urban-wilderness_952/index.html</t>
+          <t>https://books.toscrape.com/catalogue/unseen-city-the-majesty-of-pigeons-the-discreet-charm-of-snails-other-wonders-of-the-urban-wilderness_952/index.html</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/unicorn-tracks_951/index.html</t>
+          <t>https://books.toscrape.com/catalogue/unicorn-tracks_951/index.html</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/unbound-how-eight-technologies-made-us-human-transformed-society-and-brought-our-world-to-the-brink_950/index.html</t>
+          <t>https://books.toscrape.com/catalogue/unbound-how-eight-technologies-made-us-human-transformed-society-and-brought-our-world-to-the-brink_950/index.html</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/tsubasa-world-chronicle-2-tsubasa-world-chronicle-2_949/index.html</t>
+          <t>https://books.toscrape.com/catalogue/tsubasa-world-chronicle-2-tsubasa-world-chronicle-2_949/index.html</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/throwing-rocks-at-the-google-bus-how-growth-became-the-enemy-of-prosperity_948/index.html</t>
+          <t>https://books.toscrape.com/catalogue/throwing-rocks-at-the-google-bus-how-growth-became-the-enemy-of-prosperity_948/index.html</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/this-one-summer_947/index.html</t>
+          <t>https://books.toscrape.com/catalogue/this-one-summer_947/index.html</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/thirst_946/index.html</t>
+          <t>https://books.toscrape.com/catalogue/thirst_946/index.html</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-torch-is-passed-a-harding-family-story_945/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-torch-is-passed-a-harding-family-story_945/index.html</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-secret-of-dreadwillow-carse_944/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-secret-of-dreadwillow-carse_944/index.html</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-pioneer-woman-cooks-dinnertime-comfort-classics-freezer-food-16-minute-meals-and-other-delicious-ways-to-solve-supper_943/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-pioneer-woman-cooks-dinnertime-comfort-classics-freezer-food-16-minute-meals-and-other-delicious-ways-to-solve-supper_943/index.html</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-past-never-ends_942/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-past-never-ends_942/index.html</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-natural-history-of-us-the-fine-art-of-pretending-2_941/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-natural-history-of-us-the-fine-art-of-pretending-2_941/index.html</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-nameless-city-the-nameless-city-1_940/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-nameless-city-the-nameless-city-1_940/index.html</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-murder-that-never-was-forensic-instincts-5_939/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-murder-that-never-was-forensic-instincts-5_939/index.html</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-most-perfect-thing-inside-and-outside-a-birds-egg_938/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-most-perfect-thing-inside-and-outside-a-birds-egg_938/index.html</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-mindfulness-and-acceptance-workbook-for-anxiety-a-guide-to-breaking-free-from-anxiety-phobias-and-worry-using-acceptance-and-commitment-therapy_937/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-mindfulness-and-acceptance-workbook-for-anxiety-a-guide-to-breaking-free-from-anxiety-phobias-and-worry-using-acceptance-and-commitment-therapy_937/index.html</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-life-changing-magic-of-tidying-up-the-japanese-art-of-decluttering-and-organizing_936/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-life-changing-magic-of-tidying-up-the-japanese-art-of-decluttering-and-organizing_936/index.html</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-inefficiency-assassin-time-management-tactics-for-working-smarter-not-longer_935/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-inefficiency-assassin-time-management-tactics-for-working-smarter-not-longer_935/index.html</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-gutsy-girl-escapades-for-your-life-of-epic-adventure_934/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-gutsy-girl-escapades-for-your-life-of-epic-adventure_934/index.html</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-electric-pencil-drawings-from-inside-state-hospital-no-3_933/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-electric-pencil-drawings-from-inside-state-hospital-no-3_933/index.html</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-death-of-humanity-and-the-case-for-life_932/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-death-of-humanity-and-the-case-for-life_932/index.html</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-bulletproof-diet-lose-up-to-a-pound-a-day-reclaim-energy-and-focus-upgrade-your-life_931/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-bulletproof-diet-lose-up-to-a-pound-a-day-reclaim-energy-and-focus-upgrade-your-life_931/index.html</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-art-forger_930/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-art-forger_930/index.html</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-age-of-genius-the-seventeenth-century-and-the-birth-of-the-modern-mind_929/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-age-of-genius-the-seventeenth-century-and-the-birth-of-the-modern-mind_929/index.html</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-activists-tao-te-ching-ancient-advice-for-a-modern-revolution_928/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-activists-tao-te-ching-ancient-advice-for-a-modern-revolution_928/index.html</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/spark-joy-an-illustrated-master-class-on-the-art-of-organizing-and-tidying-up_927/index.html</t>
+          <t>https://books.toscrape.com/catalogue/spark-joy-an-illustrated-master-class-on-the-art-of-organizing-and-tidying-up_927/index.html</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/soul-reader_926/index.html</t>
+          <t>https://books.toscrape.com/catalogue/soul-reader_926/index.html</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/security_925/index.html</t>
+          <t>https://books.toscrape.com/catalogue/security_925/index.html</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/saga-volume-6-saga-collected-editions-6_924/index.html</t>
+          <t>https://books.toscrape.com/catalogue/saga-volume-6-saga-collected-editions-6_924/index.html</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/saga-volume-5-saga-collected-editions-5_923/index.html</t>
+          <t>https://books.toscrape.com/catalogue/saga-volume-5-saga-collected-editions-5_923/index.html</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/reskilling-america-learning-to-labor-in-the-twenty-first-century_922/index.html</t>
+          <t>https://books.toscrape.com/catalogue/reskilling-america-learning-to-labor-in-the-twenty-first-century_922/index.html</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/rat-queens-vol-3-demons-rat-queens-collected-editions-11-15_921/index.html</t>
+          <t>https://books.toscrape.com/catalogue/rat-queens-vol-3-demons-rat-queens-collected-editions-11-15_921/index.html</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/princess-jellyfish-2-in-1-omnibus-vol-01-princess-jellyfish-2-in-1-omnibus-1_920/index.html</t>
+          <t>https://books.toscrape.com/catalogue/princess-jellyfish-2-in-1-omnibus-vol-01-princess-jellyfish-2-in-1-omnibus-1_920/index.html</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/princess-between-worlds-wide-awake-princess-5_919/index.html</t>
+          <t>https://books.toscrape.com/catalogue/princess-between-worlds-wide-awake-princess-5_919/index.html</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/pop-gun-war-volume-1-gift_918/index.html</t>
+          <t>https://books.toscrape.com/catalogue/pop-gun-war-volume-1-gift_918/index.html</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/political-suicide-missteps-peccadilloes-bad-calls-backroom-hijinx-sordid-pasts-rotten-breaks-and-just-plain-dumb-mistakes-in-the-annals-of-american-politics_917/index.html</t>
+          <t>https://books.toscrape.com/catalogue/political-suicide-missteps-peccadilloes-bad-calls-backroom-hijinx-sordid-pasts-rotten-breaks-and-just-plain-dumb-mistakes-in-the-annals-of-american-politics_917/index.html</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/patience_916/index.html</t>
+          <t>https://books.toscrape.com/catalogue/patience_916/index.html</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/outcast-vol-1-a-darkness-surrounds-him-outcast-1_915/index.html</t>
+          <t>https://books.toscrape.com/catalogue/outcast-vol-1-a-darkness-surrounds-him-outcast-1_915/index.html</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/orange-the-complete-collection-1-orange-the-complete-collection-1_914/index.html</t>
+          <t>https://books.toscrape.com/catalogue/orange-the-complete-collection-1-orange-the-complete-collection-1_914/index.html</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/online-marketing-for-busy-authors-a-step-by-step-guide_913/index.html</t>
+          <t>https://books.toscrape.com/catalogue/online-marketing-for-busy-authors-a-step-by-step-guide_913/index.html</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/on-a-midnight-clear_912/index.html</t>
+          <t>https://books.toscrape.com/catalogue/on-a-midnight-clear_912/index.html</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/obsidian-lux-1_911/index.html</t>
+          <t>https://books.toscrape.com/catalogue/obsidian-lux-1_911/index.html</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/my-paris-kitchen-recipes-and-stories_910/index.html</t>
+          <t>https://books.toscrape.com/catalogue/my-paris-kitchen-recipes-and-stories_910/index.html</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/masks-and-shadows_909/index.html</t>
+          <t>https://books.toscrape.com/catalogue/masks-and-shadows_909/index.html</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/mama-tried-traditional-italian-cooking-for-the-screwed-crude-vegan-and-tattooed_908/index.html</t>
+          <t>https://books.toscrape.com/catalogue/mama-tried-traditional-italian-cooking-for-the-screwed-crude-vegan-and-tattooed_908/index.html</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/lumberjanes-vol-2-friendship-to-the-max-lumberjanes-5-8_907/index.html</t>
+          <t>https://books.toscrape.com/catalogue/lumberjanes-vol-2-friendship-to-the-max-lumberjanes-5-8_907/index.html</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/lumberjanes-vol-1-beware-the-kitten-holy-lumberjanes-1-4_906/index.html</t>
+          <t>https://books.toscrape.com/catalogue/lumberjanes-vol-1-beware-the-kitten-holy-lumberjanes-1-4_906/index.html</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/lumberjanes-vol-3-a-terrible-plan-lumberjanes-9-12_905/index.html</t>
+          <t>https://books.toscrape.com/catalogue/lumberjanes-vol-3-a-terrible-plan-lumberjanes-9-12_905/index.html</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/layered-baking-building-and-styling-spectacular-cakes_904/index.html</t>
+          <t>https://books.toscrape.com/catalogue/layered-baking-building-and-styling-spectacular-cakes_904/index.html</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/judo-seven-steps-to-black-belt-an-introductory-guide-for-beginners_903/index.html</t>
+          <t>https://books.toscrape.com/catalogue/judo-seven-steps-to-black-belt-an-introductory-guide-for-beginners_903/index.html</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/join_902/index.html</t>
+          <t>https://books.toscrape.com/catalogue/join_902/index.html</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3039,7 +3039,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/in-the-country-we-love-my-family-divided_901/index.html</t>
+          <t>https://books.toscrape.com/catalogue/in-the-country-we-love-my-family-divided_901/index.html</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/immunity-how-elie-metchnikoff-changed-the-course-of-modern-medicine_900/index.html</t>
+          <t>https://books.toscrape.com/catalogue/immunity-how-elie-metchnikoff-changed-the-course-of-modern-medicine_900/index.html</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/i-hate-fairyland-vol-1-madly-ever-after-i-hate-fairyland-compilations-1-5_899/index.html</t>
+          <t>https://books.toscrape.com/catalogue/i-hate-fairyland-vol-1-madly-ever-after-i-hate-fairyland-compilations-1-5_899/index.html</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/i-am-a-hero-omnibus-volume-1_898/index.html</t>
+          <t>https://books.toscrape.com/catalogue/i-am-a-hero-omnibus-volume-1_898/index.html</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/how-to-be-miserable-40-strategies-you-already-use_897/index.html</t>
+          <t>https://books.toscrape.com/catalogue/how-to-be-miserable-40-strategies-you-already-use_897/index.html</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/her-backup-boyfriend-the-sorensen-family-1_896/index.html</t>
+          <t>https://books.toscrape.com/catalogue/her-backup-boyfriend-the-sorensen-family-1_896/index.html</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/giant-days-vol-2-giant-days-5-8_895/index.html</t>
+          <t>https://books.toscrape.com/catalogue/giant-days-vol-2-giant-days-5-8_895/index.html</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/forever-and-forever-the-courtship-of-henry-longfellow-and-fanny-appleton_894/index.html</t>
+          <t>https://books.toscrape.com/catalogue/forever-and-forever-the-courtship-of-henry-longfellow-and-fanny-appleton_894/index.html</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/first-and-first-five-boroughs-3_893/index.html</t>
+          <t>https://books.toscrape.com/catalogue/first-and-first-five-boroughs-3_893/index.html</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/fifty-shades-darker-fifty-shades-2_892/index.html</t>
+          <t>https://books.toscrape.com/catalogue/fifty-shades-darker-fifty-shades-2_892/index.html</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/everydata-the-misinformation-hidden-in-the-little-data-you-consume-every-day_891/index.html</t>
+          <t>https://books.toscrape.com/catalogue/everydata-the-misinformation-hidden-in-the-little-data-you-consume-every-day_891/index.html</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/dont-be-a-jerk-and-other-practical-advice-from-dogen-japans-greatest-zen-master_890/index.html</t>
+          <t>https://books.toscrape.com/catalogue/dont-be-a-jerk-and-other-practical-advice-from-dogen-japans-greatest-zen-master_890/index.html</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/danganronpa-volume-1_889/index.html</t>
+          <t>https://books.toscrape.com/catalogue/danganronpa-volume-1_889/index.html</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/crown-of-midnight-throne-of-glass-2_888/index.html</t>
+          <t>https://books.toscrape.com/catalogue/crown-of-midnight-throne-of-glass-2_888/index.html</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/codename-baboushka-volume-1-the-conclave-of-death_887/index.html</t>
+          <t>https://books.toscrape.com/catalogue/codename-baboushka-volume-1-the-conclave-of-death_887/index.html</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/camp-midnight_886/index.html</t>
+          <t>https://books.toscrape.com/catalogue/camp-midnight_886/index.html</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/call-the-nurse-true-stories-of-a-country-nurse-on-a-scottish-isle_885/index.html</t>
+          <t>https://books.toscrape.com/catalogue/call-the-nurse-true-stories-of-a-country-nurse-on-a-scottish-isle_885/index.html</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/burning_884/index.html</t>
+          <t>https://books.toscrape.com/catalogue/burning_884/index.html</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/bossypants_883/index.html</t>
+          <t>https://books.toscrape.com/catalogue/bossypants_883/index.html</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/bitch-planet-vol-1-extraordinary-machine-bitch-planet-collected-editions_882/index.html</t>
+          <t>https://books.toscrape.com/catalogue/bitch-planet-vol-1-extraordinary-machine-bitch-planet-collected-editions_882/index.html</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/avatar-the-last-airbender-smoke-and-shadow-part-3-smoke-and-shadow-3_881/index.html</t>
+          <t>https://books.toscrape.com/catalogue/avatar-the-last-airbender-smoke-and-shadow-part-3-smoke-and-shadow-3_881/index.html</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -3585,7 +3585,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/algorithms-to-live-by-the-computer-science-of-human-decisions_880/index.html</t>
+          <t>https://books.toscrape.com/catalogue/algorithms-to-live-by-the-computer-science-of-human-decisions_880/index.html</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/a-world-of-flavor-your-gluten-free-passport_879/index.html</t>
+          <t>https://books.toscrape.com/catalogue/a-world-of-flavor-your-gluten-free-passport_879/index.html</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/a-piece-of-sky-a-grain-of-rice-a-memoir-in-four-meditations_878/index.html</t>
+          <t>https://books.toscrape.com/catalogue/a-piece-of-sky-a-grain-of-rice-a-memoir-in-four-meditations_878/index.html</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/a-murder-in-time_877/index.html</t>
+          <t>https://books.toscrape.com/catalogue/a-murder-in-time_877/index.html</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -3689,7 +3689,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/a-flight-of-arrows-the-pathfinders-2_876/index.html</t>
+          <t>https://books.toscrape.com/catalogue/a-flight-of-arrows-the-pathfinders-2_876/index.html</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/a-fierce-and-subtle-poison_875/index.html</t>
+          <t>https://books.toscrape.com/catalogue/a-fierce-and-subtle-poison_875/index.html</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/a-court-of-thorns-and-roses-a-court-of-thorns-and-roses-1_874/index.html</t>
+          <t>https://books.toscrape.com/catalogue/a-court-of-thorns-and-roses-a-court-of-thorns-and-roses-1_874/index.html</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/unqualified-how-god-uses-broken-people-to-do-big-things_873/index.html</t>
+          <t>https://books.toscrape.com/catalogue/unqualified-how-god-uses-broken-people-to-do-big-things_873/index.html</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/you-are-what-you-love-the-spiritual-power-of-habit_872/index.html</t>
+          <t>https://books.toscrape.com/catalogue/you-are-what-you-love-the-spiritual-power-of-habit_872/index.html</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/william-shakespeares-star-wars-verily-a-new-hope-william-shakespeares-star-wars-4_871/index.html</t>
+          <t>https://books.toscrape.com/catalogue/william-shakespeares-star-wars-verily-a-new-hope-william-shakespeares-star-wars-4_871/index.html</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/tuesday-nights-in-1980_870/index.html</t>
+          <t>https://books.toscrape.com/catalogue/tuesday-nights-in-1980_870/index.html</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/tracing-numbers-on-a-train_869/index.html</t>
+          <t>https://books.toscrape.com/catalogue/tracing-numbers-on-a-train_869/index.html</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -3897,7 +3897,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/throne-of-glass-throne-of-glass-1_868/index.html</t>
+          <t>https://books.toscrape.com/catalogue/throne-of-glass-throne-of-glass-1_868/index.html</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/thomas-jefferson-and-the-tripoli-pirates-the-forgotten-war-that-changed-american-history_867/index.html</t>
+          <t>https://books.toscrape.com/catalogue/thomas-jefferson-and-the-tripoli-pirates-the-forgotten-war-that-changed-american-history_867/index.html</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/thirteen-reasons-why_866/index.html</t>
+          <t>https://books.toscrape.com/catalogue/thirteen-reasons-why_866/index.html</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-white-cat-and-the-monk-a-retelling-of-the-poem-pangur-ban_865/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-white-cat-and-the-monk-a-retelling-of-the-poem-pangur-ban_865/index.html</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-wedding-dress_864/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-wedding-dress_864/index.html</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-vacationers_863/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-vacationers_863/index.html</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-third-wave-an-entrepreneurs-vision-of-the-future_862/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-third-wave-an-entrepreneurs-vision-of-the-future_862/index.html</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-stranger_861/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-stranger_861/index.html</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-shadow-hero-the-shadow-hero_860/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-shadow-hero-the-shadow-hero_860/index.html</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-secret-the-secret-1_859/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-secret-the-secret-1_859/index.html</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-regional-office-is-under-attack_858/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-regional-office-is-under-attack_858/index.html</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-psychopath-test-a-journey-through-the-madness-industry_857/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-psychopath-test-a-journey-through-the-madness-industry_857/index.html</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-project_856/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-project_856/index.html</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-power-of-now-a-guide-to-spiritual-enlightenment_855/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-power-of-now-a-guide-to-spiritual-enlightenment_855/index.html</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-omnivores-dilemma-a-natural-history-of-four-meals_854/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-omnivores-dilemma-a-natural-history-of-four-meals_854/index.html</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-nerdy-nummies-cookbook-sweet-treats-for-the-geek-in-all-of-us_853/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-nerdy-nummies-cookbook-sweet-treats-for-the-geek-in-all-of-us_853/index.html</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -4313,7 +4313,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-murder-of-roger-ackroyd-hercule-poirot-4_852/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-murder-of-roger-ackroyd-hercule-poirot-4_852/index.html</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-mistake-off-campus-2_851/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-mistake-off-campus-2_851/index.html</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-matchmakers-playbook-wingmen-inc-1_850/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-matchmakers-playbook-wingmen-inc-1_850/index.html</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-love-and-lemons-cookbook-an-apple-to-zucchini-celebration-of-impromptu-cooking_849/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-love-and-lemons-cookbook-an-apple-to-zucchini-celebration-of-impromptu-cooking_849/index.html</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-long-shadow-of-small-ghosts-murder-and-memory-in-an-american-city_848/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-long-shadow-of-small-ghosts-murder-and-memory-in-an-american-city_848/index.html</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-kite-runner_847/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-kite-runner_847/index.html</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-house-by-the-lake_846/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-house-by-the-lake_846/index.html</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-glittering-court-the-glittering-court-1_845/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-glittering-court-the-glittering-court-1_845/index.html</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-girl-on-the-train_844/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-girl-on-the-train_844/index.html</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-genius-of-birds_843/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-genius-of-birds_843/index.html</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-emerald-mystery_842/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-emerald-mystery_842/index.html</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-cookies-cups-cookbook-125-sweet-savory-recipes-reminding-you-to-always-eat-dessert-first_841/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-cookies-cups-cookbook-125-sweet-savory-recipes-reminding-you-to-always-eat-dessert-first_841/index.html</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-bridge-to-consciousness-im-writing-the-bridge-between-science-and-our-old-and-new-beliefs_840/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-bridge-to-consciousness-im-writing-the-bridge-between-science-and-our-old-and-new-beliefs_840/index.html</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-artists-way-a-spiritual-path-to-higher-creativity_839/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-artists-way-a-spiritual-path-to-higher-creativity_839/index.html</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-art-of-war_838/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-art-of-war_838/index.html</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-argonauts_837/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-argonauts_837/index.html</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-10-entrepreneur-live-your-startup-dream-without-quitting-your-day-job_836/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-10-entrepreneur-live-your-startup-dream-without-quitting-your-day-job_836/index.html</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/suddenly-in-love-lake-haven-1_835/index.html</t>
+          <t>https://books.toscrape.com/catalogue/suddenly-in-love-lake-haven-1_835/index.html</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/something-more-than-this_834/index.html</t>
+          <t>https://books.toscrape.com/catalogue/something-more-than-this_834/index.html</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/soft-apocalypse_833/index.html</t>
+          <t>https://books.toscrape.com/catalogue/soft-apocalypse_833/index.html</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/so-youve-been-publicly-shamed_832/index.html</t>
+          <t>https://books.toscrape.com/catalogue/so-youve-been-publicly-shamed_832/index.html</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/shoe-dog-a-memoir-by-the-creator-of-nike_831/index.html</t>
+          <t>https://books.toscrape.com/catalogue/shoe-dog-a-memoir-by-the-creator-of-nike_831/index.html</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/shobu-samurai-project-aryoku-3_830/index.html</t>
+          <t>https://books.toscrape.com/catalogue/shobu-samurai-project-aryoku-3_830/index.html</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/secrets-and-lace-fatal-hearts-1_829/index.html</t>
+          <t>https://books.toscrape.com/catalogue/secrets-and-lace-fatal-hearts-1_829/index.html</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/scarlett-epstein-hates-it-here_828/index.html</t>
+          <t>https://books.toscrape.com/catalogue/scarlett-epstein-hates-it-here_828/index.html</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/romero-and-juliet-a-tragic-tale-of-love-and-zombies_827/index.html</t>
+          <t>https://books.toscrape.com/catalogue/romero-and-juliet-a-tragic-tale-of-love-and-zombies_827/index.html</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/redeeming-love_826/index.html</t>
+          <t>https://books.toscrape.com/catalogue/redeeming-love_826/index.html</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -5015,7 +5015,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/poses-for-artists-volume-1-dynamic-and-sitting-poses-an-essential-reference-for-figure-drawing-and-the-human-form_825/index.html</t>
+          <t>https://books.toscrape.com/catalogue/poses-for-artists-volume-1-dynamic-and-sitting-poses-an-essential-reference-for-figure-drawing-and-the-human-form_825/index.html</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/poems-that-make-grown-women-cry_824/index.html</t>
+          <t>https://books.toscrape.com/catalogue/poems-that-make-grown-women-cry_824/index.html</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/nightingale-sing_823/index.html</t>
+          <t>https://books.toscrape.com/catalogue/nightingale-sing_823/index.html</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/night-sky-with-exit-wounds_822/index.html</t>
+          <t>https://books.toscrape.com/catalogue/night-sky-with-exit-wounds_822/index.html</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/mrs-houdini_821/index.html</t>
+          <t>https://books.toscrape.com/catalogue/mrs-houdini_821/index.html</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/modern-romance_820/index.html</t>
+          <t>https://books.toscrape.com/catalogue/modern-romance_820/index.html</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/miss-peregrines-home-for-peculiar-children-miss-peregrines-peculiar-children-1_819/index.html</t>
+          <t>https://books.toscrape.com/catalogue/miss-peregrines-home-for-peculiar-children-miss-peregrines-peculiar-children-1_819/index.html</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/louisa-the-extraordinary-life-of-mrs-adams_818/index.html</t>
+          <t>https://books.toscrape.com/catalogue/louisa-the-extraordinary-life-of-mrs-adams_818/index.html</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/little-red_817/index.html</t>
+          <t>https://books.toscrape.com/catalogue/little-red_817/index.html</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/library-of-souls-miss-peregrines-peculiar-children-3_816/index.html</t>
+          <t>https://books.toscrape.com/catalogue/library-of-souls-miss-peregrines-peculiar-children-3_816/index.html</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -5275,7 +5275,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/large-print-heart-of-the-pride_815/index.html</t>
+          <t>https://books.toscrape.com/catalogue/large-print-heart-of-the-pride_815/index.html</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/i-had-a-nice-time-and-other-lies-how-to-find-love-sht-like-that_814/index.html</t>
+          <t>https://books.toscrape.com/catalogue/i-had-a-nice-time-and-other-lies-how-to-find-love-sht-like-that_814/index.html</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/hollow-city-miss-peregrines-peculiar-children-2_813/index.html</t>
+          <t>https://books.toscrape.com/catalogue/hollow-city-miss-peregrines-peculiar-children-2_813/index.html</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/grumbles_812/index.html</t>
+          <t>https://books.toscrape.com/catalogue/grumbles_812/index.html</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/full-moon-over-noahs-ark-an-odyssey-to-mount-ararat-and-beyond_811/index.html</t>
+          <t>https://books.toscrape.com/catalogue/full-moon-over-noahs-ark-an-odyssey-to-mount-ararat-and-beyond_811/index.html</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/frostbite-vampire-academy-2_810/index.html</t>
+          <t>https://books.toscrape.com/catalogue/frostbite-vampire-academy-2_810/index.html</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/follow-you-home_809/index.html</t>
+          <t>https://books.toscrape.com/catalogue/follow-you-home_809/index.html</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/first-steps-for-new-christians-print-edition_808/index.html</t>
+          <t>https://books.toscrape.com/catalogue/first-steps-for-new-christians-print-edition_808/index.html</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/finders-keepers-bill-hodges-trilogy-2_807/index.html</t>
+          <t>https://books.toscrape.com/catalogue/finders-keepers-bill-hodges-trilogy-2_807/index.html</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/fables-vol-1-legends-in-exile-fables-1_806/index.html</t>
+          <t>https://books.toscrape.com/catalogue/fables-vol-1-legends-in-exile-fables-1_806/index.html</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/eureka-trivia-60_805/index.html</t>
+          <t>https://books.toscrape.com/catalogue/eureka-trivia-60_805/index.html</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/drive-the-surprising-truth-about-what-motivates-us_804/index.html</t>
+          <t>https://books.toscrape.com/catalogue/drive-the-surprising-truth-about-what-motivates-us_804/index.html</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/done-rubbed-out-reightman-bailey-1_803/index.html</t>
+          <t>https://books.toscrape.com/catalogue/done-rubbed-out-reightman-bailey-1_803/index.html</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -5613,7 +5613,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/doing-it-over-most-likely-to-1_802/index.html</t>
+          <t>https://books.toscrape.com/catalogue/doing-it-over-most-likely-to-1_802/index.html</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/deliciously-ella-every-day-quick-and-easy-recipes-for-gluten-free-snacks-packed-lunches-and-simple-meals_801/index.html</t>
+          <t>https://books.toscrape.com/catalogue/deliciously-ella-every-day-quick-and-easy-recipes-for-gluten-free-snacks-packed-lunches-and-simple-meals_801/index.html</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/dark-notes_800/index.html</t>
+          <t>https://books.toscrape.com/catalogue/dark-notes_800/index.html</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/daring-greatly-how-the-courage-to-be-vulnerable-transforms-the-way-we-live-love-parent-and-lead_799/index.html</t>
+          <t>https://books.toscrape.com/catalogue/daring-greatly-how-the-courage-to-be-vulnerable-transforms-the-way-we-live-love-parent-and-lead_799/index.html</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/close-to-you_798/index.html</t>
+          <t>https://books.toscrape.com/catalogue/close-to-you_798/index.html</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/chasing-heaven-what-dying-taught-me-about-living_797/index.html</t>
+          <t>https://books.toscrape.com/catalogue/chasing-heaven-what-dying-taught-me-about-living_797/index.html</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -5769,7 +5769,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/big-magic-creative-living-beyond-fear_796/index.html</t>
+          <t>https://books.toscrape.com/catalogue/big-magic-creative-living-beyond-fear_796/index.html</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/becoming-wise-an-inquiry-into-the-mystery-and-art-of-living_795/index.html</t>
+          <t>https://books.toscrape.com/catalogue/becoming-wise-an-inquiry-into-the-mystery-and-art-of-living_795/index.html</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -5821,7 +5821,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/beauty-restored-riley-family-legacy-novellas-3_794/index.html</t>
+          <t>https://books.toscrape.com/catalogue/beauty-restored-riley-family-legacy-novellas-3_794/index.html</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -5847,7 +5847,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/batman-the-long-halloween-batman_793/index.html</t>
+          <t>https://books.toscrape.com/catalogue/batman-the-long-halloween-batman_793/index.html</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/batman-the-dark-knight-returns-batman_792/index.html</t>
+          <t>https://books.toscrape.com/catalogue/batman-the-dark-knight-returns-batman_792/index.html</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/ayumis-violin_791/index.html</t>
+          <t>https://books.toscrape.com/catalogue/ayumis-violin_791/index.html</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -5925,7 +5925,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/anonymous_790/index.html</t>
+          <t>https://books.toscrape.com/catalogue/anonymous_790/index.html</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/amy-meets-the-saints-and-sages_789/index.html</t>
+          <t>https://books.toscrape.com/catalogue/amy-meets-the-saints-and-sages_789/index.html</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -5977,7 +5977,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/amid-the-chaos_788/index.html</t>
+          <t>https://books.toscrape.com/catalogue/amid-the-chaos_788/index.html</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/amatus_787/index.html</t>
+          <t>https://books.toscrape.com/catalogue/amatus_787/index.html</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -6029,7 +6029,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/agnostic-a-spirited-manifesto_786/index.html</t>
+          <t>https://books.toscrape.com/catalogue/agnostic-a-spirited-manifesto_786/index.html</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/zealot-the-life-and-times-of-jesus-of-nazareth_785/index.html</t>
+          <t>https://books.toscrape.com/catalogue/zealot-the-life-and-times-of-jesus-of-nazareth_785/index.html</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/you-you-1_784/index.html</t>
+          <t>https://books.toscrape.com/catalogue/you-you-1_784/index.html</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/wonder-woman-earth-one-volume-one-wonder-woman-earth-one-1_783/index.html</t>
+          <t>https://books.toscrape.com/catalogue/wonder-woman-earth-one-volume-one-wonder-woman-earth-one-1_783/index.html</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/wild-swans_782/index.html</t>
+          <t>https://books.toscrape.com/catalogue/wild-swans_782/index.html</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -6159,7 +6159,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/why-the-right-went-wrong-conservatism-from-goldwater-to-the-tea-party-and-beyond_781/index.html</t>
+          <t>https://books.toscrape.com/catalogue/why-the-right-went-wrong-conservatism-from-goldwater-to-the-tea-party-and-beyond_781/index.html</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/whole-lotta-creativity-going-on-60-fun-and-unusual-exercises-to-awaken-and-strengthen-your-creativity_780/index.html</t>
+          <t>https://books.toscrape.com/catalogue/whole-lotta-creativity-going-on-60-fun-and-unusual-exercises-to-awaken-and-strengthen-your-creativity_780/index.html</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/whats-it-like-in-space-stories-from-astronauts-whove-been-there_779/index.html</t>
+          <t>https://books.toscrape.com/catalogue/whats-it-like-in-space-stories-from-astronauts-whove-been-there_779/index.html</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/we-are-robin-vol-1-the-vigilante-business-we-are-robin-1_778/index.html</t>
+          <t>https://books.toscrape.com/catalogue/we-are-robin-vol-1-the-vigilante-business-we-are-robin-1_778/index.html</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/walt-disneys-alice-in-wonderland_777/index.html</t>
+          <t>https://books.toscrape.com/catalogue/walt-disneys-alice-in-wonderland_777/index.html</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -6289,7 +6289,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/v-for-vendetta-v-for-vendetta-complete_776/index.html</t>
+          <t>https://books.toscrape.com/catalogue/v-for-vendetta-v-for-vendetta-complete_776/index.html</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -6315,7 +6315,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/until-friday-night-the-field-party-1_775/index.html</t>
+          <t>https://books.toscrape.com/catalogue/until-friday-night-the-field-party-1_775/index.html</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/unbroken-a-world-war-ii-story-of-survival-resilience-and-redemption_774/index.html</t>
+          <t>https://books.toscrape.com/catalogue/unbroken-a-world-war-ii-story-of-survival-resilience-and-redemption_774/index.html</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/twenty-yawns_773/index.html</t>
+          <t>https://books.toscrape.com/catalogue/twenty-yawns_773/index.html</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/through-the-woods_772/index.html</t>
+          <t>https://books.toscrape.com/catalogue/through-the-woods_772/index.html</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/this-is-where-it-ends_771/index.html</t>
+          <t>https://books.toscrape.com/catalogue/this-is-where-it-ends_771/index.html</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-year-of-magical-thinking_770/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-year-of-magical-thinking_770/index.html</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-wright-brothers_769/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-wright-brothers_769/index.html</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-white-queen-the-cousins-war-1_768/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-white-queen-the-cousins-war-1_768/index.html</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-wedding-pact-the-omalleys-2_767/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-wedding-pact-the-omalleys-2_767/index.html</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-time-keeper_766/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-time-keeper_766/index.html</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -6575,7 +6575,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-testament-of-mary_765/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-testament-of-mary_765/index.html</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-star-touched-queen_764/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-star-touched-queen_764/index.html</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -6627,7 +6627,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-songs-of-the-gods_763/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-songs-of-the-gods_763/index.html</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-song-of-achilles_762/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-song-of-achilles_762/index.html</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -6679,7 +6679,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-rosie-project-don-tillman-1_761/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-rosie-project-don-tillman-1_761/index.html</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-power-of-habit-why-we-do-what-we-do-in-life-and-business_760/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-power-of-habit-why-we-do-what-we-do-in-life-and-business_760/index.html</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-marriage-of-opposites_759/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-marriage-of-opposites_759/index.html</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-lucifer-effect-understanding-how-good-people-turn-evil_758/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-lucifer-effect-understanding-how-good-people-turn-evil_758/index.html</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -6783,7 +6783,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-long-haul-diary-of-a-wimpy-kid-9_757/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-long-haul-diary-of-a-wimpy-kid-9_757/index.html</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -6809,7 +6809,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-loney_756/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-loney_756/index.html</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -6835,7 +6835,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-literature-book-big-ideas-simply-explained_755/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-literature-book-big-ideas-simply-explained_755/index.html</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-last-mile-amos-decker-2_754/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-last-mile-amos-decker-2_754/index.html</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-immortal-life-of-henrietta-lacks_753/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-immortal-life-of-henrietta-lacks_753/index.html</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -6913,7 +6913,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-hidden-oracle-the-trials-of-apollo-1_752/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-hidden-oracle-the-trials-of-apollo-1_752/index.html</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-help-yourself-cookbook-for-kids-60-easy-plant-based-recipes-kids-can-make-to-stay-healthy-and-save-the-earth_751/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-help-yourself-cookbook-for-kids-60-easy-plant-based-recipes-kids-can-make-to-stay-healthy-and-save-the-earth_751/index.html</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -6965,7 +6965,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-guilty-will-robie-4_750/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-guilty-will-robie-4_750/index.html</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-first-hostage-jb-collins-2_749/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-first-hostage-jb-collins-2_749/index.html</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-dovekeepers_748/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-dovekeepers_748/index.html</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-darkest-lie_747/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-darkest-lie_747/index.html</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -7069,7 +7069,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-bane-chronicles-the-bane-chronicles-1-11_746/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-bane-chronicles-the-bane-chronicles-1-11_746/index.html</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -7095,7 +7095,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-bad-ass-librarians-of-timbuktu-and-their-race-to-save-the-worlds-most-precious-manuscripts_745/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-bad-ass-librarians-of-timbuktu-and-their-race-to-save-the-worlds-most-precious-manuscripts_745/index.html</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-14th-colony-cotton-malone-11_744/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-14th-colony-cotton-malone-11_744/index.html</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/that-darkness-gardiner-and-renner-1_743/index.html</t>
+          <t>https://books.toscrape.com/catalogue/that-darkness-gardiner-and-renner-1_743/index.html</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/tastes-like-fear-di-marnie-rome-3_742/index.html</t>
+          <t>https://books.toscrape.com/catalogue/tastes-like-fear-di-marnie-rome-3_742/index.html</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/take-me-with-you_741/index.html</t>
+          <t>https://books.toscrape.com/catalogue/take-me-with-you_741/index.html</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -7225,7 +7225,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/swell-a-year-of-waves_740/index.html</t>
+          <t>https://books.toscrape.com/catalogue/swell-a-year-of-waves_740/index.html</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/superman-vol-1-before-truth-superman-by-gene-luen-yang-1_739/index.html</t>
+          <t>https://books.toscrape.com/catalogue/superman-vol-1-before-truth-superman-by-gene-luen-yang-1_739/index.html</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -7277,7 +7277,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/still-life-with-bread-crumbs_738/index.html</t>
+          <t>https://books.toscrape.com/catalogue/still-life-with-bread-crumbs_738/index.html</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -7303,7 +7303,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/steve-jobs_737/index.html</t>
+          <t>https://books.toscrape.com/catalogue/steve-jobs_737/index.html</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -7329,7 +7329,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/sorting-the-beef-from-the-bull-the-science-of-food-fraud-forensics_736/index.html</t>
+          <t>https://books.toscrape.com/catalogue/sorting-the-beef-from-the-bull-the-science-of-food-fraud-forensics_736/index.html</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -7355,7 +7355,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/someone-like-you-the-harrisons-2_735/index.html</t>
+          <t>https://books.toscrape.com/catalogue/someone-like-you-the-harrisons-2_735/index.html</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/so-cute-it-hurts-vol-6-so-cute-it-hurts-6_734/index.html</t>
+          <t>https://books.toscrape.com/catalogue/so-cute-it-hurts-vol-6-so-cute-it-hurts-6_734/index.html</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -7407,7 +7407,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/shtum_733/index.html</t>
+          <t>https://books.toscrape.com/catalogue/shtum_733/index.html</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/see-america-a-celebration-of-our-national-parks-treasured-sites_732/index.html</t>
+          <t>https://books.toscrape.com/catalogue/see-america-a-celebration-of-our-national-parks-treasured-sites_732/index.html</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/salt_731/index.html</t>
+          <t>https://books.toscrape.com/catalogue/salt_731/index.html</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -7485,7 +7485,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/robin-war_730/index.html</t>
+          <t>https://books.toscrape.com/catalogue/robin-war_730/index.html</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/red-hoodarsenal-vol-1-open-for-business-red-hoodarsenal-1_729/index.html</t>
+          <t>https://books.toscrape.com/catalogue/red-hoodarsenal-vol-1-open-for-business-red-hoodarsenal-1_729/index.html</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -7537,7 +7537,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/rain-fish_728/index.html</t>
+          <t>https://books.toscrape.com/catalogue/rain-fish_728/index.html</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/quarter-life-poetry-poems-for-the-young-broke-and-hangry_727/index.html</t>
+          <t>https://books.toscrape.com/catalogue/quarter-life-poetry-poems-for-the-young-broke-and-hangry_727/index.html</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -7589,7 +7589,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/pet-sematary_726/index.html</t>
+          <t>https://books.toscrape.com/catalogue/pet-sematary_726/index.html</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -7615,7 +7615,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/overload-how-to-unplug-unwind-and-unleash-yourself-from-the-pressure-of-stress_725/index.html</t>
+          <t>https://books.toscrape.com/catalogue/overload-how-to-unplug-unwind-and-unleash-yourself-from-the-pressure-of-stress_725/index.html</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -7641,7 +7641,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/once-was-a-time_724/index.html</t>
+          <t>https://books.toscrape.com/catalogue/once-was-a-time_724/index.html</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -7667,7 +7667,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/old-school-diary-of-a-wimpy-kid-10_723/index.html</t>
+          <t>https://books.toscrape.com/catalogue/old-school-diary-of-a-wimpy-kid-10_723/index.html</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/no-dream-is-too-high-life-lessons-from-a-man-who-walked-on-the-moon_722/index.html</t>
+          <t>https://books.toscrape.com/catalogue/no-dream-is-too-high-life-lessons-from-a-man-who-walked-on-the-moon_722/index.html</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -7719,7 +7719,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/naruto-3-in-1-edition-vol-14-includes-vols-40-41-42-naruto-omnibus-14_721/index.html</t>
+          <t>https://books.toscrape.com/catalogue/naruto-3-in-1-edition-vol-14-includes-vols-40-41-42-naruto-omnibus-14_721/index.html</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -7745,7 +7745,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/my-name-is-lucy-barton_720/index.html</t>
+          <t>https://books.toscrape.com/catalogue/my-name-is-lucy-barton_720/index.html</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/my-mrs-brown_719/index.html</t>
+          <t>https://books.toscrape.com/catalogue/my-mrs-brown_719/index.html</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/my-kind-of-crazy_718/index.html</t>
+          <t>https://books.toscrape.com/catalogue/my-kind-of-crazy_718/index.html</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/mr-mercedes-bill-hodges-trilogy-1_717/index.html</t>
+          <t>https://books.toscrape.com/catalogue/mr-mercedes-bill-hodges-trilogy-1_717/index.html</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/more-than-music-chasing-the-dream-1_716/index.html</t>
+          <t>https://books.toscrape.com/catalogue/more-than-music-chasing-the-dream-1_716/index.html</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/made-to-stick-why-some-ideas-survive-and-others-die_715/index.html</t>
+          <t>https://books.toscrape.com/catalogue/made-to-stick-why-some-ideas-survive-and-others-die_715/index.html</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/luis-paints-the-world_714/index.html</t>
+          <t>https://books.toscrape.com/catalogue/luis-paints-the-world_714/index.html</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -7927,7 +7927,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/luckiest-girl-alive_713/index.html</t>
+          <t>https://books.toscrape.com/catalogue/luckiest-girl-alive_713/index.html</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/lowriders-to-the-center-of-the-earth-lowriders-in-space-2_712/index.html</t>
+          <t>https://books.toscrape.com/catalogue/lowriders-to-the-center-of-the-earth-lowriders-in-space-2_712/index.html</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -7979,7 +7979,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/love-is-a-mix-tape-music-1_711/index.html</t>
+          <t>https://books.toscrape.com/catalogue/love-is-a-mix-tape-music-1_711/index.html</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -8005,7 +8005,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/looking-for-lovely-collecting-the-moments-that-matter_710/index.html</t>
+          <t>https://books.toscrape.com/catalogue/looking-for-lovely-collecting-the-moments-that-matter_710/index.html</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/living-leadership-by-insight-a-good-leader-achieves-a-great-leader-builds-monuments_709/index.html</t>
+          <t>https://books.toscrape.com/catalogue/living-leadership-by-insight-a-good-leader-achieves-a-great-leader-builds-monuments_709/index.html</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -8057,7 +8057,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/let-it-out-a-journey-through-journaling_708/index.html</t>
+          <t>https://books.toscrape.com/catalogue/let-it-out-a-journey-through-journaling_708/index.html</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/lady-midnight-the-dark-artifices-1_707/index.html</t>
+          <t>https://books.toscrape.com/catalogue/lady-midnight-the-dark-artifices-1_707/index.html</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/its-all-easy-healthy-delicious-weeknight-meals-in-under-30-minutes_706/index.html</t>
+          <t>https://books.toscrape.com/catalogue/its-all-easy-healthy-delicious-weeknight-meals-in-under-30-minutes_706/index.html</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -8135,7 +8135,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/island-of-dragons-unwanteds-7_705/index.html</t>
+          <t>https://books.toscrape.com/catalogue/island-of-dragons-unwanteds-7_705/index.html</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/i-know-what-im-doing-and-other-lies-i-tell-myself-dispatches-from-a-life-under-construction_704/index.html</t>
+          <t>https://books.toscrape.com/catalogue/i-know-what-im-doing-and-other-lies-i-tell-myself-dispatches-from-a-life-under-construction_704/index.html</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -8187,7 +8187,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/i-am-pilgrim-pilgrim-1_703/index.html</t>
+          <t>https://books.toscrape.com/catalogue/i-am-pilgrim-pilgrim-1_703/index.html</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/hyperbole-and-a-half-unfortunate-situations-flawed-coping-mechanisms-mayhem-and-other-things-that-happened_702/index.html</t>
+          <t>https://books.toscrape.com/catalogue/hyperbole-and-a-half-unfortunate-situations-flawed-coping-mechanisms-mayhem-and-other-things-that-happened_702/index.html</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/hush-hush-hush-hush-1_701/index.html</t>
+          <t>https://books.toscrape.com/catalogue/hush-hush-hush-hush-1_701/index.html</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -8265,7 +8265,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/hold-your-breath-search-and-rescue-1_700/index.html</t>
+          <t>https://books.toscrape.com/catalogue/hold-your-breath-search-and-rescue-1_700/index.html</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/hamilton-the-revolution_699/index.html</t>
+          <t>https://books.toscrape.com/catalogue/hamilton-the-revolution_699/index.html</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/greek-mythic-history_698/index.html</t>
+          <t>https://books.toscrape.com/catalogue/greek-mythic-history_698/index.html</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
@@ -8343,7 +8343,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/god-the-most-unpleasant-character-in-all-fiction_697/index.html</t>
+          <t>https://books.toscrape.com/catalogue/god-the-most-unpleasant-character-in-all-fiction_697/index.html</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
@@ -8369,7 +8369,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/glory-over-everything-beyond-the-kitchen-house_696/index.html</t>
+          <t>https://books.toscrape.com/catalogue/glory-over-everything-beyond-the-kitchen-house_696/index.html</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/feathers-displays-of-brilliant-plumage_695/index.html</t>
+          <t>https://books.toscrape.com/catalogue/feathers-displays-of-brilliant-plumage_695/index.html</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/far-away-places-on-the-brink-of-change-seven-continents-twenty-five-years_694/index.html</t>
+          <t>https://books.toscrape.com/catalogue/far-away-places-on-the-brink-of-change-seven-continents-twenty-five-years_694/index.html</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
@@ -8447,7 +8447,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/every-last-word_693/index.html</t>
+          <t>https://books.toscrape.com/catalogue/every-last-word_693/index.html</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
@@ -8473,7 +8473,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/eligible-the-austen-project-4_692/index.html</t>
+          <t>https://books.toscrape.com/catalogue/eligible-the-austen-project-4_692/index.html</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
@@ -8499,7 +8499,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/el-deafo_691/index.html</t>
+          <t>https://books.toscrape.com/catalogue/el-deafo_691/index.html</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
@@ -8525,7 +8525,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/eight-hundred-grapes_690/index.html</t>
+          <t>https://books.toscrape.com/catalogue/eight-hundred-grapes_690/index.html</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/eaternity-more-than-150-deliciously-easy-vegan-recipes-for-a-long-healthy-satisfied-joyful-life_689/index.html</t>
+          <t>https://books.toscrape.com/catalogue/eaternity-more-than-150-deliciously-easy-vegan-recipes-for-a-long-healthy-satisfied-joyful-life_689/index.html</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
@@ -8577,7 +8577,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/eat-fat-get-thin_688/index.html</t>
+          <t>https://books.toscrape.com/catalogue/eat-fat-get-thin_688/index.html</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
@@ -8603,7 +8603,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/dont-get-caught_687/index.html</t>
+          <t>https://books.toscrape.com/catalogue/dont-get-caught_687/index.html</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
@@ -8629,7 +8629,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/doctor-sleep-the-shining-2_686/index.html</t>
+          <t>https://books.toscrape.com/catalogue/doctor-sleep-the-shining-2_686/index.html</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
@@ -8655,7 +8655,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/demigods-magicians-percy-and-annabeth-meet-the-kanes-percy-jackson-kane-chronicles-crossover-1-3_685/index.html</t>
+          <t>https://books.toscrape.com/catalogue/demigods-magicians-percy-and-annabeth-meet-the-kanes-percy-jackson-kane-chronicles-crossover-1-3_685/index.html</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/dear-mr-knightley_684/index.html</t>
+          <t>https://books.toscrape.com/catalogue/dear-mr-knightley_684/index.html</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
@@ -8707,7 +8707,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/daily-fantasy-sports_683/index.html</t>
+          <t>https://books.toscrape.com/catalogue/daily-fantasy-sports_683/index.html</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
@@ -8733,7 +8733,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/crazy-love-overwhelmed-by-a-relentless-god_682/index.html</t>
+          <t>https://books.toscrape.com/catalogue/crazy-love-overwhelmed-by-a-relentless-god_682/index.html</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
@@ -8759,7 +8759,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/cometh-the-hour-the-clifton-chronicles-6_681/index.html</t>
+          <t>https://books.toscrape.com/catalogue/cometh-the-hour-the-clifton-chronicles-6_681/index.html</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
@@ -8785,7 +8785,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/code-name-verity-code-name-verity-1_680/index.html</t>
+          <t>https://books.toscrape.com/catalogue/code-name-verity-code-name-verity-1_680/index.html</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
@@ -8811,7 +8811,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/clockwork-angel-the-infernal-devices-1_679/index.html</t>
+          <t>https://books.toscrape.com/catalogue/clockwork-angel-the-infernal-devices-1_679/index.html</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
@@ -8837,7 +8837,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/city-of-glass-the-mortal-instruments-3_678/index.html</t>
+          <t>https://books.toscrape.com/catalogue/city-of-glass-the-mortal-instruments-3_678/index.html</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
@@ -8863,7 +8863,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/city-of-fallen-angels-the-mortal-instruments-4_677/index.html</t>
+          <t>https://books.toscrape.com/catalogue/city-of-fallen-angels-the-mortal-instruments-4_677/index.html</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/city-of-bones-the-mortal-instruments-1_676/index.html</t>
+          <t>https://books.toscrape.com/catalogue/city-of-bones-the-mortal-instruments-1_676/index.html</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
@@ -8915,7 +8915,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/city-of-ashes-the-mortal-instruments-2_675/index.html</t>
+          <t>https://books.toscrape.com/catalogue/city-of-ashes-the-mortal-instruments-2_675/index.html</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/cell_674/index.html</t>
+          <t>https://books.toscrape.com/catalogue/cell_674/index.html</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/catching-jordan-hundred-oaks_673/index.html</t>
+          <t>https://books.toscrape.com/catalogue/catching-jordan-hundred-oaks_673/index.html</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
@@ -8993,7 +8993,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/carry-on-warrior-thoughts-on-life-unarmed_672/index.html</t>
+          <t>https://books.toscrape.com/catalogue/carry-on-warrior-thoughts-on-life-unarmed_672/index.html</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
@@ -9019,7 +9019,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/carrie_671/index.html</t>
+          <t>https://books.toscrape.com/catalogue/carrie_671/index.html</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
@@ -9045,7 +9045,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/buying-in-the-secret-dialogue-between-what-we-buy-and-who-we-are_670/index.html</t>
+          <t>https://books.toscrape.com/catalogue/buying-in-the-secret-dialogue-between-what-we-buy-and-who-we-are_670/index.html</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/brain-on-fire-my-month-of-madness_669/index.html</t>
+          <t>https://books.toscrape.com/catalogue/brain-on-fire-my-month-of-madness_669/index.html</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
@@ -9097,7 +9097,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/batman-europa_668/index.html</t>
+          <t>https://books.toscrape.com/catalogue/batman-europa_668/index.html</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
@@ -9123,7 +9123,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/barefoot-contessa-back-to-basics_667/index.html</t>
+          <t>https://books.toscrape.com/catalogue/barefoot-contessa-back-to-basics_667/index.html</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/barefoot-contessa-at-home-everyday-recipes-youll-make-over-and-over-again_666/index.html</t>
+          <t>https://books.toscrape.com/catalogue/barefoot-contessa-at-home-everyday-recipes-youll-make-over-and-over-again_666/index.html</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
@@ -9175,7 +9175,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/balloon-animals_665/index.html</t>
+          <t>https://books.toscrape.com/catalogue/balloon-animals_665/index.html</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/art-ops-vol-1_664/index.html</t>
+          <t>https://books.toscrape.com/catalogue/art-ops-vol-1_664/index.html</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
@@ -9227,7 +9227,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/aristotle-and-dante-discover-the-secrets-of-the-universe-aristotle-and-dante-discover-the-secrets-of-the-universe-1_663/index.html</t>
+          <t>https://books.toscrape.com/catalogue/aristotle-and-dante-discover-the-secrets-of-the-universe-aristotle-and-dante-discover-the-secrets-of-the-universe-1_663/index.html</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
@@ -9253,7 +9253,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/angels-walking-angels-walking-1_662/index.html</t>
+          <t>https://books.toscrape.com/catalogue/angels-walking-angels-walking-1_662/index.html</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
@@ -9279,7 +9279,7 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/angels-demons-robert-langdon-1_661/index.html</t>
+          <t>https://books.toscrape.com/catalogue/angels-demons-robert-langdon-1_661/index.html</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
@@ -9305,7 +9305,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/all-the-light-we-cannot-see_660/index.html</t>
+          <t>https://books.toscrape.com/catalogue/all-the-light-we-cannot-see_660/index.html</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/adulthood-is-a-myth-a-sarahs-scribbles-collection_659/index.html</t>
+          <t>https://books.toscrape.com/catalogue/adulthood-is-a-myth-a-sarahs-scribbles-collection_659/index.html</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
@@ -9357,7 +9357,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/abstract-city_658/index.html</t>
+          <t>https://books.toscrape.com/catalogue/abstract-city_658/index.html</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
@@ -9383,7 +9383,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/a-time-of-torment-charlie-parker-14_657/index.html</t>
+          <t>https://books.toscrape.com/catalogue/a-time-of-torment-charlie-parker-14_657/index.html</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
@@ -9409,7 +9409,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/a-study-in-scarlet-sherlock-holmes-1_656/index.html</t>
+          <t>https://books.toscrape.com/catalogue/a-study-in-scarlet-sherlock-holmes-1_656/index.html</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/a-series-of-catastrophes-and-miracles-a-true-story-of-love-science-and-cancer_655/index.html</t>
+          <t>https://books.toscrape.com/catalogue/a-series-of-catastrophes-and-miracles-a-true-story-of-love-science-and-cancer_655/index.html</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
@@ -9461,7 +9461,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/a-peoples-history-of-the-united-states_654/index.html</t>
+          <t>https://books.toscrape.com/catalogue/a-peoples-history-of-the-united-states_654/index.html</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/a-man-called-ove_653/index.html</t>
+          <t>https://books.toscrape.com/catalogue/a-man-called-ove_653/index.html</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/a-distant-mirror-the-calamitous-14th-century_652/index.html</t>
+          <t>https://books.toscrape.com/catalogue/a-distant-mirror-the-calamitous-14th-century_652/index.html</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
@@ -9539,7 +9539,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/a-brush-of-wings-angels-walking-3_651/index.html</t>
+          <t>https://books.toscrape.com/catalogue/a-brush-of-wings-angels-walking-3_651/index.html</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/1491-new-revelations-of-the-americas-before-columbus_650/index.html</t>
+          <t>https://books.toscrape.com/catalogue/1491-new-revelations-of-the-americas-before-columbus_650/index.html</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
@@ -9591,7 +9591,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-three-searches-meaning-and-the-story_649/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-three-searches-meaning-and-the-story_649/index.html</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
@@ -9617,7 +9617,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/searching-for-meaning-in-gailana_648/index.html</t>
+          <t>https://books.toscrape.com/catalogue/searching-for-meaning-in-gailana_648/index.html</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
@@ -9643,7 +9643,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/rook_647/index.html</t>
+          <t>https://books.toscrape.com/catalogue/rook_647/index.html</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/my-kitchen-year-136-recipes-that-saved-my-life_646/index.html</t>
+          <t>https://books.toscrape.com/catalogue/my-kitchen-year-136-recipes-that-saved-my-life_646/index.html</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
@@ -9695,7 +9695,7 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/13-hours-the-inside-account-of-what-really-happened-in-benghazi_645/index.html</t>
+          <t>https://books.toscrape.com/catalogue/13-hours-the-inside-account-of-what-really-happened-in-benghazi_645/index.html</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
@@ -9721,7 +9721,7 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/will-you-wont-you-want-me_644/index.html</t>
+          <t>https://books.toscrape.com/catalogue/will-you-wont-you-want-me_644/index.html</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
@@ -9747,7 +9747,7 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/tipping-point-for-planet-earth-how-close-are-we-to-the-edge_643/index.html</t>
+          <t>https://books.toscrape.com/catalogue/tipping-point-for-planet-earth-how-close-are-we-to-the-edge_643/index.html</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-star-touched-queen_642/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-star-touched-queen_642/index.html</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-silent-sister-riley-macpherson-1_641/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-silent-sister-riley-macpherson-1_641/index.html</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-midnight-watch-a-novel-of-the-titanic-and-the-californian_640/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-midnight-watch-a-novel-of-the-titanic-and-the-californian_640/index.html</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
@@ -9851,7 +9851,7 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-lonely-city-adventures-in-the-art-of-being-alone_639/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-lonely-city-adventures-in-the-art-of-being-alone_639/index.html</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-gray-rhino-how-to-recognize-and-act-on-the-obvious-dangers-we-ignore_638/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-gray-rhino-how-to-recognize-and-act-on-the-obvious-dangers-we-ignore_638/index.html</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
@@ -9903,7 +9903,7 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-golden-condom-and-other-essays-on-love-lost-and-found_637/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-golden-condom-and-other-essays-on-love-lost-and-found_637/index.html</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
@@ -9929,7 +9929,7 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-epidemic-the-program-06_636/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-epidemic-the-program-06_636/index.html</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
@@ -9955,7 +9955,7 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-dinner-party_635/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-dinner-party_635/index.html</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
@@ -9981,7 +9981,7 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-diary-of-a-young-girl_634/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-diary-of-a-young-girl_634/index.html</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
@@ -10007,7 +10007,7 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-children_633/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-children_633/index.html</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/stars-above-the-lunar-chronicles-45_632/index.html</t>
+          <t>https://books.toscrape.com/catalogue/stars-above-the-lunar-chronicles-45_632/index.html</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
@@ -10059,7 +10059,7 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/snatched-how-a-drug-queen-went-undercover-for-the-dea-and-was-kidnapped-by-colombian-guerillas_631/index.html</t>
+          <t>https://books.toscrape.com/catalogue/snatched-how-a-drug-queen-went-undercover-for-the-dea-and-was-kidnapped-by-colombian-guerillas_631/index.html</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/raspberry-pi-electronics-projects-for-the-evil-genius_630/index.html</t>
+          <t>https://books.toscrape.com/catalogue/raspberry-pi-electronics-projects-for-the-evil-genius_630/index.html</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/quench-your-own-thirst-business-lessons-learned-over-a-beer-or-two_629/index.html</t>
+          <t>https://books.toscrape.com/catalogue/quench-your-own-thirst-business-lessons-learned-over-a-beer-or-two_629/index.html</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
@@ -10137,7 +10137,7 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/psycho-sanitarium-psycho-15_628/index.html</t>
+          <t>https://books.toscrape.com/catalogue/psycho-sanitarium-psycho-15_628/index.html</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/poisonous-max-revere-novels-3_627/index.html</t>
+          <t>https://books.toscrape.com/catalogue/poisonous-max-revere-novels-3_627/index.html</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
@@ -10189,7 +10189,7 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/one-with-you-crossfire-5_626/index.html</t>
+          <t>https://books.toscrape.com/catalogue/one-with-you-crossfire-5_626/index.html</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
@@ -10215,7 +10215,7 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/no-love-allowed-dodge-cove-1_625/index.html</t>
+          <t>https://books.toscrape.com/catalogue/no-love-allowed-dodge-cove-1_625/index.html</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/murder-at-the-42nd-street-library-raymond-ambler-1_624/index.html</t>
+          <t>https://books.toscrape.com/catalogue/murder-at-the-42nd-street-library-raymond-ambler-1_624/index.html</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
@@ -10267,7 +10267,7 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/most-wanted_623/index.html</t>
+          <t>https://books.toscrape.com/catalogue/most-wanted_623/index.html</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
@@ -10293,7 +10293,7 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/love-lies-and-spies_622/index.html</t>
+          <t>https://books.toscrape.com/catalogue/love-lies-and-spies_622/index.html</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
@@ -10319,7 +10319,7 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/how-to-speak-golf-an-illustrated-guide-to-links-lingo_621/index.html</t>
+          <t>https://books.toscrape.com/catalogue/how-to-speak-golf-an-illustrated-guide-to-links-lingo_621/index.html</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
@@ -10345,7 +10345,7 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/hide-away-eve-duncan-20_620/index.html</t>
+          <t>https://books.toscrape.com/catalogue/hide-away-eve-duncan-20_620/index.html</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
@@ -10371,7 +10371,7 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/furiously-happy-a-funny-book-about-horrible-things_619/index.html</t>
+          <t>https://books.toscrape.com/catalogue/furiously-happy-a-funny-book-about-horrible-things_619/index.html</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/everyday-italian-125-simple-and-delicious-recipes_618/index.html</t>
+          <t>https://books.toscrape.com/catalogue/everyday-italian-125-simple-and-delicious-recipes_618/index.html</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
@@ -10423,7 +10423,7 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/equal-is-unfair-americas-misguided-fight-against-income-inequality_617/index.html</t>
+          <t>https://books.toscrape.com/catalogue/equal-is-unfair-americas-misguided-fight-against-income-inequality_617/index.html</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
@@ -10449,7 +10449,7 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/eleanor-park_616/index.html</t>
+          <t>https://books.toscrape.com/catalogue/eleanor-park_616/index.html</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
@@ -10475,7 +10475,7 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/dirty-dive-bar-1_615/index.html</t>
+          <t>https://books.toscrape.com/catalogue/dirty-dive-bar-1_615/index.html</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
@@ -10501,7 +10501,7 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/can-you-keep-a-secret-fear-street-relaunch-4_614/index.html</t>
+          <t>https://books.toscrape.com/catalogue/can-you-keep-a-secret-fear-street-relaunch-4_614/index.html</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
@@ -10527,7 +10527,7 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/boar-island-anna-pigeon-19_613/index.html</t>
+          <t>https://books.toscrape.com/catalogue/boar-island-anna-pigeon-19_613/index.html</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/a-paris-apartment_612/index.html</t>
+          <t>https://books.toscrape.com/catalogue/a-paris-apartment_612/index.html</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
@@ -10579,7 +10579,7 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/a-la-mode-120-recipes-in-60-pairings-pies-tarts-cakes-crisps-and-more-topped-with-ice-cream-gelato-frozen-custard-and-more_611/index.html</t>
+          <t>https://books.toscrape.com/catalogue/a-la-mode-120-recipes-in-60-pairings-pies-tarts-cakes-crisps-and-more-topped-with-ice-cream-gelato-frozen-custard-and-more_611/index.html</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/troublemaker-surviving-hollywood-and-scientology_610/index.html</t>
+          <t>https://books.toscrape.com/catalogue/troublemaker-surviving-hollywood-and-scientology_610/index.html</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
@@ -10631,7 +10631,7 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-widow_609/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-widow_609/index.html</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
@@ -10657,7 +10657,7 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-sleep-revolution-transforming-your-life-one-night-at-a-time_608/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-sleep-revolution-transforming-your-life-one-night-at-a-time_608/index.html</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
@@ -10683,7 +10683,7 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-improbability-of-love_607/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-improbability-of-love_607/index.html</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
@@ -10709,7 +10709,7 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-art-of-startup-fundraising_606/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-art-of-startup-fundraising_606/index.html</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
@@ -10735,7 +10735,7 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/take-me-home-tonight-rock-star-romance-3_605/index.html</t>
+          <t>https://books.toscrape.com/catalogue/take-me-home-tonight-rock-star-romance-3_605/index.html</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
@@ -10761,7 +10761,7 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/sleeping-giants-themis-files-1_604/index.html</t>
+          <t>https://books.toscrape.com/catalogue/sleeping-giants-themis-files-1_604/index.html</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
@@ -10787,7 +10787,7 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/setting-the-world-on-fire-the-brief-astonishing-life-of-st-catherine-of-siena_603/index.html</t>
+          <t>https://books.toscrape.com/catalogue/setting-the-world-on-fire-the-brief-astonishing-life-of-st-catherine-of-siena_603/index.html</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/playing-with-fire_602/index.html</t>
+          <t>https://books.toscrape.com/catalogue/playing-with-fire_602/index.html</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/off-the-hook-fishing-for-trouble-1_601/index.html</t>
+          <t>https://books.toscrape.com/catalogue/off-the-hook-fishing-for-trouble-1_601/index.html</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/mothering-sunday_600/index.html</t>
+          <t>https://books.toscrape.com/catalogue/mothering-sunday_600/index.html</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
@@ -10891,7 +10891,7 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/mother-can-you-not_599/index.html</t>
+          <t>https://books.toscrape.com/catalogue/mother-can-you-not_599/index.html</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
@@ -10917,7 +10917,7 @@
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/m-train_598/index.html</t>
+          <t>https://books.toscrape.com/catalogue/m-train_598/index.html</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
@@ -10943,7 +10943,7 @@
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/lilac-girls_597/index.html</t>
+          <t>https://books.toscrape.com/catalogue/lilac-girls_597/index.html</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/lies-and-other-acts-of-love_596/index.html</t>
+          <t>https://books.toscrape.com/catalogue/lies-and-other-acts-of-love_596/index.html</t>
         </is>
       </c>
       <c r="F406" t="inlineStr">
@@ -10995,7 +10995,7 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/lab-girl_595/index.html</t>
+          <t>https://books.toscrape.com/catalogue/lab-girl_595/index.html</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
@@ -11021,7 +11021,7 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/keep-me-posted_594/index.html</t>
+          <t>https://books.toscrape.com/catalogue/keep-me-posted_594/index.html</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
@@ -11047,7 +11047,7 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/it-didnt-start-with-you-how-inherited-family-trauma-shapes-who-we-are-and-how-to-end-the-cycle_593/index.html</t>
+          <t>https://books.toscrape.com/catalogue/it-didnt-start-with-you-how-inherited-family-trauma-shapes-who-we-are-and-how-to-end-the-cycle_593/index.html</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
@@ -11073,7 +11073,7 @@
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/grey-fifty-shades-4_592/index.html</t>
+          <t>https://books.toscrape.com/catalogue/grey-fifty-shades-4_592/index.html</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
@@ -11099,7 +11099,7 @@
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/exit-pursued-by-a-bear_591/index.html</t>
+          <t>https://books.toscrape.com/catalogue/exit-pursued-by-a-bear_591/index.html</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
@@ -11125,7 +11125,7 @@
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/daredevils_590/index.html</t>
+          <t>https://books.toscrape.com/catalogue/daredevils_590/index.html</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
@@ -11151,7 +11151,7 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/cravings-recipes-for-what-you-want-to-eat_589/index.html</t>
+          <t>https://books.toscrape.com/catalogue/cravings-recipes-for-what-you-want-to-eat_589/index.html</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/born-for-this-how-to-find-the-work-you-were-meant-to-do_588/index.html</t>
+          <t>https://books.toscrape.com/catalogue/born-for-this-how-to-find-the-work-you-were-meant-to-do_588/index.html</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
@@ -11203,7 +11203,7 @@
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/arena_587/index.html</t>
+          <t>https://books.toscrape.com/catalogue/arena_587/index.html</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
@@ -11229,7 +11229,7 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/adultery_586/index.html</t>
+          <t>https://books.toscrape.com/catalogue/adultery_586/index.html</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/a-mothers-reckoning-living-in-the-aftermath-of-tragedy_585/index.html</t>
+          <t>https://books.toscrape.com/catalogue/a-mothers-reckoning-living-in-the-aftermath-of-tragedy_585/index.html</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
@@ -11281,7 +11281,7 @@
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/a-gentlemans-position-society-of-gentlemen-3_584/index.html</t>
+          <t>https://books.toscrape.com/catalogue/a-gentlemans-position-society-of-gentlemen-3_584/index.html</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
@@ -11307,7 +11307,7 @@
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/112263_583/index.html</t>
+          <t>https://books.toscrape.com/catalogue/112263_583/index.html</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/10-happier-how-i-tamed-the-voice-in-my-head-reduced-stress-without-losing-my-edge-and-found-self-help-that-actually-works_582/index.html</t>
+          <t>https://books.toscrape.com/catalogue/10-happier-how-i-tamed-the-voice-in-my-head-reduced-stress-without-losing-my-edge-and-found-self-help-that-actually-works_582/index.html</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
@@ -11359,7 +11359,7 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/10-day-green-smoothie-cleanse-lose-up-to-15-pounds-in-10-days_581/index.html</t>
+          <t>https://books.toscrape.com/catalogue/10-day-green-smoothie-cleanse-lose-up-to-15-pounds-in-10-days_581/index.html</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
@@ -11385,7 +11385,7 @@
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/without-shame_580/index.html</t>
+          <t>https://books.toscrape.com/catalogue/without-shame_580/index.html</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/watchmen_579/index.html</t>
+          <t>https://books.toscrape.com/catalogue/watchmen_579/index.html</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
@@ -11437,7 +11437,7 @@
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/unlimited-intuition-now_578/index.html</t>
+          <t>https://books.toscrape.com/catalogue/unlimited-intuition-now_578/index.html</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/underlying-notes_577/index.html</t>
+          <t>https://books.toscrape.com/catalogue/underlying-notes_577/index.html</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
@@ -11489,7 +11489,7 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-shack_576/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-shack_576/index.html</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
@@ -11515,7 +11515,7 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-new-brand-you-your-new-image-makes-the-sale-for-you_575/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-new-brand-you-your-new-image-makes-the-sale-for-you_575/index.html</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
@@ -11541,7 +11541,7 @@
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-moosewood-cookbook-recipes-from-moosewood-restaurant-ithaca-new-york_574/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-moosewood-cookbook-recipes-from-moosewood-restaurant-ithaca-new-york_574/index.html</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
@@ -11567,7 +11567,7 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-flowers-lied_573/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-flowers-lied_573/index.html</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
@@ -11593,7 +11593,7 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-fabric-of-the-cosmos-space-time-and-the-texture-of-reality_572/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-fabric-of-the-cosmos-space-time-and-the-texture-of-reality_572/index.html</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
@@ -11619,7 +11619,7 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-book-of-mormon_571/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-book-of-mormon_571/index.html</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
@@ -11645,7 +11645,7 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-art-and-science-of-low-carbohydrate-living_570/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-art-and-science-of-low-carbohydrate-living_570/index.html</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
@@ -11671,7 +11671,7 @@
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-alien-club_569/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-alien-club_569/index.html</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
@@ -11697,7 +11697,7 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/suzie-snowflake-one-beautiful-flake-a-self-esteem-story_568/index.html</t>
+          <t>https://books.toscrape.com/catalogue/suzie-snowflake-one-beautiful-flake-a-self-esteem-story_568/index.html</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
@@ -11723,7 +11723,7 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/nap-a-roo_567/index.html</t>
+          <t>https://books.toscrape.com/catalogue/nap-a-roo_567/index.html</t>
         </is>
       </c>
       <c r="F435" t="inlineStr">
@@ -11749,7 +11749,7 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/nano-what-now-finding-your-editing-process-revising-your-nanowrimo-book-and-building-a-writing-career-through-publishing-and-beyond_566/index.html</t>
+          <t>https://books.toscrape.com/catalogue/nano-what-now-finding-your-editing-process-revising-your-nanowrimo-book-and-building-a-writing-career-through-publishing-and-beyond_566/index.html</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
@@ -11775,7 +11775,7 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/modern-day-fables_565/index.html</t>
+          <t>https://books.toscrape.com/catalogue/modern-day-fables_565/index.html</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
@@ -11801,7 +11801,7 @@
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/if-i-gave-you-gods-phone-number-searching-for-spirituality-in-america_564/index.html</t>
+          <t>https://books.toscrape.com/catalogue/if-i-gave-you-gods-phone-number-searching-for-spirituality-in-america_564/index.html</t>
         </is>
       </c>
       <c r="F438" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/fruits-basket-vol-9-fruits-basket-9_563/index.html</t>
+          <t>https://books.toscrape.com/catalogue/fruits-basket-vol-9-fruits-basket-9_563/index.html</t>
         </is>
       </c>
       <c r="F439" t="inlineStr">
@@ -11853,7 +11853,7 @@
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/dress-your-family-in-corduroy-and-denim_562/index.html</t>
+          <t>https://books.toscrape.com/catalogue/dress-your-family-in-corduroy-and-denim_562/index.html</t>
         </is>
       </c>
       <c r="F440" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/dont-forget-steven_561/index.html</t>
+          <t>https://books.toscrape.com/catalogue/dont-forget-steven_561/index.html</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/chernobyl-012340-the-incredible-true-story-of-the-worlds-worst-nuclear-disaster_560/index.html</t>
+          <t>https://books.toscrape.com/catalogue/chernobyl-012340-the-incredible-true-story-of-the-worlds-worst-nuclear-disaster_560/index.html</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
@@ -11931,7 +11931,7 @@
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/art-and-fear-observations-on-the-perils-and-rewards-of-artmaking_559/index.html</t>
+          <t>https://books.toscrape.com/catalogue/art-and-fear-observations-on-the-perils-and-rewards-of-artmaking_559/index.html</t>
         </is>
       </c>
       <c r="F443" t="inlineStr">
@@ -11957,7 +11957,7 @@
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/a-shard-of-ice-the-black-symphony-saga-1_558/index.html</t>
+          <t>https://books.toscrape.com/catalogue/a-shard-of-ice-the-black-symphony-saga-1_558/index.html</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
@@ -11983,7 +11983,7 @@
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/a-heros-curse-the-unseen-chronicles-1_557/index.html</t>
+          <t>https://books.toscrape.com/catalogue/a-heros-curse-the-unseen-chronicles-1_557/index.html</t>
         </is>
       </c>
       <c r="F445" t="inlineStr">
@@ -12009,7 +12009,7 @@
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/23-degrees-south-a-tropical-tale-of-changing-whether_556/index.html</t>
+          <t>https://books.toscrape.com/catalogue/23-degrees-south-a-tropical-tale-of-changing-whether_556/index.html</t>
         </is>
       </c>
       <c r="F446" t="inlineStr">
@@ -12035,7 +12035,7 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/zero-to-one-notes-on-startups-or-how-to-build-the-future_555/index.html</t>
+          <t>https://books.toscrape.com/catalogue/zero-to-one-notes-on-startups-or-how-to-build-the-future_555/index.html</t>
         </is>
       </c>
       <c r="F447" t="inlineStr">
@@ -12061,7 +12061,7 @@
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/why-not-me_554/index.html</t>
+          <t>https://books.toscrape.com/catalogue/why-not-me_554/index.html</t>
         </is>
       </c>
       <c r="F448" t="inlineStr">
@@ -12087,7 +12087,7 @@
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/when-breath-becomes-air_553/index.html</t>
+          <t>https://books.toscrape.com/catalogue/when-breath-becomes-air_553/index.html</t>
         </is>
       </c>
       <c r="F449" t="inlineStr">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/vagabonding-an-uncommon-guide-to-the-art-of-long-term-world-travel_552/index.html</t>
+          <t>https://books.toscrape.com/catalogue/vagabonding-an-uncommon-guide-to-the-art-of-long-term-world-travel_552/index.html</t>
         </is>
       </c>
       <c r="F450" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-unlikely-pilgrimage-of-harold-fry-harold-fry-1_551/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-unlikely-pilgrimage-of-harold-fry-harold-fry-1_551/index.html</t>
         </is>
       </c>
       <c r="F451" t="inlineStr">
@@ -12165,7 +12165,7 @@
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-new-drawing-on-the-right-side-of-the-brain_550/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-new-drawing-on-the-right-side-of-the-brain_550/index.html</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-midnight-assassin-panic-scandal-and-the-hunt-for-americas-first-serial-killer_549/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-midnight-assassin-panic-scandal-and-the-hunt-for-americas-first-serial-killer_549/index.html</t>
         </is>
       </c>
       <c r="F453" t="inlineStr">
@@ -12217,7 +12217,7 @@
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-martian-the-martian-1_548/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-martian-the-martian-1_548/index.html</t>
         </is>
       </c>
       <c r="F454" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-high-mountains-of-portugal_547/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-high-mountains-of-portugal_547/index.html</t>
         </is>
       </c>
       <c r="F455" t="inlineStr">
@@ -12269,7 +12269,7 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-grownup_546/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-grownup_546/index.html</t>
         </is>
       </c>
       <c r="F456" t="inlineStr">
@@ -12295,7 +12295,7 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-e-myth-revisited-why-most-small-businesses-dont-work-and-what-to-do-about-it_545/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-e-myth-revisited-why-most-small-businesses-dont-work-and-what-to-do-about-it_545/index.html</t>
         </is>
       </c>
       <c r="F457" t="inlineStr">
@@ -12321,7 +12321,7 @@
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/south-of-sunshine_544/index.html</t>
+          <t>https://books.toscrape.com/catalogue/south-of-sunshine_544/index.html</t>
         </is>
       </c>
       <c r="F458" t="inlineStr">
@@ -12347,7 +12347,7 @@
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/smarter-faster-better-the-secrets-of-being-productive-in-life-and-business_543/index.html</t>
+          <t>https://books.toscrape.com/catalogue/smarter-faster-better-the-secrets-of-being-productive-in-life-and-business_543/index.html</t>
         </is>
       </c>
       <c r="F459" t="inlineStr">
@@ -12373,7 +12373,7 @@
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/silence-in-the-dark-logan-point-4_542/index.html</t>
+          <t>https://books.toscrape.com/catalogue/silence-in-the-dark-logan-point-4_542/index.html</t>
         </is>
       </c>
       <c r="F460" t="inlineStr">
@@ -12399,7 +12399,7 @@
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/shadows-of-the-past-logan-point-1_541/index.html</t>
+          <t>https://books.toscrape.com/catalogue/shadows-of-the-past-logan-point-1_541/index.html</t>
         </is>
       </c>
       <c r="F461" t="inlineStr">
@@ -12425,7 +12425,7 @@
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/roller-girl_540/index.html</t>
+          <t>https://books.toscrape.com/catalogue/roller-girl_540/index.html</t>
         </is>
       </c>
       <c r="F462" t="inlineStr">
@@ -12451,7 +12451,7 @@
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/rising-strong_539/index.html</t>
+          <t>https://books.toscrape.com/catalogue/rising-strong_539/index.html</t>
         </is>
       </c>
       <c r="F463" t="inlineStr">
@@ -12477,7 +12477,7 @@
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/proofs-of-god-classical-arguments-from-tertullian-to-barth_538/index.html</t>
+          <t>https://books.toscrape.com/catalogue/proofs-of-god-classical-arguments-from-tertullian-to-barth_538/index.html</t>
         </is>
       </c>
       <c r="F464" t="inlineStr">
@@ -12503,7 +12503,7 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/please-kill-me-the-uncensored-oral-history-of-punk_537/index.html</t>
+          <t>https://books.toscrape.com/catalogue/please-kill-me-the-uncensored-oral-history-of-punk_537/index.html</t>
         </is>
       </c>
       <c r="F465" t="inlineStr">
@@ -12529,7 +12529,7 @@
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/out-of-print-city-lights-spotlight-no-14_536/index.html</t>
+          <t>https://books.toscrape.com/catalogue/out-of-print-city-lights-spotlight-no-14_536/index.html</t>
         </is>
       </c>
       <c r="F466" t="inlineStr">
@@ -12555,7 +12555,7 @@
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/my-life-next-door-my-life-next-door_535/index.html</t>
+          <t>https://books.toscrape.com/catalogue/my-life-next-door-my-life-next-door_535/index.html</t>
         </is>
       </c>
       <c r="F467" t="inlineStr">
@@ -12581,7 +12581,7 @@
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/millers-valley_534/index.html</t>
+          <t>https://books.toscrape.com/catalogue/millers-valley_534/index.html</t>
         </is>
       </c>
       <c r="F468" t="inlineStr">
@@ -12607,7 +12607,7 @@
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/mans-search-for-meaning_533/index.html</t>
+          <t>https://books.toscrape.com/catalogue/mans-search-for-meaning_533/index.html</t>
         </is>
       </c>
       <c r="F469" t="inlineStr">
@@ -12633,7 +12633,7 @@
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/love-that-boy-what-two-presidents-eight-road-trips-and-my-son-taught-me-about-a-parents-expectations_532/index.html</t>
+          <t>https://books.toscrape.com/catalogue/love-that-boy-what-two-presidents-eight-road-trips-and-my-son-taught-me-about-a-parents-expectations_532/index.html</t>
         </is>
       </c>
       <c r="F470" t="inlineStr">
@@ -12659,7 +12659,7 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/living-forward-a-proven-plan-to-stop-drifting-and-get-the-life-you-want_531/index.html</t>
+          <t>https://books.toscrape.com/catalogue/living-forward-a-proven-plan-to-stop-drifting-and-get-the-life-you-want_531/index.html</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
@@ -12685,7 +12685,7 @@
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/les-fleurs-du-mal_530/index.html</t>
+          <t>https://books.toscrape.com/catalogue/les-fleurs-du-mal_530/index.html</t>
         </is>
       </c>
       <c r="F472" t="inlineStr">
@@ -12711,7 +12711,7 @@
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/left-behind-left-behind-1_529/index.html</t>
+          <t>https://books.toscrape.com/catalogue/left-behind-left-behind-1_529/index.html</t>
         </is>
       </c>
       <c r="F473" t="inlineStr">
@@ -12737,7 +12737,7 @@
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/kill-em-and-leave-searching-for-james-brown-and-the-american-soul_528/index.html</t>
+          <t>https://books.toscrape.com/catalogue/kill-em-and-leave-searching-for-james-brown-and-the-american-soul_528/index.html</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
@@ -12763,7 +12763,7 @@
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/kierkegaard-a-christian-missionary-to-christians_527/index.html</t>
+          <t>https://books.toscrape.com/catalogue/kierkegaard-a-christian-missionary-to-christians_527/index.html</t>
         </is>
       </c>
       <c r="F475" t="inlineStr">
@@ -12789,7 +12789,7 @@
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/john-vassos-industrial-design-for-modern-life_526/index.html</t>
+          <t>https://books.toscrape.com/catalogue/john-vassos-industrial-design-for-modern-life_526/index.html</t>
         </is>
       </c>
       <c r="F476" t="inlineStr">
@@ -12815,7 +12815,7 @@
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/ill-give-you-the-sun_525/index.html</t>
+          <t>https://books.toscrape.com/catalogue/ill-give-you-the-sun_525/index.html</t>
         </is>
       </c>
       <c r="F477" t="inlineStr">
@@ -12841,7 +12841,7 @@
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/i-will-find-you_524/index.html</t>
+          <t>https://books.toscrape.com/catalogue/i-will-find-you_524/index.html</t>
         </is>
       </c>
       <c r="F478" t="inlineStr">
@@ -12867,7 +12867,7 @@
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/hystopia-a-novel_523/index.html</t>
+          <t>https://books.toscrape.com/catalogue/hystopia-a-novel_523/index.html</t>
         </is>
       </c>
       <c r="F479" t="inlineStr">
@@ -12893,7 +12893,7 @@
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/howl-and-other-poems_522/index.html</t>
+          <t>https://books.toscrape.com/catalogue/howl-and-other-poems_522/index.html</t>
         </is>
       </c>
       <c r="F480" t="inlineStr">
@@ -12919,7 +12919,7 @@
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/history-of-beauty_521/index.html</t>
+          <t>https://books.toscrape.com/catalogue/history-of-beauty_521/index.html</t>
         </is>
       </c>
       <c r="F481" t="inlineStr">
@@ -12945,7 +12945,7 @@
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/heaven-is-for-real-a-little-boys-astounding-story-of-his-trip-to-heaven-and-back_520/index.html</t>
+          <t>https://books.toscrape.com/catalogue/heaven-is-for-real-a-little-boys-astounding-story-of-his-trip-to-heaven-and-back_520/index.html</t>
         </is>
       </c>
       <c r="F482" t="inlineStr">
@@ -12971,7 +12971,7 @@
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/future-shock-future-shock-1_519/index.html</t>
+          <t>https://books.toscrape.com/catalogue/future-shock-future-shock-1_519/index.html</t>
         </is>
       </c>
       <c r="F483" t="inlineStr">
@@ -12997,7 +12997,7 @@
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/enders-game-the-ender-quintet-1_518/index.html</t>
+          <t>https://books.toscrape.com/catalogue/enders-game-the-ender-quintet-1_518/index.html</t>
         </is>
       </c>
       <c r="F484" t="inlineStr">
@@ -13023,7 +13023,7 @@
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/diary-of-a-citizen-scientist-chasing-tiger-beetles-and-other-new-ways-of-engaging-the-world_517/index.html</t>
+          <t>https://books.toscrape.com/catalogue/diary-of-a-citizen-scientist-chasing-tiger-beetles-and-other-new-ways-of-engaging-the-world_517/index.html</t>
         </is>
       </c>
       <c r="F485" t="inlineStr">
@@ -13049,7 +13049,7 @@
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/death-by-leisure-a-cautionary-tale_516/index.html</t>
+          <t>https://books.toscrape.com/catalogue/death-by-leisure-a-cautionary-tale_516/index.html</t>
         </is>
       </c>
       <c r="F486" t="inlineStr">
@@ -13075,7 +13075,7 @@
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/brilliant-beacons-a-history-of-the-american-lighthouse_515/index.html</t>
+          <t>https://books.toscrape.com/catalogue/brilliant-beacons-a-history-of-the-american-lighthouse_515/index.html</t>
         </is>
       </c>
       <c r="F487" t="inlineStr">
@@ -13101,7 +13101,7 @@
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/brazen-the-courage-to-find-the-you-thats-been-hiding_514/index.html</t>
+          <t>https://books.toscrape.com/catalogue/brazen-the-courage-to-find-the-you-thats-been-hiding_514/index.html</t>
         </is>
       </c>
       <c r="F488" t="inlineStr">
@@ -13127,7 +13127,7 @@
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/between-the-world-and-me_513/index.html</t>
+          <t>https://books.toscrape.com/catalogue/between-the-world-and-me_513/index.html</t>
         </is>
       </c>
       <c r="F489" t="inlineStr">
@@ -13153,7 +13153,7 @@
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/being-mortal-medicine-and-what-matters-in-the-end_512/index.html</t>
+          <t>https://books.toscrape.com/catalogue/being-mortal-medicine-and-what-matters-in-the-end_512/index.html</t>
         </is>
       </c>
       <c r="F490" t="inlineStr">
@@ -13179,7 +13179,7 @@
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/a-murder-over-a-girl-justice-gender-junior-high_511/index.html</t>
+          <t>https://books.toscrape.com/catalogue/a-murder-over-a-girl-justice-gender-junior-high_511/index.html</t>
         </is>
       </c>
       <c r="F491" t="inlineStr">
@@ -13205,7 +13205,7 @@
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/32-yolks_510/index.html</t>
+          <t>https://books.toscrape.com/catalogue/32-yolks_510/index.html</t>
         </is>
       </c>
       <c r="F492" t="inlineStr">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/most-blessed-of-the-patriarchs-thomas-jefferson-and-the-empire-of-the-imagination_509/index.html</t>
+          <t>https://books.toscrape.com/catalogue/most-blessed-of-the-patriarchs-thomas-jefferson-and-the-empire-of-the-imagination_509/index.html</t>
         </is>
       </c>
       <c r="F493" t="inlineStr">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/you-are-a-badass-how-to-stop-doubting-your-greatness-and-start-living-an-awesome-life_508/index.html</t>
+          <t>https://books.toscrape.com/catalogue/you-are-a-badass-how-to-stop-doubting-your-greatness-and-start-living-an-awesome-life_508/index.html</t>
         </is>
       </c>
       <c r="F494" t="inlineStr">
@@ -13283,7 +13283,7 @@
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/wildlife-of-new-york-a-five-borough-coloring-book_507/index.html</t>
+          <t>https://books.toscrape.com/catalogue/wildlife-of-new-york-a-five-borough-coloring-book_507/index.html</t>
         </is>
       </c>
       <c r="F495" t="inlineStr">
@@ -13309,7 +13309,7 @@
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/what-happened-on-beale-street-secrets-of-the-south-mysteries-2_506/index.html</t>
+          <t>https://books.toscrape.com/catalogue/what-happened-on-beale-street-secrets-of-the-south-mysteries-2_506/index.html</t>
         </is>
       </c>
       <c r="F496" t="inlineStr">
@@ -13335,7 +13335,7 @@
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/unreasonable-hope-finding-faith-in-the-god-who-brings-purpose-to-your-pain_505/index.html</t>
+          <t>https://books.toscrape.com/catalogue/unreasonable-hope-finding-faith-in-the-god-who-brings-purpose-to-your-pain_505/index.html</t>
         </is>
       </c>
       <c r="F497" t="inlineStr">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/under-the-tuscan-sun_504/index.html</t>
+          <t>https://books.toscrape.com/catalogue/under-the-tuscan-sun_504/index.html</t>
         </is>
       </c>
       <c r="F498" t="inlineStr">
@@ -13387,7 +13387,7 @@
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/toddlers-are-aholes-its-not-your-fault_503/index.html</t>
+          <t>https://books.toscrape.com/catalogue/toddlers-are-aholes-its-not-your-fault_503/index.html</t>
         </is>
       </c>
       <c r="F499" t="inlineStr">
@@ -13413,7 +13413,7 @@
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-year-of-living-biblically-one-mans-humble-quest-to-follow-the-bible-as-literally-as-possible_502/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-year-of-living-biblically-one-mans-humble-quest-to-follow-the-bible-as-literally-as-possible_502/index.html</t>
         </is>
       </c>
       <c r="F500" t="inlineStr">
@@ -13439,7 +13439,7 @@
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-whale_501/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-whale_501/index.html</t>
         </is>
       </c>
       <c r="F501" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-story-of-art_500/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-story-of-art_500/index.html</t>
         </is>
       </c>
       <c r="F502" t="inlineStr">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-origin-of-species_499/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-origin-of-species_499/index.html</t>
         </is>
       </c>
       <c r="F503" t="inlineStr">
@@ -13517,7 +13517,7 @@
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-great-gatsby_498/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-great-gatsby_498/index.html</t>
         </is>
       </c>
       <c r="F504" t="inlineStr">
@@ -13543,7 +13543,7 @@
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-good-girl_497/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-good-girl_497/index.html</t>
         </is>
       </c>
       <c r="F505" t="inlineStr">
@@ -13569,7 +13569,7 @@
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-glass-castle_496/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-glass-castle_496/index.html</t>
         </is>
       </c>
       <c r="F506" t="inlineStr">
@@ -13595,7 +13595,7 @@
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-faith-of-christopher-hitchens-the-restless-soul-of-the-worlds-most-notorious-atheist_495/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-faith-of-christopher-hitchens-the-restless-soul-of-the-worlds-most-notorious-atheist_495/index.html</t>
         </is>
       </c>
       <c r="F507" t="inlineStr">
@@ -13621,7 +13621,7 @@
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-drowning-girls_494/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-drowning-girls_494/index.html</t>
         </is>
       </c>
       <c r="F508" t="inlineStr">
@@ -13647,7 +13647,7 @@
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-constant-princess-the-tudor-court-1_493/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-constant-princess-the-tudor-court-1_493/index.html</t>
         </is>
       </c>
       <c r="F509" t="inlineStr">
@@ -13673,7 +13673,7 @@
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-bourne-identity-jason-bourne-1_492/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-bourne-identity-jason-bourne-1_492/index.html</t>
         </is>
       </c>
       <c r="F510" t="inlineStr">
@@ -13699,7 +13699,7 @@
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-bachelor-girls-guide-to-murder-herringford-and-watts-mysteries-1_491/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-bachelor-girls-guide-to-murder-herringford-and-watts-mysteries-1_491/index.html</t>
         </is>
       </c>
       <c r="F511" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-art-book_490/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-art-book_490/index.html</t>
         </is>
       </c>
       <c r="F512" t="inlineStr">
@@ -13751,7 +13751,7 @@
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-7-habits-of-highly-effective-people-powerful-lessons-in-personal-change_489/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-7-habits-of-highly-effective-people-powerful-lessons-in-personal-change_489/index.html</t>
         </is>
       </c>
       <c r="F513" t="inlineStr">
@@ -13777,7 +13777,7 @@
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/team-of-rivals-the-political-genius-of-abraham-lincoln_488/index.html</t>
+          <t>https://books.toscrape.com/catalogue/team-of-rivals-the-political-genius-of-abraham-lincoln_488/index.html</t>
         </is>
       </c>
       <c r="F514" t="inlineStr">
@@ -13803,7 +13803,7 @@
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/steal-like-an-artist-10-things-nobody-told-you-about-being-creative_487/index.html</t>
+          <t>https://books.toscrape.com/catalogue/steal-like-an-artist-10-things-nobody-told-you-about-being-creative_487/index.html</t>
         </is>
       </c>
       <c r="F515" t="inlineStr">
@@ -13829,7 +13829,7 @@
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/sit-stay-love_486/index.html</t>
+          <t>https://books.toscrape.com/catalogue/sit-stay-love_486/index.html</t>
         </is>
       </c>
       <c r="F516" t="inlineStr">
@@ -13855,7 +13855,7 @@
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/sister-dear_485/index.html</t>
+          <t>https://books.toscrape.com/catalogue/sister-dear_485/index.html</t>
         </is>
       </c>
       <c r="F517" t="inlineStr">
@@ -13881,7 +13881,7 @@
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/shrunken-treasures-literary-classics-short-sweet-and-silly_484/index.html</t>
+          <t>https://books.toscrape.com/catalogue/shrunken-treasures-literary-classics-short-sweet-and-silly_484/index.html</t>
         </is>
       </c>
       <c r="F518" t="inlineStr">
@@ -13907,7 +13907,7 @@
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/rich-dad-poor-dad_483/index.html</t>
+          <t>https://books.toscrape.com/catalogue/rich-dad-poor-dad_483/index.html</t>
         </is>
       </c>
       <c r="F519" t="inlineStr">
@@ -13933,7 +13933,7 @@
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/raymie-nightingale_482/index.html</t>
+          <t>https://books.toscrape.com/catalogue/raymie-nightingale_482/index.html</t>
         </is>
       </c>
       <c r="F520" t="inlineStr">
@@ -13959,7 +13959,7 @@
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/playing-from-the-heart_481/index.html</t>
+          <t>https://books.toscrape.com/catalogue/playing-from-the-heart_481/index.html</t>
         </is>
       </c>
       <c r="F521" t="inlineStr">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/nightstruck-a-novel_480/index.html</t>
+          <t>https://books.toscrape.com/catalogue/nightstruck-a-novel_480/index.html</t>
         </is>
       </c>
       <c r="F522" t="inlineStr">
@@ -14011,7 +14011,7 @@
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/naturally-lean-125-nourishing-gluten-free-plant-based-recipes-all-under-300-calories_479/index.html</t>
+          <t>https://books.toscrape.com/catalogue/naturally-lean-125-nourishing-gluten-free-plant-based-recipes-all-under-300-calories_479/index.html</t>
         </is>
       </c>
       <c r="F523" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/meternity_478/index.html</t>
+          <t>https://books.toscrape.com/catalogue/meternity_478/index.html</t>
         </is>
       </c>
       <c r="F524" t="inlineStr">
@@ -14063,7 +14063,7 @@
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/memoirs-of-a-geisha_477/index.html</t>
+          <t>https://books.toscrape.com/catalogue/memoirs-of-a-geisha_477/index.html</t>
         </is>
       </c>
       <c r="F525" t="inlineStr">
@@ -14089,7 +14089,7 @@
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/like-never-before-walker-family-2_476/index.html</t>
+          <t>https://books.toscrape.com/catalogue/like-never-before-walker-family-2_476/index.html</t>
         </is>
       </c>
       <c r="F526" t="inlineStr">
@@ -14115,7 +14115,7 @@
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/life-of-pi_475/index.html</t>
+          <t>https://books.toscrape.com/catalogue/life-of-pi_475/index.html</t>
         </is>
       </c>
       <c r="F527" t="inlineStr">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/leave-this-song-behind-teen-poetry-at-its-best_474/index.html</t>
+          <t>https://books.toscrape.com/catalogue/leave-this-song-behind-teen-poetry-at-its-best_474/index.html</t>
         </is>
       </c>
       <c r="F528" t="inlineStr">
@@ -14167,7 +14167,7 @@
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/kings-folly-the-kinsman-chronicles-1_473/index.html</t>
+          <t>https://books.toscrape.com/catalogue/kings-folly-the-kinsman-chronicles-1_473/index.html</t>
         </is>
       </c>
       <c r="F529" t="inlineStr">
@@ -14193,7 +14193,7 @@
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/john-adams_472/index.html</t>
+          <t>https://books.toscrape.com/catalogue/john-adams_472/index.html</t>
         </is>
       </c>
       <c r="F530" t="inlineStr">
@@ -14219,7 +14219,7 @@
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/how-to-cook-everything-vegetarian-simple-meatless-recipes-for-great-food-how-to-cook-everything_471/index.html</t>
+          <t>https://books.toscrape.com/catalogue/how-to-cook-everything-vegetarian-simple-meatless-recipes-for-great-food-how-to-cook-everything_471/index.html</t>
         </is>
       </c>
       <c r="F531" t="inlineStr">
@@ -14245,7 +14245,7 @@
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/how-to-be-a-domestic-goddess-baking-and-the-art-of-comfort-cooking_470/index.html</t>
+          <t>https://books.toscrape.com/catalogue/how-to-be-a-domestic-goddess-baking-and-the-art-of-comfort-cooking_470/index.html</t>
         </is>
       </c>
       <c r="F532" t="inlineStr">
@@ -14271,7 +14271,7 @@
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/good-in-bed-cannie-shapiro-1_469/index.html</t>
+          <t>https://books.toscrape.com/catalogue/good-in-bed-cannie-shapiro-1_469/index.html</t>
         </is>
       </c>
       <c r="F533" t="inlineStr">
@@ -14297,7 +14297,7 @@
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/fruits-basket-vol-7-fruits-basket-7_468/index.html</t>
+          <t>https://books.toscrape.com/catalogue/fruits-basket-vol-7-fruits-basket-7_468/index.html</t>
         </is>
       </c>
       <c r="F534" t="inlineStr">
@@ -14323,7 +14323,7 @@
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/for-the-love-fighting-for-grace-in-a-world-of-impossible-standards_467/index.html</t>
+          <t>https://books.toscrape.com/catalogue/for-the-love-fighting-for-grace-in-a-world-of-impossible-standards_467/index.html</t>
         </is>
       </c>
       <c r="F535" t="inlineStr">
@@ -14349,7 +14349,7 @@
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/finding-god-in-the-ruins-how-god-redeems-pain_466/index.html</t>
+          <t>https://books.toscrape.com/catalogue/finding-god-in-the-ruins-how-god-redeems-pain_466/index.html</t>
         </is>
       </c>
       <c r="F536" t="inlineStr">
@@ -14375,7 +14375,7 @@
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/every-heart-a-doorway-every-heart-a-doorway-1_465/index.html</t>
+          <t>https://books.toscrape.com/catalogue/every-heart-a-doorway-every-heart-a-doorway-1_465/index.html</t>
         </is>
       </c>
       <c r="F537" t="inlineStr">
@@ -14401,7 +14401,7 @@
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/delivering-the-truth-quaker-midwife-mystery-1_464/index.html</t>
+          <t>https://books.toscrape.com/catalogue/delivering-the-truth-quaker-midwife-mystery-1_464/index.html</t>
         </is>
       </c>
       <c r="F538" t="inlineStr">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/counted-with-the-stars-out-from-egypt-1_463/index.html</t>
+          <t>https://books.toscrape.com/catalogue/counted-with-the-stars-out-from-egypt-1_463/index.html</t>
         </is>
       </c>
       <c r="F539" t="inlineStr">
@@ -14453,7 +14453,7 @@
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/chronicles-vol-1_462/index.html</t>
+          <t>https://books.toscrape.com/catalogue/chronicles-vol-1_462/index.html</t>
         </is>
       </c>
       <c r="F540" t="inlineStr">
@@ -14479,7 +14479,7 @@
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/blue-like-jazz-nonreligious-thoughts-on-christian-spirituality_461/index.html</t>
+          <t>https://books.toscrape.com/catalogue/blue-like-jazz-nonreligious-thoughts-on-christian-spirituality_461/index.html</t>
         </is>
       </c>
       <c r="F541" t="inlineStr">
@@ -14505,7 +14505,7 @@
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/benjamin-franklin-an-american-life_460/index.html</t>
+          <t>https://books.toscrape.com/catalogue/benjamin-franklin-an-american-life_460/index.html</t>
         </is>
       </c>
       <c r="F542" t="inlineStr">
@@ -14531,7 +14531,7 @@
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/at-the-existentialist-cafe-freedom-being-and-apricot-cocktails-with-jean-paul-sartre-simone-de-beauvoir-albert-camus-martin-heidegger-edmund-husserl-karl-jaspers-maurice-merleau-ponty-and-others_459/index.html</t>
+          <t>https://books.toscrape.com/catalogue/at-the-existentialist-cafe-freedom-being-and-apricot-cocktails-with-jean-paul-sartre-simone-de-beauvoir-albert-camus-martin-heidegger-edmund-husserl-karl-jaspers-maurice-merleau-ponty-and-others_459/index.html</t>
         </is>
       </c>
       <c r="F543" t="inlineStr">
@@ -14557,7 +14557,7 @@
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/a-summer-in-europe_458/index.html</t>
+          <t>https://books.toscrape.com/catalogue/a-summer-in-europe_458/index.html</t>
         </is>
       </c>
       <c r="F544" t="inlineStr">
@@ -14583,7 +14583,7 @@
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/a-short-history-of-nearly-everything_457/index.html</t>
+          <t>https://books.toscrape.com/catalogue/a-short-history-of-nearly-everything_457/index.html</t>
         </is>
       </c>
       <c r="F545" t="inlineStr">
@@ -14609,7 +14609,7 @@
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/a-gathering-of-shadows-shades-of-magic-2_456/index.html</t>
+          <t>https://books.toscrape.com/catalogue/a-gathering-of-shadows-shades-of-magic-2_456/index.html</t>
         </is>
       </c>
       <c r="F546" t="inlineStr">
@@ -14635,7 +14635,7 @@
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-sound-of-love_455/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-sound-of-love_455/index.html</t>
         </is>
       </c>
       <c r="F547" t="inlineStr">
@@ -14661,7 +14661,7 @@
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-rise-and-fall-of-the-third-reich-a-history-of-nazi-germany_454/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-rise-and-fall-of-the-third-reich-a-history-of-nazi-germany_454/index.html</t>
         </is>
       </c>
       <c r="F548" t="inlineStr">
@@ -14687,7 +14687,7 @@
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-perks-of-being-a-wallflower_453/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-perks-of-being-a-wallflower_453/index.html</t>
         </is>
       </c>
       <c r="F549" t="inlineStr">
@@ -14713,7 +14713,7 @@
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-mysterious-affair-at-styles-hercule-poirot-1_452/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-mysterious-affair-at-styles-hercule-poirot-1_452/index.html</t>
         </is>
       </c>
       <c r="F550" t="inlineStr">
@@ -14739,7 +14739,7 @@
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-man-who-mistook-his-wife-for-a-hat-and-other-clinical-tales_451/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-man-who-mistook-his-wife-for-a-hat-and-other-clinical-tales_451/index.html</t>
         </is>
       </c>
       <c r="F551" t="inlineStr">
@@ -14765,7 +14765,7 @@
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-makings-of-a-fatherless-child_450/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-makings-of-a-fatherless-child_450/index.html</t>
         </is>
       </c>
       <c r="F552" t="inlineStr">
@@ -14791,7 +14791,7 @@
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-joy-of-cooking_449/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-joy-of-cooking_449/index.html</t>
         </is>
       </c>
       <c r="F553" t="inlineStr">
@@ -14817,7 +14817,7 @@
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-invention-of-wings_448/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-invention-of-wings_448/index.html</t>
         </is>
       </c>
       <c r="F554" t="inlineStr">
@@ -14843,7 +14843,7 @@
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-hobbit-middle-earth-universe_447/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-hobbit-middle-earth-universe_447/index.html</t>
         </is>
       </c>
       <c r="F555" t="inlineStr">
@@ -14869,7 +14869,7 @@
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-great-railway-bazaar_446/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-great-railway-bazaar_446/index.html</t>
         </is>
       </c>
       <c r="F556" t="inlineStr">
@@ -14895,7 +14895,7 @@
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-golden-compass-his-dark-materials-1_445/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-golden-compass-his-dark-materials-1_445/index.html</t>
         </is>
       </c>
       <c r="F557" t="inlineStr">
@@ -14921,7 +14921,7 @@
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-god-delusion_444/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-god-delusion_444/index.html</t>
         </is>
       </c>
       <c r="F558" t="inlineStr">
@@ -14947,7 +14947,7 @@
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-girl-you-left-behind-the-girl-you-left-behind-1_443/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-girl-you-left-behind-the-girl-you-left-behind-1_443/index.html</t>
         </is>
       </c>
       <c r="F559" t="inlineStr">
@@ -14973,7 +14973,7 @@
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-fellowship-of-the-ring-the-lord-of-the-rings-1_442/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-fellowship-of-the-ring-the-lord-of-the-rings-1_442/index.html</t>
         </is>
       </c>
       <c r="F560" t="inlineStr">
@@ -14999,7 +14999,7 @@
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-collected-poems-of-wb-yeats-the-collected-works-of-wb-yeats-1_441/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-collected-poems-of-wb-yeats-the-collected-works-of-wb-yeats-1_441/index.html</t>
         </is>
       </c>
       <c r="F561" t="inlineStr">
@@ -15025,7 +15025,7 @@
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-barefoot-contessa-cookbook_440/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-barefoot-contessa-cookbook_440/index.html</t>
         </is>
       </c>
       <c r="F562" t="inlineStr">
@@ -15051,7 +15051,7 @@
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/tell-the-wolves-im-home_439/index.html</t>
+          <t>https://books.toscrape.com/catalogue/tell-the-wolves-im-home_439/index.html</t>
         </is>
       </c>
       <c r="F563" t="inlineStr">
@@ -15077,7 +15077,7 @@
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/ship-leaves-harbor-essays-on-travel-by-a-recovering-journeyman_438/index.html</t>
+          <t>https://books.toscrape.com/catalogue/ship-leaves-harbor-essays-on-travel-by-a-recovering-journeyman_438/index.html</t>
         </is>
       </c>
       <c r="F564" t="inlineStr">
@@ -15103,7 +15103,7 @@
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/pride-and-prejudice_437/index.html</t>
+          <t>https://books.toscrape.com/catalogue/pride-and-prejudice_437/index.html</t>
         </is>
       </c>
       <c r="F565" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/musicophilia-tales-of-music-and-the-brain_436/index.html</t>
+          <t>https://books.toscrape.com/catalogue/musicophilia-tales-of-music-and-the-brain_436/index.html</t>
         </is>
       </c>
       <c r="F566" t="inlineStr">
@@ -15155,7 +15155,7 @@
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/mere-christianity_435/index.html</t>
+          <t>https://books.toscrape.com/catalogue/mere-christianity_435/index.html</t>
         </is>
       </c>
       <c r="F567" t="inlineStr">
@@ -15181,7 +15181,7 @@
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/me-before-you-me-before-you-1_434/index.html</t>
+          <t>https://books.toscrape.com/catalogue/me-before-you-me-before-you-1_434/index.html</t>
         </is>
       </c>
       <c r="F568" t="inlineStr">
@@ -15207,7 +15207,7 @@
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/in-the-woods-dublin-murder-squad-1_433/index.html</t>
+          <t>https://books.toscrape.com/catalogue/in-the-woods-dublin-murder-squad-1_433/index.html</t>
         </is>
       </c>
       <c r="F569" t="inlineStr">
@@ -15233,7 +15233,7 @@
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/in-cold-blood_432/index.html</t>
+          <t>https://books.toscrape.com/catalogue/in-cold-blood_432/index.html</t>
         </is>
       </c>
       <c r="F570" t="inlineStr">
@@ -15259,7 +15259,7 @@
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/how-to-stop-worrying-and-start-living_431/index.html</t>
+          <t>https://books.toscrape.com/catalogue/how-to-stop-worrying-and-start-living_431/index.html</t>
         </is>
       </c>
       <c r="F571" t="inlineStr">
@@ -15285,7 +15285,7 @@
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/give-it-back_430/index.html</t>
+          <t>https://books.toscrape.com/catalogue/give-it-back_430/index.html</t>
         </is>
       </c>
       <c r="F572" t="inlineStr">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/girl-interrupted_429/index.html</t>
+          <t>https://books.toscrape.com/catalogue/girl-interrupted_429/index.html</t>
         </is>
       </c>
       <c r="F573" t="inlineStr">
@@ -15337,7 +15337,7 @@
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/fun-home-a-family-tragicomic_428/index.html</t>
+          <t>https://books.toscrape.com/catalogue/fun-home-a-family-tragicomic_428/index.html</t>
         </is>
       </c>
       <c r="F574" t="inlineStr">
@@ -15363,7 +15363,7 @@
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/fruits-basket-vol-6-fruits-basket-6_427/index.html</t>
+          <t>https://books.toscrape.com/catalogue/fruits-basket-vol-6-fruits-basket-6_427/index.html</t>
         </is>
       </c>
       <c r="F575" t="inlineStr">
@@ -15389,7 +15389,7 @@
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/deception-point_426/index.html</t>
+          <t>https://books.toscrape.com/catalogue/deception-point_426/index.html</t>
         </is>
       </c>
       <c r="F576" t="inlineStr">
@@ -15415,7 +15415,7 @@
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/death-note-vol-6-give-and-take-death-note-6_425/index.html</t>
+          <t>https://books.toscrape.com/catalogue/death-note-vol-6-give-and-take-death-note-6_425/index.html</t>
         </is>
       </c>
       <c r="F577" t="inlineStr">
@@ -15441,7 +15441,7 @@
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/catherine-the-great-portrait-of-a-woman_424/index.html</t>
+          <t>https://books.toscrape.com/catalogue/catherine-the-great-portrait-of-a-woman_424/index.html</t>
         </is>
       </c>
       <c r="F578" t="inlineStr">
@@ -15467,7 +15467,7 @@
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/better-homes-and-gardens-new-cook-book_423/index.html</t>
+          <t>https://books.toscrape.com/catalogue/better-homes-and-gardens-new-cook-book_423/index.html</t>
         </is>
       </c>
       <c r="F579" t="inlineStr">
@@ -15493,7 +15493,7 @@
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/an-unquiet-mind-a-memoir-of-moods-and-madness_422/index.html</t>
+          <t>https://books.toscrape.com/catalogue/an-unquiet-mind-a-memoir-of-moods-and-madness_422/index.html</t>
         </is>
       </c>
       <c r="F580" t="inlineStr">
@@ -15519,7 +15519,7 @@
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/a-year-in-provence-provence-1_421/index.html</t>
+          <t>https://books.toscrape.com/catalogue/a-year-in-provence-provence-1_421/index.html</t>
         </is>
       </c>
       <c r="F581" t="inlineStr">
@@ -15545,7 +15545,7 @@
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/world-without-end-the-pillars-of-the-earth-2_420/index.html</t>
+          <t>https://books.toscrape.com/catalogue/world-without-end-the-pillars-of-the-earth-2_420/index.html</t>
         </is>
       </c>
       <c r="F582" t="inlineStr">
@@ -15571,7 +15571,7 @@
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/will-grayson-will-grayson-will-grayson-will-grayson_419/index.html</t>
+          <t>https://books.toscrape.com/catalogue/will-grayson-will-grayson-will-grayson-will-grayson_419/index.html</t>
         </is>
       </c>
       <c r="F583" t="inlineStr">
@@ -15597,7 +15597,7 @@
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/why-save-the-bankers-and-other-essays-on-our-economic-and-political-crisis_418/index.html</t>
+          <t>https://books.toscrape.com/catalogue/why-save-the-bankers-and-other-essays-on-our-economic-and-political-crisis_418/index.html</t>
         </is>
       </c>
       <c r="F584" t="inlineStr">
@@ -15623,7 +15623,7 @@
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/where-she-went-if-i-stay-2_417/index.html</t>
+          <t>https://books.toscrape.com/catalogue/where-she-went-if-i-stay-2_417/index.html</t>
         </is>
       </c>
       <c r="F585" t="inlineStr">
@@ -15649,7 +15649,7 @@
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/what-if-serious-scientific-answers-to-absurd-hypothetical-questions_416/index.html</t>
+          <t>https://books.toscrape.com/catalogue/what-if-serious-scientific-answers-to-absurd-hypothetical-questions_416/index.html</t>
         </is>
       </c>
       <c r="F586" t="inlineStr">
@@ -15675,7 +15675,7 @@
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/two-summers_415/index.html</t>
+          <t>https://books.toscrape.com/catalogue/two-summers_415/index.html</t>
         </is>
       </c>
       <c r="F587" t="inlineStr">
@@ -15701,7 +15701,7 @@
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/this-is-your-brain-on-music-the-science-of-a-human-obsession_414/index.html</t>
+          <t>https://books.toscrape.com/catalogue/this-is-your-brain-on-music-the-science-of-a-human-obsession_414/index.html</t>
         </is>
       </c>
       <c r="F588" t="inlineStr">
@@ -15727,7 +15727,7 @@
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-secret-garden_413/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-secret-garden_413/index.html</t>
         </is>
       </c>
       <c r="F589" t="inlineStr">
@@ -15753,7 +15753,7 @@
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-raven-king-the-raven-cycle-4_412/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-raven-king-the-raven-cycle-4_412/index.html</t>
         </is>
       </c>
       <c r="F590" t="inlineStr">
@@ -15779,7 +15779,7 @@
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-raven-boys-the-raven-cycle-1_411/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-raven-boys-the-raven-cycle-1_411/index.html</t>
         </is>
       </c>
       <c r="F591" t="inlineStr">
@@ -15805,7 +15805,7 @@
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-power-greens-cookbook-140-delicious-superfood-recipes_410/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-power-greens-cookbook-140-delicious-superfood-recipes_410/index.html</t>
         </is>
       </c>
       <c r="F592" t="inlineStr">
@@ -15831,7 +15831,7 @@
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-metamorphosis_409/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-metamorphosis_409/index.html</t>
         </is>
       </c>
       <c r="F593" t="inlineStr">
@@ -15857,7 +15857,7 @@
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-mathews-men-seven-brothers-and-the-war-against-hitlers-u-boats_408/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-mathews-men-seven-brothers-and-the-war-against-hitlers-u-boats_408/index.html</t>
         </is>
       </c>
       <c r="F594" t="inlineStr">
@@ -15883,7 +15883,7 @@
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-little-paris-bookshop_407/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-little-paris-bookshop_407/index.html</t>
         </is>
       </c>
       <c r="F595" t="inlineStr">
@@ -15909,7 +15909,7 @@
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-hiding-place_406/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-hiding-place_406/index.html</t>
         </is>
       </c>
       <c r="F596" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-grand-design_405/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-grand-design_405/index.html</t>
         </is>
       </c>
       <c r="F597" t="inlineStr">
@@ -15961,7 +15961,7 @@
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-firm_404/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-firm_404/index.html</t>
         </is>
       </c>
       <c r="F598" t="inlineStr">
@@ -15987,7 +15987,7 @@
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-fault-in-our-stars_403/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-fault-in-our-stars_403/index.html</t>
         </is>
       </c>
       <c r="F599" t="inlineStr">
@@ -16013,7 +16013,7 @@
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-false-prince-the-ascendance-trilogy-1_402/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-false-prince-the-ascendance-trilogy-1_402/index.html</t>
         </is>
       </c>
       <c r="F600" t="inlineStr">
@@ -16039,7 +16039,7 @@
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-expatriates_401/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-expatriates_401/index.html</t>
         </is>
       </c>
       <c r="F601" t="inlineStr">
@@ -16065,7 +16065,7 @@
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-dream-thieves-the-raven-cycle-2_400/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-dream-thieves-the-raven-cycle-2_400/index.html</t>
         </is>
       </c>
       <c r="F602" t="inlineStr">
@@ -16091,7 +16091,7 @@
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-darkest-corners_399/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-darkest-corners_399/index.html</t>
         </is>
       </c>
       <c r="F603" t="inlineStr">
@@ -16117,7 +16117,7 @@
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-crossover_398/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-crossover_398/index.html</t>
         </is>
       </c>
       <c r="F604" t="inlineStr">
@@ -16143,7 +16143,7 @@
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-5th-wave-the-5th-wave-1_397/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-5th-wave-the-5th-wave-1_397/index.html</t>
         </is>
       </c>
       <c r="F605" t="inlineStr">
@@ -16169,7 +16169,7 @@
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/tell-the-wind-and-fire_396/index.html</t>
+          <t>https://books.toscrape.com/catalogue/tell-the-wind-and-fire_396/index.html</t>
         </is>
       </c>
       <c r="F606" t="inlineStr">
@@ -16195,7 +16195,7 @@
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/tell-me-three-things_395/index.html</t>
+          <t>https://books.toscrape.com/catalogue/tell-me-three-things_395/index.html</t>
         </is>
       </c>
       <c r="F607" t="inlineStr">
@@ -16221,7 +16221,7 @@
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/talking-to-girls-about-duran-duran-one-young-mans-quest-for-true-love-and-a-cooler-haircut_394/index.html</t>
+          <t>https://books.toscrape.com/catalogue/talking-to-girls-about-duran-duran-one-young-mans-quest-for-true-love-and-a-cooler-haircut_394/index.html</t>
         </is>
       </c>
       <c r="F608" t="inlineStr">
@@ -16247,7 +16247,7 @@
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/siddhartha_393/index.html</t>
+          <t>https://books.toscrape.com/catalogue/siddhartha_393/index.html</t>
         </is>
       </c>
       <c r="F609" t="inlineStr">
@@ -16273,7 +16273,7 @@
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/shiver-the-wolves-of-mercy-falls-1_392/index.html</t>
+          <t>https://books.toscrape.com/catalogue/shiver-the-wolves-of-mercy-falls-1_392/index.html</t>
         </is>
       </c>
       <c r="F610" t="inlineStr">
@@ -16299,7 +16299,7 @@
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/remember-me_391/index.html</t>
+          <t>https://books.toscrape.com/catalogue/remember-me_391/index.html</t>
         </is>
       </c>
       <c r="F611" t="inlineStr">
@@ -16325,7 +16325,7 @@
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/red-dragon-hannibal-lecter-1_390/index.html</t>
+          <t>https://books.toscrape.com/catalogue/red-dragon-hannibal-lecter-1_390/index.html</t>
         </is>
       </c>
       <c r="F612" t="inlineStr">
@@ -16351,7 +16351,7 @@
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/peak-secrets-from-the-new-science-of-expertise_389/index.html</t>
+          <t>https://books.toscrape.com/catalogue/peak-secrets-from-the-new-science-of-expertise_389/index.html</t>
         </is>
       </c>
       <c r="F613" t="inlineStr">
@@ -16377,7 +16377,7 @@
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/my-mother-was-nuts_388/index.html</t>
+          <t>https://books.toscrape.com/catalogue/my-mother-was-nuts_388/index.html</t>
         </is>
       </c>
       <c r="F614" t="inlineStr">
@@ -16403,7 +16403,7 @@
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/mexican-today-new-and-rediscovered-recipes-for-contemporary-kitchens_387/index.html</t>
+          <t>https://books.toscrape.com/catalogue/mexican-today-new-and-rediscovered-recipes-for-contemporary-kitchens_387/index.html</t>
         </is>
       </c>
       <c r="F615" t="inlineStr">
@@ -16429,7 +16429,7 @@
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/maybe-something-beautiful-how-art-transformed-a-neighborhood_386/index.html</t>
+          <t>https://books.toscrape.com/catalogue/maybe-something-beautiful-how-art-transformed-a-neighborhood_386/index.html</t>
         </is>
       </c>
       <c r="F616" t="inlineStr">
@@ -16455,7 +16455,7 @@
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/lola-and-the-boy-next-door-anna-and-the-french-kiss-2_385/index.html</t>
+          <t>https://books.toscrape.com/catalogue/lola-and-the-boy-next-door-anna-and-the-french-kiss-2_385/index.html</t>
         </is>
       </c>
       <c r="F617" t="inlineStr">
@@ -16481,7 +16481,7 @@
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/logan-kade-fallen-crest-high-55_384/index.html</t>
+          <t>https://books.toscrape.com/catalogue/logan-kade-fallen-crest-high-55_384/index.html</t>
         </is>
       </c>
       <c r="F618" t="inlineStr">
@@ -16507,7 +16507,7 @@
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/last-one-home-new-beginnings-1_383/index.html</t>
+          <t>https://books.toscrape.com/catalogue/last-one-home-new-beginnings-1_383/index.html</t>
         </is>
       </c>
       <c r="F619" t="inlineStr">
@@ -16533,7 +16533,7 @@
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/killing-floor-jack-reacher-1_382/index.html</t>
+          <t>https://books.toscrape.com/catalogue/killing-floor-jack-reacher-1_382/index.html</t>
         </is>
       </c>
       <c r="F620" t="inlineStr">
@@ -16559,7 +16559,7 @@
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/kill-the-boy-band_381/index.html</t>
+          <t>https://books.toscrape.com/catalogue/kill-the-boy-band_381/index.html</t>
         </is>
       </c>
       <c r="F621" t="inlineStr">
@@ -16585,7 +16585,7 @@
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/isla-and-the-happily-ever-after-anna-and-the-french-kiss-3_380/index.html</t>
+          <t>https://books.toscrape.com/catalogue/isla-and-the-happily-ever-after-anna-and-the-french-kiss-3_380/index.html</t>
         </is>
       </c>
       <c r="F622" t="inlineStr">
@@ -16611,7 +16611,7 @@
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/if-i-stay-if-i-stay-1_379/index.html</t>
+          <t>https://books.toscrape.com/catalogue/if-i-stay-if-i-stay-1_379/index.html</t>
         </is>
       </c>
       <c r="F623" t="inlineStr">
@@ -16637,7 +16637,7 @@
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/i-know-why-the-caged-bird-sings-maya-angelous-autobiography-1_378/index.html</t>
+          <t>https://books.toscrape.com/catalogue/i-know-why-the-caged-bird-sings-maya-angelous-autobiography-1_378/index.html</t>
         </is>
       </c>
       <c r="F624" t="inlineStr">
@@ -16663,7 +16663,7 @@
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/harry-potter-and-the-deathly-hallows-harry-potter-7_377/index.html</t>
+          <t>https://books.toscrape.com/catalogue/harry-potter-and-the-deathly-hallows-harry-potter-7_377/index.html</t>
         </is>
       </c>
       <c r="F625" t="inlineStr">
@@ -16689,7 +16689,7 @@
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/fruits-basket-vol-5-fruits-basket-5_376/index.html</t>
+          <t>https://books.toscrape.com/catalogue/fruits-basket-vol-5-fruits-basket-5_376/index.html</t>
         </is>
       </c>
       <c r="F626" t="inlineStr">
@@ -16715,7 +16715,7 @@
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/foundation-foundation-publication-order-1_375/index.html</t>
+          <t>https://books.toscrape.com/catalogue/foundation-foundation-publication-order-1_375/index.html</t>
         </is>
       </c>
       <c r="F627" t="inlineStr">
@@ -16741,7 +16741,7 @@
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/fool-me-once_374/index.html</t>
+          <t>https://books.toscrape.com/catalogue/fool-me-once_374/index.html</t>
         </is>
       </c>
       <c r="F628" t="inlineStr">
@@ -16767,7 +16767,7 @@
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/find-her-detective-dd-warren-8_373/index.html</t>
+          <t>https://books.toscrape.com/catalogue/find-her-detective-dd-warren-8_373/index.html</t>
         </is>
       </c>
       <c r="F629" t="inlineStr">
@@ -16793,7 +16793,7 @@
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/evicted-poverty-and-profit-in-the-american-city_372/index.html</t>
+          <t>https://books.toscrape.com/catalogue/evicted-poverty-and-profit-in-the-american-city_372/index.html</t>
         </is>
       </c>
       <c r="F630" t="inlineStr">
@@ -16819,7 +16819,7 @@
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/drama_371/index.html</t>
+          <t>https://books.toscrape.com/catalogue/drama_371/index.html</t>
         </is>
       </c>
       <c r="F631" t="inlineStr">
@@ -16845,7 +16845,7 @@
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/dracula-the-un-dead_370/index.html</t>
+          <t>https://books.toscrape.com/catalogue/dracula-the-un-dead_370/index.html</t>
         </is>
       </c>
       <c r="F632" t="inlineStr">
@@ -16871,7 +16871,7 @@
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/digital-fortress_369/index.html</t>
+          <t>https://books.toscrape.com/catalogue/digital-fortress_369/index.html</t>
         </is>
       </c>
       <c r="F633" t="inlineStr">
@@ -16897,7 +16897,7 @@
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/death-note-vol-5-whiteout-death-note-5_368/index.html</t>
+          <t>https://books.toscrape.com/catalogue/death-note-vol-5-whiteout-death-note-5_368/index.html</t>
         </is>
       </c>
       <c r="F634" t="inlineStr">
@@ -16923,7 +16923,7 @@
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/data-a-love-story-how-i-gamed-online-dating-to-meet-my-match_367/index.html</t>
+          <t>https://books.toscrape.com/catalogue/data-a-love-story-how-i-gamed-online-dating-to-meet-my-match_367/index.html</t>
         </is>
       </c>
       <c r="F635" t="inlineStr">
@@ -16949,7 +16949,7 @@
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/critique-of-pure-reason_366/index.html</t>
+          <t>https://books.toscrape.com/catalogue/critique-of-pure-reason_366/index.html</t>
         </is>
       </c>
       <c r="F636" t="inlineStr">
@@ -16975,7 +16975,7 @@
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/booked_365/index.html</t>
+          <t>https://books.toscrape.com/catalogue/booked_365/index.html</t>
         </is>
       </c>
       <c r="F637" t="inlineStr">
@@ -17001,7 +17001,7 @@
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/blue-lily-lily-blue-the-raven-cycle-3_364/index.html</t>
+          <t>https://books.toscrape.com/catalogue/blue-lily-lily-blue-the-raven-cycle-3_364/index.html</t>
         </is>
       </c>
       <c r="F638" t="inlineStr">
@@ -17027,7 +17027,7 @@
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/approval-junkie-adventures-in-caring-too-much_363/index.html</t>
+          <t>https://books.toscrape.com/catalogue/approval-junkie-adventures-in-caring-too-much_363/index.html</t>
         </is>
       </c>
       <c r="F639" t="inlineStr">
@@ -17053,7 +17053,7 @@
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/an-abundance-of-katherines_362/index.html</t>
+          <t>https://books.toscrape.com/catalogue/an-abundance-of-katherines_362/index.html</t>
         </is>
       </c>
       <c r="F640" t="inlineStr">
@@ -17079,7 +17079,7 @@
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/americas-war-for-the-greater-middle-east-a-military-history_361/index.html</t>
+          <t>https://books.toscrape.com/catalogue/americas-war-for-the-greater-middle-east-a-military-history_361/index.html</t>
         </is>
       </c>
       <c r="F641" t="inlineStr">
@@ -17105,7 +17105,7 @@
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/alight-the-generations-trilogy-2_360/index.html</t>
+          <t>https://books.toscrape.com/catalogue/alight-the-generations-trilogy-2_360/index.html</t>
         </is>
       </c>
       <c r="F642" t="inlineStr">
@@ -17131,7 +17131,7 @@
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/a-girls-guide-to-moving-on-new-beginnings-2_359/index.html</t>
+          <t>https://books.toscrape.com/catalogue/a-girls-guide-to-moving-on-new-beginnings-2_359/index.html</t>
         </is>
       </c>
       <c r="F643" t="inlineStr">
@@ -17157,7 +17157,7 @@
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/a-game-of-thrones-a-song-of-ice-and-fire-1_358/index.html</t>
+          <t>https://books.toscrape.com/catalogue/a-game-of-thrones-a-song-of-ice-and-fire-1_358/index.html</t>
         </is>
       </c>
       <c r="F644" t="inlineStr">
@@ -17183,7 +17183,7 @@
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/a-feast-for-crows-a-song-of-ice-and-fire-4_357/index.html</t>
+          <t>https://books.toscrape.com/catalogue/a-feast-for-crows-a-song-of-ice-and-fire-4_357/index.html</t>
         </is>
       </c>
       <c r="F645" t="inlineStr">
@@ -17209,7 +17209,7 @@
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/a-clash-of-kings-a-song-of-ice-and-fire-2_356/index.html</t>
+          <t>https://books.toscrape.com/catalogue/a-clash-of-kings-a-song-of-ice-and-fire-2_356/index.html</t>
         </is>
       </c>
       <c r="F646" t="inlineStr">
@@ -17235,7 +17235,7 @@
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/vogue-colors-a-to-z-a-fashion-coloring-book_355/index.html</t>
+          <t>https://books.toscrape.com/catalogue/vogue-colors-a-to-z-a-fashion-coloring-book_355/index.html</t>
         </is>
       </c>
       <c r="F647" t="inlineStr">
@@ -17261,7 +17261,7 @@
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-shining-the-shining-1_354/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-shining-the-shining-1_354/index.html</t>
         </is>
       </c>
       <c r="F648" t="inlineStr">
@@ -17287,7 +17287,7 @@
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-pilgrims-progress_353/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-pilgrims-progress_353/index.html</t>
         </is>
       </c>
       <c r="F649" t="inlineStr">
@@ -17313,7 +17313,7 @@
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-perfect-play-play-by-play-1_352/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-perfect-play-play-by-play-1_352/index.html</t>
         </is>
       </c>
       <c r="F650" t="inlineStr">
@@ -17339,7 +17339,7 @@
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-passion-of-dolssa_351/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-passion-of-dolssa_351/index.html</t>
         </is>
       </c>
       <c r="F651" t="inlineStr">
@@ -17365,7 +17365,7 @@
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-jazz-of-physics-the-secret-link-between-music-and-the-structure-of-the-universe_350/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-jazz-of-physics-the-secret-link-between-music-and-the-structure-of-the-universe_350/index.html</t>
         </is>
       </c>
       <c r="F652" t="inlineStr">
@@ -17391,7 +17391,7 @@
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-hunger-games-the-hunger-games-1_349/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-hunger-games-the-hunger-games-1_349/index.html</t>
         </is>
       </c>
       <c r="F653" t="inlineStr">
@@ -17417,7 +17417,7 @@
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-hound-of-the-baskervilles-sherlock-holmes-5_348/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-hound-of-the-baskervilles-sherlock-holmes-5_348/index.html</t>
         </is>
       </c>
       <c r="F654" t="inlineStr">
@@ -17443,7 +17443,7 @@
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-gunning-of-america-business-and-the-making-of-american-gun-culture_347/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-gunning-of-america-business-and-the-making-of-american-gun-culture_347/index.html</t>
         </is>
       </c>
       <c r="F655" t="inlineStr">
@@ -17469,7 +17469,7 @@
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-geography-of-bliss-one-grumps-search-for-the-happiest-places-in-the-world_346/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-geography-of-bliss-one-grumps-search-for-the-happiest-places-in-the-world_346/index.html</t>
         </is>
       </c>
       <c r="F656" t="inlineStr">
@@ -17495,7 +17495,7 @@
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-demonists-demonist-1_345/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-demonists-demonist-1_345/index.html</t>
         </is>
       </c>
       <c r="F657" t="inlineStr">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-demon-prince-of-momochi-house-vol-4-the-demon-prince-of-momochi-house-4_344/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-demon-prince-of-momochi-house-vol-4-the-demon-prince-of-momochi-house-4_344/index.html</t>
         </is>
       </c>
       <c r="F658" t="inlineStr">
@@ -17547,7 +17547,7 @@
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-bone-hunters-lexy-vaughan-steven-macaulay-2_343/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-bone-hunters-lexy-vaughan-steven-macaulay-2_343/index.html</t>
         </is>
       </c>
       <c r="F659" t="inlineStr">
@@ -17573,7 +17573,7 @@
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-beast-black-dagger-brotherhood-14_342/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-beast-black-dagger-brotherhood-14_342/index.html</t>
         </is>
       </c>
       <c r="F660" t="inlineStr">
@@ -17599,7 +17599,7 @@
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/some-women_341/index.html</t>
+          <t>https://books.toscrape.com/catalogue/some-women_341/index.html</t>
         </is>
       </c>
       <c r="F661" t="inlineStr">
@@ -17625,7 +17625,7 @@
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/shopaholic-ties-the-knot-shopaholic-3_340/index.html</t>
+          <t>https://books.toscrape.com/catalogue/shopaholic-ties-the-knot-shopaholic-3_340/index.html</t>
         </is>
       </c>
       <c r="F662" t="inlineStr">
@@ -17651,7 +17651,7 @@
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/paper-and-fire-the-great-library-2_339/index.html</t>
+          <t>https://books.toscrape.com/catalogue/paper-and-fire-the-great-library-2_339/index.html</t>
         </is>
       </c>
       <c r="F663" t="inlineStr">
@@ -17677,7 +17677,7 @@
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/outlander-outlander-1_338/index.html</t>
+          <t>https://books.toscrape.com/catalogue/outlander-outlander-1_338/index.html</t>
         </is>
       </c>
       <c r="F664" t="inlineStr">
@@ -17703,7 +17703,7 @@
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/orchestra-of-exiles-the-story-of-bronislaw-huberman-the-israel-philharmonic-and-the-one-thousand-jews-he-saved-from-nazi-horrors_337/index.html</t>
+          <t>https://books.toscrape.com/catalogue/orchestra-of-exiles-the-story-of-bronislaw-huberman-the-israel-philharmonic-and-the-one-thousand-jews-he-saved-from-nazi-horrors_337/index.html</t>
         </is>
       </c>
       <c r="F665" t="inlineStr">
@@ -17729,7 +17729,7 @@
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/no-one-here-gets-out-alive_336/index.html</t>
+          <t>https://books.toscrape.com/catalogue/no-one-here-gets-out-alive_336/index.html</t>
         </is>
       </c>
       <c r="F666" t="inlineStr">
@@ -17755,7 +17755,7 @@
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/night-shift-night-shift-1-20_335/index.html</t>
+          <t>https://books.toscrape.com/catalogue/night-shift-night-shift-1-20_335/index.html</t>
         </is>
       </c>
       <c r="F667" t="inlineStr">
@@ -17781,7 +17781,7 @@
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/needful-things_334/index.html</t>
+          <t>https://books.toscrape.com/catalogue/needful-things_334/index.html</t>
         </is>
       </c>
       <c r="F668" t="inlineStr">
@@ -17807,7 +17807,7 @@
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/mockingjay-the-hunger-games-3_333/index.html</t>
+          <t>https://books.toscrape.com/catalogue/mockingjay-the-hunger-games-3_333/index.html</t>
         </is>
       </c>
       <c r="F669" t="inlineStr">
@@ -17833,7 +17833,7 @@
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/misery_332/index.html</t>
+          <t>https://books.toscrape.com/catalogue/misery_332/index.html</t>
         </is>
       </c>
       <c r="F670" t="inlineStr">
@@ -17859,7 +17859,7 @@
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/little-women-little-women-1_331/index.html</t>
+          <t>https://books.toscrape.com/catalogue/little-women-little-women-1_331/index.html</t>
         </is>
       </c>
       <c r="F671" t="inlineStr">
@@ -17885,7 +17885,7 @@
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/it_330/index.html</t>
+          <t>https://books.toscrape.com/catalogue/it_330/index.html</t>
         </is>
       </c>
       <c r="F672" t="inlineStr">
@@ -17911,7 +17911,7 @@
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/harry-potter-and-the-sorcerers-stone-harry-potter-1_329/index.html</t>
+          <t>https://books.toscrape.com/catalogue/harry-potter-and-the-sorcerers-stone-harry-potter-1_329/index.html</t>
         </is>
       </c>
       <c r="F673" t="inlineStr">
@@ -17937,7 +17937,7 @@
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/harry-potter-and-the-prisoner-of-azkaban-harry-potter-3_328/index.html</t>
+          <t>https://books.toscrape.com/catalogue/harry-potter-and-the-prisoner-of-azkaban-harry-potter-3_328/index.html</t>
         </is>
       </c>
       <c r="F674" t="inlineStr">
@@ -17963,7 +17963,7 @@
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/harry-potter-and-the-order-of-the-phoenix-harry-potter-5_327/index.html</t>
+          <t>https://books.toscrape.com/catalogue/harry-potter-and-the-order-of-the-phoenix-harry-potter-5_327/index.html</t>
         </is>
       </c>
       <c r="F675" t="inlineStr">
@@ -17989,7 +17989,7 @@
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/harry-potter-and-the-half-blood-prince-harry-potter-6_326/index.html</t>
+          <t>https://books.toscrape.com/catalogue/harry-potter-and-the-half-blood-prince-harry-potter-6_326/index.html</t>
         </is>
       </c>
       <c r="F676" t="inlineStr">
@@ -18015,7 +18015,7 @@
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/harry-potter-and-the-chamber-of-secrets-harry-potter-2_325/index.html</t>
+          <t>https://books.toscrape.com/catalogue/harry-potter-and-the-chamber-of-secrets-harry-potter-2_325/index.html</t>
         </is>
       </c>
       <c r="F677" t="inlineStr">
@@ -18041,7 +18041,7 @@
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/gone-with-the-wind_324/index.html</t>
+          <t>https://books.toscrape.com/catalogue/gone-with-the-wind_324/index.html</t>
         </is>
       </c>
       <c r="F678" t="inlineStr">
@@ -18067,7 +18067,7 @@
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/god-is-not-great-how-religion-poisons-everything_323/index.html</t>
+          <t>https://books.toscrape.com/catalogue/god-is-not-great-how-religion-poisons-everything_323/index.html</t>
         </is>
       </c>
       <c r="F679" t="inlineStr">
@@ -18093,7 +18093,7 @@
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/girl-with-a-pearl-earring_322/index.html</t>
+          <t>https://books.toscrape.com/catalogue/girl-with-a-pearl-earring_322/index.html</t>
         </is>
       </c>
       <c r="F680" t="inlineStr">
@@ -18119,7 +18119,7 @@
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/fruits-basket-vol-4-fruits-basket-4_321/index.html</t>
+          <t>https://books.toscrape.com/catalogue/fruits-basket-vol-4-fruits-basket-4_321/index.html</t>
         </is>
       </c>
       <c r="F681" t="inlineStr">
@@ -18145,7 +18145,7 @@
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/far-from-true-promise-falls-trilogy-2_320/index.html</t>
+          <t>https://books.toscrape.com/catalogue/far-from-true-promise-falls-trilogy-2_320/index.html</t>
         </is>
       </c>
       <c r="F682" t="inlineStr">
@@ -18171,7 +18171,7 @@
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/dark-lover-black-dagger-brotherhood-1_319/index.html</t>
+          <t>https://books.toscrape.com/catalogue/dark-lover-black-dagger-brotherhood-1_319/index.html</t>
         </is>
       </c>
       <c r="F683" t="inlineStr">
@@ -18197,7 +18197,7 @@
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/confessions-of-a-shopaholic-shopaholic-1_318/index.html</t>
+          <t>https://books.toscrape.com/catalogue/confessions-of-a-shopaholic-shopaholic-1_318/index.html</t>
         </is>
       </c>
       <c r="F684" t="inlineStr">
@@ -18223,7 +18223,7 @@
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/changing-the-game-play-by-play-2_317/index.html</t>
+          <t>https://books.toscrape.com/catalogue/changing-the-game-play-by-play-2_317/index.html</t>
         </is>
       </c>
       <c r="F685" t="inlineStr">
@@ -18249,7 +18249,7 @@
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/candide_316/index.html</t>
+          <t>https://books.toscrape.com/catalogue/candide_316/index.html</t>
         </is>
       </c>
       <c r="F686" t="inlineStr">
@@ -18275,7 +18275,7 @@
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/can-you-keep-a-secret_315/index.html</t>
+          <t>https://books.toscrape.com/catalogue/can-you-keep-a-secret_315/index.html</t>
         </is>
       </c>
       <c r="F687" t="inlineStr">
@@ -18301,7 +18301,7 @@
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/atlas-shrugged_314/index.html</t>
+          <t>https://books.toscrape.com/catalogue/atlas-shrugged_314/index.html</t>
         </is>
       </c>
       <c r="F688" t="inlineStr">
@@ -18327,7 +18327,7 @@
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/animal-farm_313/index.html</t>
+          <t>https://books.toscrape.com/catalogue/animal-farm_313/index.html</t>
         </is>
       </c>
       <c r="F689" t="inlineStr">
@@ -18353,7 +18353,7 @@
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/a-walk-to-remember_312/index.html</t>
+          <t>https://books.toscrape.com/catalogue/a-walk-to-remember_312/index.html</t>
         </is>
       </c>
       <c r="F690" t="inlineStr">
@@ -18379,7 +18379,7 @@
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/a-new-earth-awakening-to-your-lifes-purpose_311/index.html</t>
+          <t>https://books.toscrape.com/catalogue/a-new-earth-awakening-to-your-lifes-purpose_311/index.html</t>
         </is>
       </c>
       <c r="F691" t="inlineStr">
@@ -18405,7 +18405,7 @@
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/a-history-of-god-the-4000-year-quest-of-judaism-christianity-and-islam_310/index.html</t>
+          <t>https://books.toscrape.com/catalogue/a-history-of-god-the-4000-year-quest-of-judaism-christianity-and-islam_310/index.html</t>
         </is>
       </c>
       <c r="F692" t="inlineStr">
@@ -18431,7 +18431,7 @@
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/salems-lot_309/index.html</t>
+          <t>https://books.toscrape.com/catalogue/salems-lot_309/index.html</t>
         </is>
       </c>
       <c r="F693" t="inlineStr">
@@ -18457,7 +18457,7 @@
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/zero-history-blue-ant-3_308/index.html</t>
+          <t>https://books.toscrape.com/catalogue/zero-history-blue-ant-3_308/index.html</t>
         </is>
       </c>
       <c r="F694" t="inlineStr">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/wuthering-heights_307/index.html</t>
+          <t>https://books.toscrape.com/catalogue/wuthering-heights_307/index.html</t>
         </is>
       </c>
       <c r="F695" t="inlineStr">
@@ -18509,7 +18509,7 @@
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/world-war-z-an-oral-history-of-the-zombie-war_306/index.html</t>
+          <t>https://books.toscrape.com/catalogue/world-war-z-an-oral-history-of-the-zombie-war_306/index.html</t>
         </is>
       </c>
       <c r="F696" t="inlineStr">
@@ -18535,7 +18535,7 @@
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/wild-from-lost-to-found-on-the-pacific-crest-trail_305/index.html</t>
+          <t>https://books.toscrape.com/catalogue/wild-from-lost-to-found-on-the-pacific-crest-trail_305/index.html</t>
         </is>
       </c>
       <c r="F697" t="inlineStr">
@@ -18561,7 +18561,7 @@
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/whered-you-go-bernadette_304/index.html</t>
+          <t>https://books.toscrape.com/catalogue/whered-you-go-bernadette_304/index.html</t>
         </is>
       </c>
       <c r="F698" t="inlineStr">
@@ -18587,7 +18587,7 @@
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/when-you-are-engulfed-in-flames_303/index.html</t>
+          <t>https://books.toscrape.com/catalogue/when-you-are-engulfed-in-flames_303/index.html</t>
         </is>
       </c>
       <c r="F699" t="inlineStr">
@@ -18613,7 +18613,7 @@
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/we-the-people-the-modern-day-figures-who-have-reshaped-and-affirmed-the-founding-fathers-vision-of-america_302/index.html</t>
+          <t>https://books.toscrape.com/catalogue/we-the-people-the-modern-day-figures-who-have-reshaped-and-affirmed-the-founding-fathers-vision-of-america_302/index.html</t>
         </is>
       </c>
       <c r="F700" t="inlineStr">
@@ -18639,7 +18639,7 @@
       </c>
       <c r="E701" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/we-are-all-completely-beside-ourselves_301/index.html</t>
+          <t>https://books.toscrape.com/catalogue/we-are-all-completely-beside-ourselves_301/index.html</t>
         </is>
       </c>
       <c r="F701" t="inlineStr">
@@ -18665,7 +18665,7 @@
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/walk-the-edge-thunder-road-2_300/index.html</t>
+          <t>https://books.toscrape.com/catalogue/walk-the-edge-thunder-road-2_300/index.html</t>
         </is>
       </c>
       <c r="F702" t="inlineStr">
@@ -18691,7 +18691,7 @@
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/voyager-outlander-3_299/index.html</t>
+          <t>https://books.toscrape.com/catalogue/voyager-outlander-3_299/index.html</t>
         </is>
       </c>
       <c r="F703" t="inlineStr">
@@ -18717,7 +18717,7 @@
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/very-good-lives-the-fringe-benefits-of-failure-and-the-importance-of-imagination_298/index.html</t>
+          <t>https://books.toscrape.com/catalogue/very-good-lives-the-fringe-benefits-of-failure-and-the-importance-of-imagination_298/index.html</t>
         </is>
       </c>
       <c r="F704" t="inlineStr">
@@ -18743,7 +18743,7 @@
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/vegan-vegetarian-omnivore-dinner-for-everyone-at-the-table_297/index.html</t>
+          <t>https://books.toscrape.com/catalogue/vegan-vegetarian-omnivore-dinner-for-everyone-at-the-table_297/index.html</t>
         </is>
       </c>
       <c r="F705" t="inlineStr">
@@ -18769,7 +18769,7 @@
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/unstuffed-decluttering-your-home-mind-and-soul_296/index.html</t>
+          <t>https://books.toscrape.com/catalogue/unstuffed-decluttering-your-home-mind-and-soul_296/index.html</t>
         </is>
       </c>
       <c r="F706" t="inlineStr">
@@ -18795,7 +18795,7 @@
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/under-the-banner-of-heaven-a-story-of-violent-faith_295/index.html</t>
+          <t>https://books.toscrape.com/catalogue/under-the-banner-of-heaven-a-story-of-violent-faith_295/index.html</t>
         </is>
       </c>
       <c r="F707" t="inlineStr">
@@ -18821,7 +18821,7 @@
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/two-boys-kissing_294/index.html</t>
+          <t>https://books.toscrape.com/catalogue/two-boys-kissing_294/index.html</t>
         </is>
       </c>
       <c r="F708" t="inlineStr">
@@ -18847,7 +18847,7 @@
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/twilight-twilight-1_293/index.html</t>
+          <t>https://books.toscrape.com/catalogue/twilight-twilight-1_293/index.html</t>
         </is>
       </c>
       <c r="F709" t="inlineStr">
@@ -18873,7 +18873,7 @@
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/twenties-girl_292/index.html</t>
+          <t>https://books.toscrape.com/catalogue/twenties-girl_292/index.html</t>
         </is>
       </c>
       <c r="F710" t="inlineStr">
@@ -18899,7 +18899,7 @@
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/trespassing-across-america-one-mans-epic-never-done-before-and-sort-of-illegal-hike-across-the-heartland_291/index.html</t>
+          <t>https://books.toscrape.com/catalogue/trespassing-across-america-one-mans-epic-never-done-before-and-sort-of-illegal-hike-across-the-heartland_291/index.html</t>
         </is>
       </c>
       <c r="F711" t="inlineStr">
@@ -18925,7 +18925,7 @@
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/three-martini-lunch_290/index.html</t>
+          <t>https://books.toscrape.com/catalogue/three-martini-lunch_290/index.html</t>
         </is>
       </c>
       <c r="F712" t="inlineStr">
@@ -18951,7 +18951,7 @@
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/thinking-fast-and-slow_289/index.html</t>
+          <t>https://books.toscrape.com/catalogue/thinking-fast-and-slow_289/index.html</t>
         </is>
       </c>
       <c r="F713" t="inlineStr">
@@ -18977,7 +18977,7 @@
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-wild-robot_288/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-wild-robot_288/index.html</t>
         </is>
       </c>
       <c r="F714" t="inlineStr">
@@ -19003,7 +19003,7 @@
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-wicked-the-divine-vol-3-commercial-suicide-the-wicked-the-divine_287/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-wicked-the-divine-vol-3-commercial-suicide-the-wicked-the-divine_287/index.html</t>
         </is>
       </c>
       <c r="F715" t="inlineStr">
@@ -19029,7 +19029,7 @@
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-undomestic-goddess_286/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-undomestic-goddess_286/index.html</t>
         </is>
       </c>
       <c r="F716" t="inlineStr">
@@ -19055,7 +19055,7 @@
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-travelers_285/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-travelers_285/index.html</t>
         </is>
       </c>
       <c r="F717" t="inlineStr">
@@ -19081,7 +19081,7 @@
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-tipping-point-how-little-things-can-make-a-big-difference_284/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-tipping-point-how-little-things-can-make-a-big-difference_284/index.html</t>
         </is>
       </c>
       <c r="F718" t="inlineStr">
@@ -19107,7 +19107,7 @@
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-thing-about-jellyfish_283/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-thing-about-jellyfish_283/index.html</t>
         </is>
       </c>
       <c r="F719" t="inlineStr">
@@ -19133,7 +19133,7 @@
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-stand_282/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-stand_282/index.html</t>
         </is>
       </c>
       <c r="F720" t="inlineStr">
@@ -19159,7 +19159,7 @@
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-smitten-kitchen-cookbook_281/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-smitten-kitchen-cookbook_281/index.html</t>
         </is>
       </c>
       <c r="F721" t="inlineStr">
@@ -19185,7 +19185,7 @@
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-silkworm-cormoran-strike-2_280/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-silkworm-cormoran-strike-2_280/index.html</t>
         </is>
       </c>
       <c r="F722" t="inlineStr">
@@ -19211,7 +19211,7 @@
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-sandman-vol-3-dream-country-the-sandman-volumes-3_279/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-sandman-vol-3-dream-country-the-sandman-volumes-3_279/index.html</t>
         </is>
       </c>
       <c r="F723" t="inlineStr">
@@ -19237,7 +19237,7 @@
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-rose-the-dagger-the-wrath-and-the-dawn-2_278/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-rose-the-dagger-the-wrath-and-the-dawn-2_278/index.html</t>
         </is>
       </c>
       <c r="F724" t="inlineStr">
@@ -19263,7 +19263,7 @@
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-road-to-little-dribbling-adventures-of-an-american-in-britain-notes-from-a-small-island-2_277/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-road-to-little-dribbling-adventures-of-an-american-in-britain-notes-from-a-small-island-2_277/index.html</t>
         </is>
       </c>
       <c r="F725" t="inlineStr">
@@ -19289,7 +19289,7 @@
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-rise-of-theodore-roosevelt-theodore-roosevelt-1_276/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-rise-of-theodore-roosevelt-theodore-roosevelt-1_276/index.html</t>
         </is>
       </c>
       <c r="F726" t="inlineStr">
@@ -19315,7 +19315,7 @@
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-restaurant-at-the-end-of-the-universe-hitchhikers-guide-to-the-galaxy-2_275/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-restaurant-at-the-end-of-the-universe-hitchhikers-guide-to-the-galaxy-2_275/index.html</t>
         </is>
       </c>
       <c r="F727" t="inlineStr">
@@ -19341,7 +19341,7 @@
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-rest-is-noise-listening-to-the-twentieth-century_274/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-rest-is-noise-listening-to-the-twentieth-century_274/index.html</t>
         </is>
       </c>
       <c r="F728" t="inlineStr">
@@ -19367,7 +19367,7 @@
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-red-tent_273/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-red-tent_273/index.html</t>
         </is>
       </c>
       <c r="F729" t="inlineStr">
@@ -19393,7 +19393,7 @@
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-purpose-driven-life-what-on-earth-am-i-here-for_272/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-purpose-driven-life-what-on-earth-am-i-here-for_272/index.html</t>
         </is>
       </c>
       <c r="F730" t="inlineStr">
@@ -19419,7 +19419,7 @@
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-purest-hook-second-circle-tattoos-3_271/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-purest-hook-second-circle-tattoos-3_271/index.html</t>
         </is>
       </c>
       <c r="F731" t="inlineStr">
@@ -19445,7 +19445,7 @@
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-picture-of-dorian-gray_270/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-picture-of-dorian-gray_270/index.html</t>
         </is>
       </c>
       <c r="F732" t="inlineStr">
@@ -19471,7 +19471,7 @@
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-paris-wife_269/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-paris-wife_269/index.html</t>
         </is>
       </c>
       <c r="F733" t="inlineStr">
@@ -19497,7 +19497,7 @@
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-obsession_268/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-obsession_268/index.html</t>
         </is>
       </c>
       <c r="F734" t="inlineStr">
@@ -19523,7 +19523,7 @@
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-nightingale_267/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-nightingale_267/index.html</t>
         </is>
       </c>
       <c r="F735" t="inlineStr">
@@ -19549,7 +19549,7 @@
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-new-guy-and-other-senior-year-distractions_266/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-new-guy-and-other-senior-year-distractions_266/index.html</t>
         </is>
       </c>
       <c r="F736" t="inlineStr">
@@ -19575,7 +19575,7 @@
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-nanny-diaries-nanny-1_265/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-nanny-diaries-nanny-1_265/index.html</t>
         </is>
       </c>
       <c r="F737" t="inlineStr">
@@ -19601,7 +19601,7 @@
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-name-of-god-is-mercy_264/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-name-of-god-is-mercy_264/index.html</t>
         </is>
       </c>
       <c r="F738" t="inlineStr">
@@ -19627,7 +19627,7 @@
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-maze-runner-the-maze-runner-1_263/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-maze-runner-the-maze-runner-1_263/index.html</t>
         </is>
       </c>
       <c r="F739" t="inlineStr">
@@ -19653,7 +19653,7 @@
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-lovers-dictionary_262/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-lovers-dictionary_262/index.html</t>
         </is>
       </c>
       <c r="F740" t="inlineStr">
@@ -19679,7 +19679,7 @@
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-lonely-ones_261/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-lonely-ones_261/index.html</t>
         </is>
       </c>
       <c r="F741" t="inlineStr">
@@ -19705,7 +19705,7 @@
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-lean-startup-how-todays-entrepreneurs-use-continuous-innovation-to-create-radically-successful-businesses_260/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-lean-startup-how-todays-entrepreneurs-use-continuous-innovation-to-create-radically-successful-businesses_260/index.html</t>
         </is>
       </c>
       <c r="F742" t="inlineStr">
@@ -19731,7 +19731,7 @@
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-last-painting-of-sara-de-vos_259/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-last-painting-of-sara-de-vos_259/index.html</t>
         </is>
       </c>
       <c r="F743" t="inlineStr">
@@ -19757,7 +19757,7 @@
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-land-of-10000-madonnas_258/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-land-of-10000-madonnas_258/index.html</t>
         </is>
       </c>
       <c r="F744" t="inlineStr">
@@ -19783,7 +19783,7 @@
       </c>
       <c r="E745" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-infinities_257/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-infinities_257/index.html</t>
         </is>
       </c>
       <c r="F745" t="inlineStr">
@@ -19809,7 +19809,7 @@
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-husbands-secret_256/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-husbands-secret_256/index.html</t>
         </is>
       </c>
       <c r="F746" t="inlineStr">
@@ -19835,7 +19835,7 @@
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-hitchhikers-guide-to-the-galaxy-hitchhikers-guide-to-the-galaxy-1_255/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-hitchhikers-guide-to-the-galaxy-hitchhikers-guide-to-the-galaxy-1_255/index.html</t>
         </is>
       </c>
       <c r="F747" t="inlineStr">
@@ -19861,7 +19861,7 @@
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-guns-of-august_254/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-guns-of-august_254/index.html</t>
         </is>
       </c>
       <c r="F748" t="inlineStr">
@@ -19887,7 +19887,7 @@
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-guernsey-literary-and-potato-peel-pie-society_253/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-guernsey-literary-and-potato-peel-pie-society_253/index.html</t>
         </is>
       </c>
       <c r="F749" t="inlineStr">
@@ -19913,7 +19913,7 @@
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-goldfinch_252/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-goldfinch_252/index.html</t>
         </is>
       </c>
       <c r="F750" t="inlineStr">
@@ -19939,7 +19939,7 @@
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-giver-the-giver-quartet-1_251/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-giver-the-giver-quartet-1_251/index.html</t>
         </is>
       </c>
       <c r="F751" t="inlineStr">
@@ -19965,7 +19965,7 @@
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-girl-with-all-the-gifts_250/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-girl-with-all-the-gifts_250/index.html</t>
         </is>
       </c>
       <c r="F752" t="inlineStr">
@@ -19991,7 +19991,7 @@
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-girl-who-played-with-fire-millennium-trilogy-2_249/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-girl-who-played-with-fire-millennium-trilogy-2_249/index.html</t>
         </is>
       </c>
       <c r="F753" t="inlineStr">
@@ -20017,7 +20017,7 @@
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-girl-who-kicked-the-hornets-nest-millennium-trilogy-3_248/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-girl-who-kicked-the-hornets-nest-millennium-trilogy-3_248/index.html</t>
         </is>
       </c>
       <c r="F754" t="inlineStr">
@@ -20043,7 +20043,7 @@
       </c>
       <c r="E755" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-exiled_247/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-exiled_247/index.html</t>
         </is>
       </c>
       <c r="F755" t="inlineStr">
@@ -20069,7 +20069,7 @@
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-end-of-faith-religion-terror-and-the-future-of-reason_246/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-end-of-faith-religion-terror-and-the-future-of-reason_246/index.html</t>
         </is>
       </c>
       <c r="F756" t="inlineStr">
@@ -20095,7 +20095,7 @@
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-elegant-universe-superstrings-hidden-dimensions-and-the-quest-for-the-ultimate-theory_245/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-elegant-universe-superstrings-hidden-dimensions-and-the-quest-for-the-ultimate-theory_245/index.html</t>
         </is>
       </c>
       <c r="F757" t="inlineStr">
@@ -20121,7 +20121,7 @@
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-disappearing-spoon-and-other-true-tales-of-madness-love-and-the-history-of-the-world-from-the-periodic-table-of-the-elements_244/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-disappearing-spoon-and-other-true-tales-of-madness-love-and-the-history-of-the-world-from-the-periodic-table-of-the-elements_244/index.html</t>
         </is>
       </c>
       <c r="F758" t="inlineStr">
@@ -20147,7 +20147,7 @@
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-devil-wears-prada-the-devil-wears-prada-1_243/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-devil-wears-prada-the-devil-wears-prada-1_243/index.html</t>
         </is>
       </c>
       <c r="F759" t="inlineStr">
@@ -20173,7 +20173,7 @@
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-demon-haunted-world-science-as-a-candle-in-the-dark_242/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-demon-haunted-world-science-as-a-candle-in-the-dark_242/index.html</t>
         </is>
       </c>
       <c r="F760" t="inlineStr">
@@ -20199,7 +20199,7 @@
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-day-the-crayons-came-home-crayons_241/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-day-the-crayons-came-home-crayons_241/index.html</t>
         </is>
       </c>
       <c r="F761" t="inlineStr">
@@ -20225,7 +20225,7 @@
       </c>
       <c r="E762" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-da-vinci-code-robert-langdon-2_240/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-da-vinci-code-robert-langdon-2_240/index.html</t>
         </is>
       </c>
       <c r="F762" t="inlineStr">
@@ -20251,7 +20251,7 @@
       </c>
       <c r="E763" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-cuckoos-calling-cormoran-strike-1_239/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-cuckoos-calling-cormoran-strike-1_239/index.html</t>
         </is>
       </c>
       <c r="F763" t="inlineStr">
@@ -20277,7 +20277,7 @@
       </c>
       <c r="E764" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-complete-stories-and-poems-the-works-of-edgar-allan-poe-cameo-edition_238/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-complete-stories-and-poems-the-works-of-edgar-allan-poe-cameo-edition_238/index.html</t>
         </is>
       </c>
       <c r="F764" t="inlineStr">
@@ -20303,7 +20303,7 @@
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-complete-poems_237/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-complete-poems_237/index.html</t>
         </is>
       </c>
       <c r="F765" t="inlineStr">
@@ -20329,7 +20329,7 @@
       </c>
       <c r="E766" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-catcher-in-the-rye_236/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-catcher-in-the-rye_236/index.html</t>
         </is>
       </c>
       <c r="F766" t="inlineStr">
@@ -20355,7 +20355,7 @@
       </c>
       <c r="E767" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-cat-in-the-hat-beginner-books-b-1_235/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-cat-in-the-hat-beginner-books-b-1_235/index.html</t>
         </is>
       </c>
       <c r="F767" t="inlineStr">
@@ -20381,7 +20381,7 @@
       </c>
       <c r="E768" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-case-for-christ-cases-for-christianity_234/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-case-for-christ-cases-for-christianity_234/index.html</t>
         </is>
       </c>
       <c r="F768" t="inlineStr">
@@ -20407,7 +20407,7 @@
       </c>
       <c r="E769" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-book-thief_233/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-book-thief_233/index.html</t>
         </is>
       </c>
       <c r="F769" t="inlineStr">
@@ -20433,7 +20433,7 @@
       </c>
       <c r="E770" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-book-of-basketball-the-nba-according-to-the-sports-guy_232/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-book-of-basketball-the-nba-according-to-the-sports-guy_232/index.html</t>
         </is>
       </c>
       <c r="F770" t="inlineStr">
@@ -20459,7 +20459,7 @@
       </c>
       <c r="E771" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-blind-side-evolution-of-a-game_231/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-blind-side-evolution-of-a-game_231/index.html</t>
         </is>
       </c>
       <c r="F771" t="inlineStr">
@@ -20485,7 +20485,7 @@
       </c>
       <c r="E772" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-autobiography-of-malcolm-x_230/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-autobiography-of-malcolm-x_230/index.html</t>
         </is>
       </c>
       <c r="F772" t="inlineStr">
@@ -20511,7 +20511,7 @@
       </c>
       <c r="E773" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-art-of-simple-food-notes-lessons-and-recipes-from-a-delicious-revolution_229/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-art-of-simple-food-notes-lessons-and-recipes-from-a-delicious-revolution_229/index.html</t>
         </is>
       </c>
       <c r="F773" t="inlineStr">
@@ -20537,7 +20537,7 @@
       </c>
       <c r="E774" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-art-of-fielding_228/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-art-of-fielding_228/index.html</t>
         </is>
       </c>
       <c r="F774" t="inlineStr">
@@ -20563,7 +20563,7 @@
       </c>
       <c r="E775" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/surely-youre-joking-mr-feynman-adventures-of-a-curious-character_227/index.html</t>
+          <t>https://books.toscrape.com/catalogue/surely-youre-joking-mr-feynman-adventures-of-a-curious-character_227/index.html</t>
         </is>
       </c>
       <c r="F775" t="inlineStr">
@@ -20589,7 +20589,7 @@
       </c>
       <c r="E776" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/stiff-the-curious-lives-of-human-cadavers_226/index.html</t>
+          <t>https://books.toscrape.com/catalogue/stiff-the-curious-lives-of-human-cadavers_226/index.html</t>
         </is>
       </c>
       <c r="F776" t="inlineStr">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="E777" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/spilled-milk-based-on-a-true-story_225/index.html</t>
+          <t>https://books.toscrape.com/catalogue/spilled-milk-based-on-a-true-story_225/index.html</t>
         </is>
       </c>
       <c r="F777" t="inlineStr">
@@ -20641,7 +20641,7 @@
       </c>
       <c r="E778" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/something-borrowed-darcy-rachel-1_224/index.html</t>
+          <t>https://books.toscrape.com/catalogue/something-borrowed-darcy-rachel-1_224/index.html</t>
         </is>
       </c>
       <c r="F778" t="inlineStr">
@@ -20667,7 +20667,7 @@
       </c>
       <c r="E779" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/something-blue-darcy-rachel-2_223/index.html</t>
+          <t>https://books.toscrape.com/catalogue/something-blue-darcy-rachel-2_223/index.html</t>
         </is>
       </c>
       <c r="F779" t="inlineStr">
@@ -20693,7 +20693,7 @@
       </c>
       <c r="E780" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/soldier-talon-3_222/index.html</t>
+          <t>https://books.toscrape.com/catalogue/soldier-talon-3_222/index.html</t>
         </is>
       </c>
       <c r="F780" t="inlineStr">
@@ -20719,7 +20719,7 @@
       </c>
       <c r="E781" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/shopaholic-baby-shopaholic-5_221/index.html</t>
+          <t>https://books.toscrape.com/catalogue/shopaholic-baby-shopaholic-5_221/index.html</t>
         </is>
       </c>
       <c r="F781" t="inlineStr">
@@ -20745,7 +20745,7 @@
       </c>
       <c r="E782" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/seven-days-in-the-art-world_220/index.html</t>
+          <t>https://books.toscrape.com/catalogue/seven-days-in-the-art-world_220/index.html</t>
         </is>
       </c>
       <c r="F782" t="inlineStr">
@@ -20771,7 +20771,7 @@
       </c>
       <c r="E783" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/seven-brief-lessons-on-physics_219/index.html</t>
+          <t>https://books.toscrape.com/catalogue/seven-brief-lessons-on-physics_219/index.html</t>
         </is>
       </c>
       <c r="F783" t="inlineStr">
@@ -20797,7 +20797,7 @@
       </c>
       <c r="E784" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/scarlet-the-lunar-chronicles-2_218/index.html</t>
+          <t>https://books.toscrape.com/catalogue/scarlet-the-lunar-chronicles-2_218/index.html</t>
         </is>
       </c>
       <c r="F784" t="inlineStr">
@@ -20823,7 +20823,7 @@
       </c>
       <c r="E785" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/sarahs-key_217/index.html</t>
+          <t>https://books.toscrape.com/catalogue/sarahs-key_217/index.html</t>
         </is>
       </c>
       <c r="F785" t="inlineStr">
@@ -20849,7 +20849,7 @@
       </c>
       <c r="E786" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/saga-volume-3-saga-collected-editions-3_216/index.html</t>
+          <t>https://books.toscrape.com/catalogue/saga-volume-3-saga-collected-editions-3_216/index.html</t>
         </is>
       </c>
       <c r="F786" t="inlineStr">
@@ -20875,7 +20875,7 @@
       </c>
       <c r="E787" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/running-with-scissors_215/index.html</t>
+          <t>https://books.toscrape.com/catalogue/running-with-scissors_215/index.html</t>
         </is>
       </c>
       <c r="F787" t="inlineStr">
@@ -20901,7 +20901,7 @@
       </c>
       <c r="E788" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/rogue-lawyer-rogue-lawyer-1_214/index.html</t>
+          <t>https://books.toscrape.com/catalogue/rogue-lawyer-rogue-lawyer-1_214/index.html</t>
         </is>
       </c>
       <c r="F788" t="inlineStr">
@@ -20927,7 +20927,7 @@
       </c>
       <c r="E789" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/rise-of-the-rocket-girls-the-women-who-propelled-us-from-missiles-to-the-moon-to-mars_213/index.html</t>
+          <t>https://books.toscrape.com/catalogue/rise-of-the-rocket-girls-the-women-who-propelled-us-from-missiles-to-the-moon-to-mars_213/index.html</t>
         </is>
       </c>
       <c r="F789" t="inlineStr">
@@ -20953,7 +20953,7 @@
       </c>
       <c r="E790" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/rework_212/index.html</t>
+          <t>https://books.toscrape.com/catalogue/rework_212/index.html</t>
         </is>
       </c>
       <c r="F790" t="inlineStr">
@@ -20979,7 +20979,7 @@
       </c>
       <c r="E791" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/reservations-for-two_211/index.html</t>
+          <t>https://books.toscrape.com/catalogue/reservations-for-two_211/index.html</t>
         </is>
       </c>
       <c r="F791" t="inlineStr">
@@ -21005,7 +21005,7 @@
       </c>
       <c r="E792" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/red-the-true-story-of-red-riding-hood_210/index.html</t>
+          <t>https://books.toscrape.com/catalogue/red-the-true-story-of-red-riding-hood_210/index.html</t>
         </is>
       </c>
       <c r="F792" t="inlineStr">
@@ -21031,7 +21031,7 @@
       </c>
       <c r="E793" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/ready-player-one_209/index.html</t>
+          <t>https://books.toscrape.com/catalogue/ready-player-one_209/index.html</t>
         </is>
       </c>
       <c r="F793" t="inlineStr">
@@ -21057,7 +21057,7 @@
       </c>
       <c r="E794" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/quiet-the-power-of-introverts-in-a-world-that-cant-stop-talking_208/index.html</t>
+          <t>https://books.toscrape.com/catalogue/quiet-the-power-of-introverts-in-a-world-that-cant-stop-talking_208/index.html</t>
         </is>
       </c>
       <c r="F794" t="inlineStr">
@@ -21083,7 +21083,7 @@
       </c>
       <c r="E795" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/prodigy-the-graphic-novel-legend-the-graphic-novel-2_207/index.html</t>
+          <t>https://books.toscrape.com/catalogue/prodigy-the-graphic-novel-legend-the-graphic-novel-2_207/index.html</t>
         </is>
       </c>
       <c r="F795" t="inlineStr">
@@ -21109,7 +21109,7 @@
       </c>
       <c r="E796" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/persepolis-the-story-of-a-childhood-persepolis-1-2_206/index.html</t>
+          <t>https://books.toscrape.com/catalogue/persepolis-the-story-of-a-childhood-persepolis-1-2_206/index.html</t>
         </is>
       </c>
       <c r="F796" t="inlineStr">
@@ -21135,7 +21135,7 @@
       </c>
       <c r="E797" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/packing-for-mars-the-curious-science-of-life-in-the-void_205/index.html</t>
+          <t>https://books.toscrape.com/catalogue/packing-for-mars-the-curious-science-of-life-in-the-void_205/index.html</t>
         </is>
       </c>
       <c r="F797" t="inlineStr">
@@ -21161,7 +21161,7 @@
       </c>
       <c r="E798" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/outliers-the-story-of-success_204/index.html</t>
+          <t>https://books.toscrape.com/catalogue/outliers-the-story-of-success_204/index.html</t>
         </is>
       </c>
       <c r="F798" t="inlineStr">
@@ -21187,7 +21187,7 @@
       </c>
       <c r="E799" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/original-fake_203/index.html</t>
+          <t>https://books.toscrape.com/catalogue/original-fake_203/index.html</t>
         </is>
       </c>
       <c r="F799" t="inlineStr">
@@ -21213,7 +21213,7 @@
       </c>
       <c r="E800" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/orange-is-the-new-black_202/index.html</t>
+          <t>https://books.toscrape.com/catalogue/orange-is-the-new-black_202/index.html</t>
         </is>
       </c>
       <c r="F800" t="inlineStr">
@@ -21239,7 +21239,7 @@
       </c>
       <c r="E801" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/one-for-the-money-stephanie-plum-1_201/index.html</t>
+          <t>https://books.toscrape.com/catalogue/one-for-the-money-stephanie-plum-1_201/index.html</t>
         </is>
       </c>
       <c r="F801" t="inlineStr">
@@ -21265,7 +21265,7 @@
       </c>
       <c r="E802" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/notes-from-a-small-island-notes-from-a-small-island-1_200/index.html</t>
+          <t>https://books.toscrape.com/catalogue/notes-from-a-small-island-notes-from-a-small-island-1_200/index.html</t>
         </is>
       </c>
       <c r="F802" t="inlineStr">
@@ -21291,7 +21291,7 @@
       </c>
       <c r="E803" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/night-the-night-trilogy-1_199/index.html</t>
+          <t>https://books.toscrape.com/catalogue/night-the-night-trilogy-1_199/index.html</t>
         </is>
       </c>
       <c r="F803" t="inlineStr">
@@ -21317,7 +21317,7 @@
       </c>
       <c r="E804" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/neither-here-nor-there-travels-in-europe_198/index.html</t>
+          <t>https://books.toscrape.com/catalogue/neither-here-nor-there-travels-in-europe_198/index.html</t>
         </is>
       </c>
       <c r="F804" t="inlineStr">
@@ -21343,7 +21343,7 @@
       </c>
       <c r="E805" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/naked_197/index.html</t>
+          <t>https://books.toscrape.com/catalogue/naked_197/index.html</t>
         </is>
       </c>
       <c r="F805" t="inlineStr">
@@ -21369,7 +21369,7 @@
       </c>
       <c r="E806" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/morning-star-red-rising-3_196/index.html</t>
+          <t>https://books.toscrape.com/catalogue/morning-star-red-rising-3_196/index.html</t>
         </is>
       </c>
       <c r="F806" t="inlineStr">
@@ -21395,7 +21395,7 @@
       </c>
       <c r="E807" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/miracles-from-heaven-a-little-girl-her-journey-to-heaven-and-her-amazing-story-of-healing_195/index.html</t>
+          <t>https://books.toscrape.com/catalogue/miracles-from-heaven-a-little-girl-her-journey-to-heaven-and-her-amazing-story-of-healing_195/index.html</t>
         </is>
       </c>
       <c r="F807" t="inlineStr">
@@ -21421,7 +21421,7 @@
       </c>
       <c r="E808" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/midnight-riot-peter-grant-rivers-of-london-books-1_194/index.html</t>
+          <t>https://books.toscrape.com/catalogue/midnight-riot-peter-grant-rivers-of-london-books-1_194/index.html</t>
         </is>
       </c>
       <c r="F808" t="inlineStr">
@@ -21447,7 +21447,7 @@
       </c>
       <c r="E809" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/me-talk-pretty-one-day_193/index.html</t>
+          <t>https://books.toscrape.com/catalogue/me-talk-pretty-one-day_193/index.html</t>
         </is>
       </c>
       <c r="F809" t="inlineStr">
@@ -21473,7 +21473,7 @@
       </c>
       <c r="E810" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/manuscript-found-in-accra_192/index.html</t>
+          <t>https://books.toscrape.com/catalogue/manuscript-found-in-accra_192/index.html</t>
         </is>
       </c>
       <c r="F810" t="inlineStr">
@@ -21499,7 +21499,7 @@
       </c>
       <c r="E811" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/lust-wonder_191/index.html</t>
+          <t>https://books.toscrape.com/catalogue/lust-wonder_191/index.html</t>
         </is>
       </c>
       <c r="F811" t="inlineStr">
@@ -21525,7 +21525,7 @@
       </c>
       <c r="E812" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/lila-gilead-3_190/index.html</t>
+          <t>https://books.toscrape.com/catalogue/lila-gilead-3_190/index.html</t>
         </is>
       </c>
       <c r="F812" t="inlineStr">
@@ -21551,7 +21551,7 @@
       </c>
       <c r="E813" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/life-the-universe-and-everything-hitchhikers-guide-to-the-galaxy-3_189/index.html</t>
+          <t>https://books.toscrape.com/catalogue/life-the-universe-and-everything-hitchhikers-guide-to-the-galaxy-3_189/index.html</t>
         </is>
       </c>
       <c r="F813" t="inlineStr">
@@ -21577,7 +21577,7 @@
       </c>
       <c r="E814" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/life-without-a-recipe_188/index.html</t>
+          <t>https://books.toscrape.com/catalogue/life-without-a-recipe_188/index.html</t>
         </is>
       </c>
       <c r="F814" t="inlineStr">
@@ -21603,7 +21603,7 @@
       </c>
       <c r="E815" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/life-after-life_187/index.html</t>
+          <t>https://books.toscrape.com/catalogue/life-after-life_187/index.html</t>
         </is>
       </c>
       <c r="F815" t="inlineStr">
@@ -21629,7 +21629,7 @@
       </c>
       <c r="E816" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/letter-to-a-christian-nation_186/index.html</t>
+          <t>https://books.toscrape.com/catalogue/letter-to-a-christian-nation_186/index.html</t>
         </is>
       </c>
       <c r="F816" t="inlineStr">
@@ -21655,7 +21655,7 @@
       </c>
       <c r="E817" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/lets-pretend-this-never-happened-a-mostly-true-memoir_185/index.html</t>
+          <t>https://books.toscrape.com/catalogue/lets-pretend-this-never-happened-a-mostly-true-memoir_185/index.html</t>
         </is>
       </c>
       <c r="F817" t="inlineStr">
@@ -21681,7 +21681,7 @@
       </c>
       <c r="E818" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/legend-legend-1_184/index.html</t>
+          <t>https://books.toscrape.com/catalogue/legend-legend-1_184/index.html</t>
         </is>
       </c>
       <c r="F818" t="inlineStr">
@@ -21707,7 +21707,7 @@
       </c>
       <c r="E819" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/lean-in-women-work-and-the-will-to-lead_183/index.html</t>
+          <t>https://books.toscrape.com/catalogue/lean-in-women-work-and-the-will-to-lead_183/index.html</t>
         </is>
       </c>
       <c r="F819" t="inlineStr">
@@ -21733,7 +21733,7 @@
       </c>
       <c r="E820" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/lamb-the-gospel-according-to-biff-christs-childhood-pal_182/index.html</t>
+          <t>https://books.toscrape.com/catalogue/lamb-the-gospel-according-to-biff-christs-childhood-pal_182/index.html</t>
         </is>
       </c>
       <c r="F820" t="inlineStr">
@@ -21759,7 +21759,7 @@
       </c>
       <c r="E821" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/lady-renegades-rebel-belle-3_181/index.html</t>
+          <t>https://books.toscrape.com/catalogue/lady-renegades-rebel-belle-3_181/index.html</t>
         </is>
       </c>
       <c r="F821" t="inlineStr">
@@ -21785,7 +21785,7 @@
       </c>
       <c r="E822" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/jurassic-park-jurassic-park-1_180/index.html</t>
+          <t>https://books.toscrape.com/catalogue/jurassic-park-jurassic-park-1_180/index.html</t>
         </is>
       </c>
       <c r="F822" t="inlineStr">
@@ -21811,7 +21811,7 @@
       </c>
       <c r="E823" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/its-never-too-late-to-begin-again-discovering-creativity-and-meaning-at-midlife-and-beyond_179/index.html</t>
+          <t>https://books.toscrape.com/catalogue/its-never-too-late-to-begin-again-discovering-creativity-and-meaning-at-midlife-and-beyond_179/index.html</t>
         </is>
       </c>
       <c r="F823" t="inlineStr">
@@ -21837,7 +21837,7 @@
       </c>
       <c r="E824" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/is-everyone-hanging-out-without-me-and-other-concerns_178/index.html</t>
+          <t>https://books.toscrape.com/catalogue/is-everyone-hanging-out-without-me-and-other-concerns_178/index.html</t>
         </is>
       </c>
       <c r="F824" t="inlineStr">
@@ -21863,7 +21863,7 @@
       </c>
       <c r="E825" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/into-the-wild_177/index.html</t>
+          <t>https://books.toscrape.com/catalogue/into-the-wild_177/index.html</t>
         </is>
       </c>
       <c r="F825" t="inlineStr">
@@ -21889,7 +21889,7 @@
       </c>
       <c r="E826" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/inferno-robert-langdon-4_176/index.html</t>
+          <t>https://books.toscrape.com/catalogue/inferno-robert-langdon-4_176/index.html</t>
         </is>
       </c>
       <c r="F826" t="inlineStr">
@@ -21915,7 +21915,7 @@
       </c>
       <c r="E827" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/in-the-garden-of-beasts-love-terror-and-an-american-family-in-hitlers-berlin_175/index.html</t>
+          <t>https://books.toscrape.com/catalogue/in-the-garden-of-beasts-love-terror-and-an-american-family-in-hitlers-berlin_175/index.html</t>
         </is>
       </c>
       <c r="F827" t="inlineStr">
@@ -21941,7 +21941,7 @@
       </c>
       <c r="E828" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/if-i-run-if-i-run-1_174/index.html</t>
+          <t>https://books.toscrape.com/catalogue/if-i-run-if-i-run-1_174/index.html</t>
         </is>
       </c>
       <c r="F828" t="inlineStr">
@@ -21967,7 +21967,7 @@
       </c>
       <c r="E829" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/ive-got-your-number_173/index.html</t>
+          <t>https://books.toscrape.com/catalogue/ive-got-your-number_173/index.html</t>
         </is>
       </c>
       <c r="F829" t="inlineStr">
@@ -21993,7 +21993,7 @@
       </c>
       <c r="E830" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/i-am-malala-the-girl-who-stood-up-for-education-and-was-shot-by-the-taliban_172/index.html</t>
+          <t>https://books.toscrape.com/catalogue/i-am-malala-the-girl-who-stood-up-for-education-and-was-shot-by-the-taliban_172/index.html</t>
         </is>
       </c>
       <c r="F830" t="inlineStr">
@@ -22019,7 +22019,7 @@
       </c>
       <c r="E831" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/hungry-girl-clean-hungry-easy-all-natural-recipes-for-healthy-eating-in-the-real-world_171/index.html</t>
+          <t>https://books.toscrape.com/catalogue/hungry-girl-clean-hungry-easy-all-natural-recipes-for-healthy-eating-in-the-real-world_171/index.html</t>
         </is>
       </c>
       <c r="F831" t="inlineStr">
@@ -22045,7 +22045,7 @@
       </c>
       <c r="E832" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/house-of-lost-worlds-dinosaurs-dynasties-and-the-story-of-life-on-earth_170/index.html</t>
+          <t>https://books.toscrape.com/catalogue/house-of-lost-worlds-dinosaurs-dynasties-and-the-story-of-life-on-earth_170/index.html</t>
         </is>
       </c>
       <c r="F832" t="inlineStr">
@@ -22071,7 +22071,7 @@
       </c>
       <c r="E833" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/house-of-leaves_169/index.html</t>
+          <t>https://books.toscrape.com/catalogue/house-of-leaves_169/index.html</t>
         </is>
       </c>
       <c r="F833" t="inlineStr">
@@ -22097,7 +22097,7 @@
       </c>
       <c r="E834" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/horrible-bear_168/index.html</t>
+          <t>https://books.toscrape.com/catalogue/horrible-bear_168/index.html</t>
         </is>
       </c>
       <c r="F834" t="inlineStr">
@@ -22123,7 +22123,7 @@
       </c>
       <c r="E835" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/holidays-on-ice_167/index.html</t>
+          <t>https://books.toscrape.com/catalogue/holidays-on-ice_167/index.html</t>
         </is>
       </c>
       <c r="F835" t="inlineStr">
@@ -22149,7 +22149,7 @@
       </c>
       <c r="E836" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/heir-to-the-sky_166/index.html</t>
+          <t>https://books.toscrape.com/catalogue/heir-to-the-sky_166/index.html</t>
         </is>
       </c>
       <c r="F836" t="inlineStr">
@@ -22175,7 +22175,7 @@
       </c>
       <c r="E837" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/green-eggs-and-ham-beginner-books-b-16_165/index.html</t>
+          <t>https://books.toscrape.com/catalogue/green-eggs-and-ham-beginner-books-b-16_165/index.html</t>
         </is>
       </c>
       <c r="F837" t="inlineStr">
@@ -22201,7 +22201,7 @@
       </c>
       <c r="E838" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/grayson-vol-3-nemesis-grayson-3_164/index.html</t>
+          <t>https://books.toscrape.com/catalogue/grayson-vol-3-nemesis-grayson-3_164/index.html</t>
         </is>
       </c>
       <c r="F838" t="inlineStr">
@@ -22227,7 +22227,7 @@
       </c>
       <c r="E839" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/gratitude_163/index.html</t>
+          <t>https://books.toscrape.com/catalogue/gratitude_163/index.html</t>
         </is>
       </c>
       <c r="F839" t="inlineStr">
@@ -22253,7 +22253,7 @@
       </c>
       <c r="E840" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/gone-girl_162/index.html</t>
+          <t>https://books.toscrape.com/catalogue/gone-girl_162/index.html</t>
         </is>
       </c>
       <c r="F840" t="inlineStr">
@@ -22279,7 +22279,7 @@
       </c>
       <c r="E841" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/golden-heart-of-dread-3_161/index.html</t>
+          <t>https://books.toscrape.com/catalogue/golden-heart-of-dread-3_161/index.html</t>
         </is>
       </c>
       <c r="F841" t="inlineStr">
@@ -22305,7 +22305,7 @@
       </c>
       <c r="E842" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/girl-in-the-blue-coat_160/index.html</t>
+          <t>https://books.toscrape.com/catalogue/girl-in-the-blue-coat_160/index.html</t>
         </is>
       </c>
       <c r="F842" t="inlineStr">
@@ -22331,7 +22331,7 @@
       </c>
       <c r="E843" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/fruits-basket-vol-3-fruits-basket-3_159/index.html</t>
+          <t>https://books.toscrape.com/catalogue/fruits-basket-vol-3-fruits-basket-3_159/index.html</t>
         </is>
       </c>
       <c r="F843" t="inlineStr">
@@ -22357,7 +22357,7 @@
       </c>
       <c r="E844" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/friday-night-lights-a-town-a-team-and-a-dream_158/index.html</t>
+          <t>https://books.toscrape.com/catalogue/friday-night-lights-a-town-a-team-and-a-dream_158/index.html</t>
         </is>
       </c>
       <c r="F844" t="inlineStr">
@@ -22383,7 +22383,7 @@
       </c>
       <c r="E845" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/fire-bound-sea-havensisters-of-the-heart-5_157/index.html</t>
+          <t>https://books.toscrape.com/catalogue/fire-bound-sea-havensisters-of-the-heart-5_157/index.html</t>
         </is>
       </c>
       <c r="F845" t="inlineStr">
@@ -22409,7 +22409,7 @@
       </c>
       <c r="E846" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/fifty-shades-freed-fifty-shades-3_156/index.html</t>
+          <t>https://books.toscrape.com/catalogue/fifty-shades-freed-fifty-shades-3_156/index.html</t>
         </is>
       </c>
       <c r="F846" t="inlineStr">
@@ -22435,7 +22435,7 @@
       </c>
       <c r="E847" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/fellside_155/index.html</t>
+          <t>https://books.toscrape.com/catalogue/fellside_155/index.html</t>
         </is>
       </c>
       <c r="F847" t="inlineStr">
@@ -22461,7 +22461,7 @@
       </c>
       <c r="E848" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/extreme-prey-lucas-davenport-26_154/index.html</t>
+          <t>https://books.toscrape.com/catalogue/extreme-prey-lucas-davenport-26_154/index.html</t>
         </is>
       </c>
       <c r="F848" t="inlineStr">
@@ -22487,7 +22487,7 @@
       </c>
       <c r="E849" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/eragon-the-inheritance-cycle-1_153/index.html</t>
+          <t>https://books.toscrape.com/catalogue/eragon-the-inheritance-cycle-1_153/index.html</t>
         </is>
       </c>
       <c r="F849" t="inlineStr">
@@ -22513,7 +22513,7 @@
       </c>
       <c r="E850" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/eclipse-twilight-3_152/index.html</t>
+          <t>https://books.toscrape.com/catalogue/eclipse-twilight-3_152/index.html</t>
         </is>
       </c>
       <c r="F850" t="inlineStr">
@@ -22539,7 +22539,7 @@
       </c>
       <c r="E851" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/dune-dune-1_151/index.html</t>
+          <t>https://books.toscrape.com/catalogue/dune-dune-1_151/index.html</t>
         </is>
       </c>
       <c r="F851" t="inlineStr">
@@ -22565,7 +22565,7 @@
       </c>
       <c r="E852" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/dracula_150/index.html</t>
+          <t>https://books.toscrape.com/catalogue/dracula_150/index.html</t>
         </is>
       </c>
       <c r="F852" t="inlineStr">
@@ -22591,7 +22591,7 @@
       </c>
       <c r="E853" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/do-androids-dream-of-electric-sheep-blade-runner-1_149/index.html</t>
+          <t>https://books.toscrape.com/catalogue/do-androids-dream-of-electric-sheep-blade-runner-1_149/index.html</t>
         </is>
       </c>
       <c r="F853" t="inlineStr">
@@ -22617,7 +22617,7 @@
       </c>
       <c r="E854" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/disrupted-my-misadventure-in-the-start-up-bubble_148/index.html</t>
+          <t>https://books.toscrape.com/catalogue/disrupted-my-misadventure-in-the-start-up-bubble_148/index.html</t>
         </is>
       </c>
       <c r="F854" t="inlineStr">
@@ -22643,7 +22643,7 @@
       </c>
       <c r="E855" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/dead-wake-the-last-crossing-of-the-lusitania_147/index.html</t>
+          <t>https://books.toscrape.com/catalogue/dead-wake-the-last-crossing-of-the-lusitania_147/index.html</t>
         </is>
       </c>
       <c r="F855" t="inlineStr">
@@ -22669,7 +22669,7 @@
       </c>
       <c r="E856" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/david-and-goliath-underdogs-misfits-and-the-art-of-battling-giants_146/index.html</t>
+          <t>https://books.toscrape.com/catalogue/david-and-goliath-underdogs-misfits-and-the-art-of-battling-giants_146/index.html</t>
         </is>
       </c>
       <c r="F856" t="inlineStr">
@@ -22695,7 +22695,7 @@
       </c>
       <c r="E857" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/darkfever-fever-1_145/index.html</t>
+          <t>https://books.toscrape.com/catalogue/darkfever-fever-1_145/index.html</t>
         </is>
       </c>
       <c r="F857" t="inlineStr">
@@ -22721,7 +22721,7 @@
       </c>
       <c r="E858" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/dark-places_144/index.html</t>
+          <t>https://books.toscrape.com/catalogue/dark-places_144/index.html</t>
         </is>
       </c>
       <c r="F858" t="inlineStr">
@@ -22747,7 +22747,7 @@
       </c>
       <c r="E859" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/crazy-rich-asians-crazy-rich-asians-1_143/index.html</t>
+          <t>https://books.toscrape.com/catalogue/crazy-rich-asians-crazy-rich-asians-1_143/index.html</t>
         </is>
       </c>
       <c r="F859" t="inlineStr">
@@ -22773,7 +22773,7 @@
       </c>
       <c r="E860" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/counting-thyme_142/index.html</t>
+          <t>https://books.toscrape.com/catalogue/counting-thyme_142/index.html</t>
         </is>
       </c>
       <c r="F860" t="inlineStr">
@@ -22799,7 +22799,7 @@
       </c>
       <c r="E861" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/cosmos_141/index.html</t>
+          <t>https://books.toscrape.com/catalogue/cosmos_141/index.html</t>
         </is>
       </c>
       <c r="F861" t="inlineStr">
@@ -22825,7 +22825,7 @@
       </c>
       <c r="E862" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/civilization-and-its-discontents_140/index.html</t>
+          <t>https://books.toscrape.com/catalogue/civilization-and-its-discontents_140/index.html</t>
         </is>
       </c>
       <c r="F862" t="inlineStr">
@@ -22851,7 +22851,7 @@
       </c>
       <c r="E863" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/cinder-the-lunar-chronicles-1_139/index.html</t>
+          <t>https://books.toscrape.com/catalogue/cinder-the-lunar-chronicles-1_139/index.html</t>
         </is>
       </c>
       <c r="F863" t="inlineStr">
@@ -22877,7 +22877,7 @@
       </c>
       <c r="E864" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/catastrophic-happiness-finding-joy-in-childhoods-messy-years_138/index.html</t>
+          <t>https://books.toscrape.com/catalogue/catastrophic-happiness-finding-joy-in-childhoods-messy-years_138/index.html</t>
         </is>
       </c>
       <c r="F864" t="inlineStr">
@@ -22903,7 +22903,7 @@
       </c>
       <c r="E865" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/career-of-evil-cormoran-strike-3_137/index.html</t>
+          <t>https://books.toscrape.com/catalogue/career-of-evil-cormoran-strike-3_137/index.html</t>
         </is>
       </c>
       <c r="F865" t="inlineStr">
@@ -22929,7 +22929,7 @@
       </c>
       <c r="E866" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/breaking-dawn-twilight-4_136/index.html</t>
+          <t>https://books.toscrape.com/catalogue/breaking-dawn-twilight-4_136/index.html</t>
         </is>
       </c>
       <c r="F866" t="inlineStr">
@@ -22955,7 +22955,7 @@
       </c>
       <c r="E867" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/brave-enough_135/index.html</t>
+          <t>https://books.toscrape.com/catalogue/brave-enough_135/index.html</t>
         </is>
       </c>
       <c r="F867" t="inlineStr">
@@ -22981,7 +22981,7 @@
       </c>
       <c r="E868" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/boy-meets-boy_134/index.html</t>
+          <t>https://books.toscrape.com/catalogue/boy-meets-boy_134/index.html</t>
         </is>
       </c>
       <c r="F868" t="inlineStr">
@@ -23007,7 +23007,7 @@
       </c>
       <c r="E869" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/born-to-run-a-hidden-tribe-superathletes-and-the-greatest-race-the-world-has-never-seen_133/index.html</t>
+          <t>https://books.toscrape.com/catalogue/born-to-run-a-hidden-tribe-superathletes-and-the-greatest-race-the-world-has-never-seen_133/index.html</t>
         </is>
       </c>
       <c r="F869" t="inlineStr">
@@ -23033,7 +23033,7 @@
       </c>
       <c r="E870" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/blink-the-power-of-thinking-without-thinking_132/index.html</t>
+          <t>https://books.toscrape.com/catalogue/blink-the-power-of-thinking-without-thinking_132/index.html</t>
         </is>
       </c>
       <c r="F870" t="inlineStr">
@@ -23059,7 +23059,7 @@
       </c>
       <c r="E871" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/black-flags-the-rise-of-isis_131/index.html</t>
+          <t>https://books.toscrape.com/catalogue/black-flags-the-rise-of-isis_131/index.html</t>
         </is>
       </c>
       <c r="F871" t="inlineStr">
@@ -23085,7 +23085,7 @@
       </c>
       <c r="E872" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/black-butler-vol-1-black-butler-1_130/index.html</t>
+          <t>https://books.toscrape.com/catalogue/black-butler-vol-1-black-butler-1_130/index.html</t>
         </is>
       </c>
       <c r="F872" t="inlineStr">
@@ -23111,7 +23111,7 @@
       </c>
       <c r="E873" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/big-little-lies_129/index.html</t>
+          <t>https://books.toscrape.com/catalogue/big-little-lies_129/index.html</t>
         </is>
       </c>
       <c r="F873" t="inlineStr">
@@ -23137,7 +23137,7 @@
       </c>
       <c r="E874" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/between-shades-of-gray_128/index.html</t>
+          <t>https://books.toscrape.com/catalogue/between-shades-of-gray_128/index.html</t>
         </is>
       </c>
       <c r="F874" t="inlineStr">
@@ -23163,7 +23163,7 @@
       </c>
       <c r="E875" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/best-of-my-love-fools-gold-20_127/index.html</t>
+          <t>https://books.toscrape.com/catalogue/best-of-my-love-fools-gold-20_127/index.html</t>
         </is>
       </c>
       <c r="F875" t="inlineStr">
@@ -23189,7 +23189,7 @@
       </c>
       <c r="E876" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/beowulf_126/index.html</t>
+          <t>https://books.toscrape.com/catalogue/beowulf_126/index.html</t>
         </is>
       </c>
       <c r="F876" t="inlineStr">
@@ -23215,7 +23215,7 @@
       </c>
       <c r="E877" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/beautiful-creatures-caster-chronicles-1_125/index.html</t>
+          <t>https://books.toscrape.com/catalogue/beautiful-creatures-caster-chronicles-1_125/index.html</t>
         </is>
       </c>
       <c r="F877" t="inlineStr">
@@ -23241,7 +23241,7 @@
       </c>
       <c r="E878" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/awkward_124/index.html</t>
+          <t>https://books.toscrape.com/catalogue/awkward_124/index.html</t>
         </is>
       </c>
       <c r="F878" t="inlineStr">
@@ -23267,7 +23267,7 @@
       </c>
       <c r="E879" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/ash_123/index.html</t>
+          <t>https://books.toscrape.com/catalogue/ash_123/index.html</t>
         </is>
       </c>
       <c r="F879" t="inlineStr">
@@ -23293,7 +23293,7 @@
       </c>
       <c r="E880" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/are-we-there-yet_122/index.html</t>
+          <t>https://books.toscrape.com/catalogue/are-we-there-yet_122/index.html</t>
         </is>
       </c>
       <c r="F880" t="inlineStr">
@@ -23319,7 +23319,7 @@
       </c>
       <c r="E881" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/are-we-smart-enough-to-know-how-smart-animals-are_121/index.html</t>
+          <t>https://books.toscrape.com/catalogue/are-we-smart-enough-to-know-how-smart-animals-are_121/index.html</t>
         </is>
       </c>
       <c r="F881" t="inlineStr">
@@ -23345,7 +23345,7 @@
       </c>
       <c r="E882" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/annie-on-my-mind_120/index.html</t>
+          <t>https://books.toscrape.com/catalogue/annie-on-my-mind_120/index.html</t>
         </is>
       </c>
       <c r="F882" t="inlineStr">
@@ -23371,7 +23371,7 @@
       </c>
       <c r="E883" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/and-then-there-were-none_119/index.html</t>
+          <t>https://books.toscrape.com/catalogue/and-then-there-were-none_119/index.html</t>
         </is>
       </c>
       <c r="F883" t="inlineStr">
@@ -23397,7 +23397,7 @@
       </c>
       <c r="E884" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/a-walk-in-the-woods-rediscovering-america-on-the-appalachian-trail_118/index.html</t>
+          <t>https://books.toscrape.com/catalogue/a-walk-in-the-woods-rediscovering-america-on-the-appalachian-trail_118/index.html</t>
         </is>
       </c>
       <c r="F884" t="inlineStr">
@@ -23423,7 +23423,7 @@
       </c>
       <c r="E885" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/a-visit-from-the-goon-squad_117/index.html</t>
+          <t>https://books.toscrape.com/catalogue/a-visit-from-the-goon-squad_117/index.html</t>
         </is>
       </c>
       <c r="F885" t="inlineStr">
@@ -23449,7 +23449,7 @@
       </c>
       <c r="E886" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/a-storm-of-swords-a-song-of-ice-and-fire-3_116/index.html</t>
+          <t>https://books.toscrape.com/catalogue/a-storm-of-swords-a-song-of-ice-and-fire-3_116/index.html</t>
         </is>
       </c>
       <c r="F886" t="inlineStr">
@@ -23475,7 +23475,7 @@
       </c>
       <c r="E887" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/a-heartbreaking-work-of-staggering-genius_115/index.html</t>
+          <t>https://books.toscrape.com/catalogue/a-heartbreaking-work-of-staggering-genius_115/index.html</t>
         </is>
       </c>
       <c r="F887" t="inlineStr">
@@ -23501,7 +23501,7 @@
       </c>
       <c r="E888" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/8-keys-to-mental-health-through-exercise_114/index.html</t>
+          <t>https://books.toscrape.com/catalogue/8-keys-to-mental-health-through-exercise_114/index.html</t>
         </is>
       </c>
       <c r="F888" t="inlineStr">
@@ -23527,7 +23527,7 @@
       </c>
       <c r="E889" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/girlboss_113/index.html</t>
+          <t>https://books.toscrape.com/catalogue/girlboss_113/index.html</t>
         </is>
       </c>
       <c r="F889" t="inlineStr">
@@ -23553,7 +23553,7 @@
       </c>
       <c r="E890" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-suffragettes-little-black-classics-96_112/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-suffragettes-little-black-classics-96_112/index.html</t>
         </is>
       </c>
       <c r="F890" t="inlineStr">
@@ -23579,7 +23579,7 @@
       </c>
       <c r="E891" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-sense-of-an-ending_111/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-sense-of-an-ending_111/index.html</t>
         </is>
       </c>
       <c r="F891" t="inlineStr">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="E892" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-sandman-vol-2-the-dolls-house-the-sandman-volumes-2_110/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-sandman-vol-2-the-dolls-house-the-sandman-volumes-2_110/index.html</t>
         </is>
       </c>
       <c r="F892" t="inlineStr">
@@ -23631,7 +23631,7 @@
       </c>
       <c r="E893" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-course-of-love_109/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-course-of-love_109/index.html</t>
         </is>
       </c>
       <c r="F893" t="inlineStr">
@@ -23657,7 +23657,7 @@
       </c>
       <c r="E894" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/sugar-rush-offensive-line-2_108/index.html</t>
+          <t>https://books.toscrape.com/catalogue/sugar-rush-offensive-line-2_108/index.html</t>
         </is>
       </c>
       <c r="F894" t="inlineStr">
@@ -23683,7 +23683,7 @@
       </c>
       <c r="E895" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/saga-volume-2-saga-collected-editions-2_107/index.html</t>
+          <t>https://books.toscrape.com/catalogue/saga-volume-2-saga-collected-editions-2_107/index.html</t>
         </is>
       </c>
       <c r="F895" t="inlineStr">
@@ -23709,7 +23709,7 @@
       </c>
       <c r="E896" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/run-spot-run-the-ethics-of-keeping-pets_106/index.html</t>
+          <t>https://books.toscrape.com/catalogue/run-spot-run-the-ethics-of-keeping-pets_106/index.html</t>
         </is>
       </c>
       <c r="F896" t="inlineStr">
@@ -23735,7 +23735,7 @@
       </c>
       <c r="E897" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/new-moon-twilight-2_105/index.html</t>
+          <t>https://books.toscrape.com/catalogue/new-moon-twilight-2_105/index.html</t>
         </is>
       </c>
       <c r="F897" t="inlineStr">
@@ -23761,7 +23761,7 @@
       </c>
       <c r="E898" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/life_104/index.html</t>
+          <t>https://books.toscrape.com/catalogue/life_104/index.html</t>
         </is>
       </c>
       <c r="F898" t="inlineStr">
@@ -23787,7 +23787,7 @@
       </c>
       <c r="E899" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/kindle-paperwhite-users-guide_103/index.html</t>
+          <t>https://books.toscrape.com/catalogue/kindle-paperwhite-users-guide_103/index.html</t>
         </is>
       </c>
       <c r="F899" t="inlineStr">
@@ -23813,7 +23813,7 @@
       </c>
       <c r="E900" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/h-is-for-hawk_102/index.html</t>
+          <t>https://books.toscrape.com/catalogue/h-is-for-hawk_102/index.html</t>
         </is>
       </c>
       <c r="F900" t="inlineStr">
@@ -23839,7 +23839,7 @@
       </c>
       <c r="E901" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/girl-online-on-tour-girl-online-2_101/index.html</t>
+          <t>https://books.toscrape.com/catalogue/girl-online-on-tour-girl-online-2_101/index.html</t>
         </is>
       </c>
       <c r="F901" t="inlineStr">
@@ -23865,7 +23865,7 @@
       </c>
       <c r="E902" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/fruits-basket-vol-2-fruits-basket-2_100/index.html</t>
+          <t>https://books.toscrape.com/catalogue/fruits-basket-vol-2-fruits-basket-2_100/index.html</t>
         </is>
       </c>
       <c r="F902" t="inlineStr">
@@ -23891,7 +23891,7 @@
       </c>
       <c r="E903" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/diary-of-a-minecraft-zombie-book-1-a-scare-of-a-dare-an-unofficial-minecraft-book_99/index.html</t>
+          <t>https://books.toscrape.com/catalogue/diary-of-a-minecraft-zombie-book-1-a-scare-of-a-dare-an-unofficial-minecraft-book_99/index.html</t>
         </is>
       </c>
       <c r="F903" t="inlineStr">
@@ -23917,7 +23917,7 @@
       </c>
       <c r="E904" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/y-the-last-man-vol-1-unmanned-y-the-last-man-1_98/index.html</t>
+          <t>https://books.toscrape.com/catalogue/y-the-last-man-vol-1-unmanned-y-the-last-man-1_98/index.html</t>
         </is>
       </c>
       <c r="F904" t="inlineStr">
@@ -23943,7 +23943,7 @@
       </c>
       <c r="E905" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/while-you-were-mine_97/index.html</t>
+          <t>https://books.toscrape.com/catalogue/while-you-were-mine_97/index.html</t>
         </is>
       </c>
       <c r="F905" t="inlineStr">
@@ -23969,7 +23969,7 @@
       </c>
       <c r="E906" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/where-lightning-strikes-bleeding-stars-3_96/index.html</t>
+          <t>https://books.toscrape.com/catalogue/where-lightning-strikes-bleeding-stars-3_96/index.html</t>
         </is>
       </c>
       <c r="F906" t="inlineStr">
@@ -23995,7 +23995,7 @@
       </c>
       <c r="E907" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/when-im-gone_95/index.html</t>
+          <t>https://books.toscrape.com/catalogue/when-im-gone_95/index.html</t>
         </is>
       </c>
       <c r="F907" t="inlineStr">
@@ -24021,7 +24021,7 @@
       </c>
       <c r="E908" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/ways-of-seeing_94/index.html</t>
+          <t>https://books.toscrape.com/catalogue/ways-of-seeing_94/index.html</t>
         </is>
       </c>
       <c r="F908" t="inlineStr">
@@ -24047,7 +24047,7 @@
       </c>
       <c r="E909" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/vampire-knight-vol-1-vampire-knight-1_93/index.html</t>
+          <t>https://books.toscrape.com/catalogue/vampire-knight-vol-1-vampire-knight-1_93/index.html</t>
         </is>
       </c>
       <c r="F909" t="inlineStr">
@@ -24073,7 +24073,7 @@
       </c>
       <c r="E910" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/vampire-girl-vampire-girl-1_92/index.html</t>
+          <t>https://books.toscrape.com/catalogue/vampire-girl-vampire-girl-1_92/index.html</t>
         </is>
       </c>
       <c r="F910" t="inlineStr">
@@ -24099,7 +24099,7 @@
       </c>
       <c r="E911" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/twenty-love-poems-and-a-song-of-despair_91/index.html</t>
+          <t>https://books.toscrape.com/catalogue/twenty-love-poems-and-a-song-of-despair_91/index.html</t>
         </is>
       </c>
       <c r="F911" t="inlineStr">
@@ -24125,7 +24125,7 @@
       </c>
       <c r="E912" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/travels-with-charley-in-search-of-america_90/index.html</t>
+          <t>https://books.toscrape.com/catalogue/travels-with-charley-in-search-of-america_90/index.html</t>
         </is>
       </c>
       <c r="F912" t="inlineStr">
@@ -24151,7 +24151,7 @@
       </c>
       <c r="E913" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/three-wishes-river-of-time-california-1_89/index.html</t>
+          <t>https://books.toscrape.com/catalogue/three-wishes-river-of-time-california-1_89/index.html</t>
         </is>
       </c>
       <c r="F913" t="inlineStr">
@@ -24177,7 +24177,7 @@
       </c>
       <c r="E914" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/this-one-moment-pushing-limits-1_88/index.html</t>
+          <t>https://books.toscrape.com/catalogue/this-one-moment-pushing-limits-1_88/index.html</t>
         </is>
       </c>
       <c r="F914" t="inlineStr">
@@ -24203,7 +24203,7 @@
       </c>
       <c r="E915" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-zombie-room_87/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-zombie-room_87/index.html</t>
         </is>
       </c>
       <c r="F915" t="inlineStr">
@@ -24229,7 +24229,7 @@
       </c>
       <c r="E916" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-wicked-the-divine-vol-1-the-faust-act-the-wicked-the-divine_86/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-wicked-the-divine-vol-1-the-faust-act-the-wicked-the-divine_86/index.html</t>
         </is>
       </c>
       <c r="F916" t="inlineStr">
@@ -24255,7 +24255,7 @@
       </c>
       <c r="E917" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-tumor_85/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-tumor_85/index.html</t>
         </is>
       </c>
       <c r="F917" t="inlineStr">
@@ -24281,7 +24281,7 @@
       </c>
       <c r="E918" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-story-of-hong-gildong_84/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-story-of-hong-gildong_84/index.html</t>
         </is>
       </c>
       <c r="F918" t="inlineStr">
@@ -24307,7 +24307,7 @@
       </c>
       <c r="E919" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-silent-wife_83/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-silent-wife_83/index.html</t>
         </is>
       </c>
       <c r="F919" t="inlineStr">
@@ -24333,7 +24333,7 @@
       </c>
       <c r="E920" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-silent-twin-detective-jennifer-knight-3_82/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-silent-twin-detective-jennifer-knight-3_82/index.html</t>
         </is>
       </c>
       <c r="F920" t="inlineStr">
@@ -24359,7 +24359,7 @@
       </c>
       <c r="E921" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-selfish-gene_81/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-selfish-gene_81/index.html</t>
         </is>
       </c>
       <c r="F921" t="inlineStr">
@@ -24385,7 +24385,7 @@
       </c>
       <c r="E922" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-secret-healer_80/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-secret-healer_80/index.html</t>
         </is>
       </c>
       <c r="F922" t="inlineStr">
@@ -24411,7 +24411,7 @@
       </c>
       <c r="E923" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-sandman-vol-1-preludes-and-nocturnes-the-sandman-volumes-1_79/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-sandman-vol-1-preludes-and-nocturnes-the-sandman-volumes-1_79/index.html</t>
         </is>
       </c>
       <c r="F923" t="inlineStr">
@@ -24437,7 +24437,7 @@
       </c>
       <c r="E924" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-republic_78/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-republic_78/index.html</t>
         </is>
       </c>
       <c r="F924" t="inlineStr">
@@ -24463,7 +24463,7 @@
       </c>
       <c r="E925" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-odyssey_77/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-odyssey_77/index.html</t>
         </is>
       </c>
       <c r="F925" t="inlineStr">
@@ -24489,7 +24489,7 @@
       </c>
       <c r="E926" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-no-1-ladies-detective-agency-no-1-ladies-detective-agency-1_76/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-no-1-ladies-detective-agency-no-1-ladies-detective-agency-1_76/index.html</t>
         </is>
       </c>
       <c r="F926" t="inlineStr">
@@ -24515,7 +24515,7 @@
       </c>
       <c r="E927" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-nicomachean-ethics_75/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-nicomachean-ethics_75/index.html</t>
         </is>
       </c>
       <c r="F927" t="inlineStr">
@@ -24541,7 +24541,7 @@
       </c>
       <c r="E928" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-name-of-the-wind-the-kingkiller-chronicle-1_74/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-name-of-the-wind-the-kingkiller-chronicle-1_74/index.html</t>
         </is>
       </c>
       <c r="F928" t="inlineStr">
@@ -24567,7 +24567,7 @@
       </c>
       <c r="E929" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-mirror-the-maze-the-wrath-and-the-dawn-15_73/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-mirror-the-maze-the-wrath-and-the-dawn-15_73/index.html</t>
         </is>
       </c>
       <c r="F929" t="inlineStr">
@@ -24593,7 +24593,7 @@
       </c>
       <c r="E930" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-little-prince_72/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-little-prince_72/index.html</t>
         </is>
       </c>
       <c r="F930" t="inlineStr">
@@ -24619,7 +24619,7 @@
       </c>
       <c r="E931" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-light-of-the-fireflies_71/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-light-of-the-fireflies_71/index.html</t>
         </is>
       </c>
       <c r="F931" t="inlineStr">
@@ -24645,7 +24645,7 @@
       </c>
       <c r="E932" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-last-girl-the-dominion-trilogy-1_70/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-last-girl-the-dominion-trilogy-1_70/index.html</t>
         </is>
       </c>
       <c r="F932" t="inlineStr">
@@ -24671,7 +24671,7 @@
       </c>
       <c r="E933" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-iliad_69/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-iliad_69/index.html</t>
         </is>
       </c>
       <c r="F933" t="inlineStr">
@@ -24697,7 +24697,7 @@
       </c>
       <c r="E934" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-hook-up-game-on-1_68/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-hook-up-game-on-1_68/index.html</t>
         </is>
       </c>
       <c r="F934" t="inlineStr">
@@ -24723,7 +24723,7 @@
       </c>
       <c r="E935" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-haters_67/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-haters_67/index.html</t>
         </is>
       </c>
       <c r="F935" t="inlineStr">
@@ -24749,7 +24749,7 @@
       </c>
       <c r="E936" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-girl-you-lost_66/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-girl-you-lost_66/index.html</t>
         </is>
       </c>
       <c r="F936" t="inlineStr">
@@ -24775,7 +24775,7 @@
       </c>
       <c r="E937" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-girl-in-the-ice-dci-erika-foster-1_65/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-girl-in-the-ice-dci-erika-foster-1_65/index.html</t>
         </is>
       </c>
       <c r="F937" t="inlineStr">
@@ -24801,7 +24801,7 @@
       </c>
       <c r="E938" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-end-of-the-jesus-era-an-investigation-1_64/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-end-of-the-jesus-era-an-investigation-1_64/index.html</t>
         </is>
       </c>
       <c r="F938" t="inlineStr">
@@ -24827,7 +24827,7 @@
       </c>
       <c r="E939" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-edge-of-reason-bridget-jones-2_63/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-edge-of-reason-bridget-jones-2_63/index.html</t>
         </is>
       </c>
       <c r="F939" t="inlineStr">
@@ -24853,7 +24853,7 @@
       </c>
       <c r="E940" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-complete-maus-maus-1-2_62/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-complete-maus-maus-1-2_62/index.html</t>
         </is>
       </c>
       <c r="F940" t="inlineStr">
@@ -24879,7 +24879,7 @@
       </c>
       <c r="E941" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-communist-manifesto_61/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-communist-manifesto_61/index.html</t>
         </is>
       </c>
       <c r="F941" t="inlineStr">
@@ -24905,7 +24905,7 @@
       </c>
       <c r="E942" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-bhagavad-gita_60/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-bhagavad-gita_60/index.html</t>
         </is>
       </c>
       <c r="F942" t="inlineStr">
@@ -24931,7 +24931,7 @@
       </c>
       <c r="E943" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-bette-davis-club_59/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-bette-davis-club_59/index.html</t>
         </is>
       </c>
       <c r="F943" t="inlineStr">
@@ -24957,7 +24957,7 @@
       </c>
       <c r="E944" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/the-art-of-not-breathing_58/index.html</t>
+          <t>https://books.toscrape.com/catalogue/the-art-of-not-breathing_58/index.html</t>
         </is>
       </c>
       <c r="F944" t="inlineStr">
@@ -24983,7 +24983,7 @@
       </c>
       <c r="E945" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/taking-shots-assassins-1_57/index.html</t>
+          <t>https://books.toscrape.com/catalogue/taking-shots-assassins-1_57/index.html</t>
         </is>
       </c>
       <c r="F945" t="inlineStr">
@@ -25009,7 +25009,7 @@
       </c>
       <c r="E946" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/starlark_56/index.html</t>
+          <t>https://books.toscrape.com/catalogue/starlark_56/index.html</t>
         </is>
       </c>
       <c r="F946" t="inlineStr">
@@ -25035,7 +25035,7 @@
       </c>
       <c r="E947" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/skip-beat-vol-01-skip-beat-1_55/index.html</t>
+          <t>https://books.toscrape.com/catalogue/skip-beat-vol-01-skip-beat-1_55/index.html</t>
         </is>
       </c>
       <c r="F947" t="inlineStr">
@@ -25061,7 +25061,7 @@
       </c>
       <c r="E948" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/sister-sable-the-mad-queen-1_54/index.html</t>
+          <t>https://books.toscrape.com/catalogue/sister-sable-the-mad-queen-1_54/index.html</t>
         </is>
       </c>
       <c r="F948" t="inlineStr">
@@ -25087,7 +25087,7 @@
       </c>
       <c r="E949" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/shatter-me-shatter-me-1_53/index.html</t>
+          <t>https://books.toscrape.com/catalogue/shatter-me-shatter-me-1_53/index.html</t>
         </is>
       </c>
       <c r="F949" t="inlineStr">
@@ -25113,7 +25113,7 @@
       </c>
       <c r="E950" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/shameless_52/index.html</t>
+          <t>https://books.toscrape.com/catalogue/shameless_52/index.html</t>
         </is>
       </c>
       <c r="F950" t="inlineStr">
@@ -25139,7 +25139,7 @@
       </c>
       <c r="E951" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/shadow-rites-jane-yellowrock-10_51/index.html</t>
+          <t>https://books.toscrape.com/catalogue/shadow-rites-jane-yellowrock-10_51/index.html</t>
         </is>
       </c>
       <c r="F951" t="inlineStr">
@@ -25165,7 +25165,7 @@
       </c>
       <c r="E952" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/settling-the-score-the-summer-games-1_50/index.html</t>
+          <t>https://books.toscrape.com/catalogue/settling-the-score-the-summer-games-1_50/index.html</t>
         </is>
       </c>
       <c r="F952" t="inlineStr">
@@ -25191,7 +25191,7 @@
       </c>
       <c r="E953" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/sense-and-sensibility_49/index.html</t>
+          <t>https://books.toscrape.com/catalogue/sense-and-sensibility_49/index.html</t>
         </is>
       </c>
       <c r="F953" t="inlineStr">
@@ -25217,7 +25217,7 @@
       </c>
       <c r="E954" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/saga-volume-1-saga-collected-editions-1_48/index.html</t>
+          <t>https://books.toscrape.com/catalogue/saga-volume-1-saga-collected-editions-1_48/index.html</t>
         </is>
       </c>
       <c r="F954" t="inlineStr">
@@ -25243,7 +25243,7 @@
       </c>
       <c r="E955" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/rhythm-chord-malykhin_47/index.html</t>
+          <t>https://books.toscrape.com/catalogue/rhythm-chord-malykhin_47/index.html</t>
         </is>
       </c>
       <c r="F955" t="inlineStr">
@@ -25269,7 +25269,7 @@
       </c>
       <c r="E956" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/rat-queens-vol-1-sass-sorcery-rat-queens-collected-editions-1-5_46/index.html</t>
+          <t>https://books.toscrape.com/catalogue/rat-queens-vol-1-sass-sorcery-rat-queens-collected-editions-1-5_46/index.html</t>
         </is>
       </c>
       <c r="F956" t="inlineStr">
@@ -25295,7 +25295,7 @@
       </c>
       <c r="E957" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/paradise-lost-paradise-1_45/index.html</t>
+          <t>https://books.toscrape.com/catalogue/paradise-lost-paradise-1_45/index.html</t>
         </is>
       </c>
       <c r="F957" t="inlineStr">
@@ -25321,7 +25321,7 @@
       </c>
       <c r="E958" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/paper-girls-vol-1-paper-girls-1-5_44/index.html</t>
+          <t>https://books.toscrape.com/catalogue/paper-girls-vol-1-paper-girls-1-5_44/index.html</t>
         </is>
       </c>
       <c r="F958" t="inlineStr">
@@ -25347,7 +25347,7 @@
       </c>
       <c r="E959" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/ouran-high-school-host-club-vol-1-ouran-high-school-host-club-1_43/index.html</t>
+          <t>https://books.toscrape.com/catalogue/ouran-high-school-host-club-vol-1-ouran-high-school-host-club-1_43/index.html</t>
         </is>
       </c>
       <c r="F959" t="inlineStr">
@@ -25373,7 +25373,7 @@
       </c>
       <c r="E960" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/origins-alphas-05_42/index.html</t>
+          <t>https://books.toscrape.com/catalogue/origins-alphas-05_42/index.html</t>
         </is>
       </c>
       <c r="F960" t="inlineStr">
@@ -25399,7 +25399,7 @@
       </c>
       <c r="E961" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/one-second-seven-7_41/index.html</t>
+          <t>https://books.toscrape.com/catalogue/one-second-seven-7_41/index.html</t>
         </is>
       </c>
       <c r="F961" t="inlineStr">
@@ -25425,7 +25425,7 @@
       </c>
       <c r="E962" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/on-the-road-duluoz-legend_40/index.html</t>
+          <t>https://books.toscrape.com/catalogue/on-the-road-duluoz-legend_40/index.html</t>
         </is>
       </c>
       <c r="F962" t="inlineStr">
@@ -25451,7 +25451,7 @@
       </c>
       <c r="E963" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/old-records-never-die-one-mans-quest-for-his-vinyl-and-his-past_39/index.html</t>
+          <t>https://books.toscrape.com/catalogue/old-records-never-die-one-mans-quest-for-his-vinyl-and-his-past_39/index.html</t>
         </is>
       </c>
       <c r="F963" t="inlineStr">
@@ -25477,7 +25477,7 @@
       </c>
       <c r="E964" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/off-sides-off-1_38/index.html</t>
+          <t>https://books.toscrape.com/catalogue/off-sides-off-1_38/index.html</t>
         </is>
       </c>
       <c r="F964" t="inlineStr">
@@ -25503,7 +25503,7 @@
       </c>
       <c r="E965" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/of-mice-and-men_37/index.html</t>
+          <t>https://books.toscrape.com/catalogue/of-mice-and-men_37/index.html</t>
         </is>
       </c>
       <c r="F965" t="inlineStr">
@@ -25529,7 +25529,7 @@
       </c>
       <c r="E966" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/myriad-prentor-1_36/index.html</t>
+          <t>https://books.toscrape.com/catalogue/myriad-prentor-1_36/index.html</t>
         </is>
       </c>
       <c r="F966" t="inlineStr">
@@ -25555,7 +25555,7 @@
       </c>
       <c r="E967" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/my-perfect-mistake-over-the-top-1_35/index.html</t>
+          <t>https://books.toscrape.com/catalogue/my-perfect-mistake-over-the-top-1_35/index.html</t>
         </is>
       </c>
       <c r="F967" t="inlineStr">
@@ -25581,7 +25581,7 @@
       </c>
       <c r="E968" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/ms-marvel-vol-1-no-normal-ms-marvel-2014-2015-1_34/index.html</t>
+          <t>https://books.toscrape.com/catalogue/ms-marvel-vol-1-no-normal-ms-marvel-2014-2015-1_34/index.html</t>
         </is>
       </c>
       <c r="F968" t="inlineStr">
@@ -25607,7 +25607,7 @@
       </c>
       <c r="E969" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/meditations_33/index.html</t>
+          <t>https://books.toscrape.com/catalogue/meditations_33/index.html</t>
         </is>
       </c>
       <c r="F969" t="inlineStr">
@@ -25633,7 +25633,7 @@
       </c>
       <c r="E970" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/matilda_32/index.html</t>
+          <t>https://books.toscrape.com/catalogue/matilda_32/index.html</t>
         </is>
       </c>
       <c r="F970" t="inlineStr">
@@ -25659,7 +25659,7 @@
       </c>
       <c r="E971" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/lost-among-the-living_31/index.html</t>
+          <t>https://books.toscrape.com/catalogue/lost-among-the-living_31/index.html</t>
         </is>
       </c>
       <c r="F971" t="inlineStr">
@@ -25685,7 +25685,7 @@
       </c>
       <c r="E972" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/lord-of-the-flies_30/index.html</t>
+          <t>https://books.toscrape.com/catalogue/lord-of-the-flies_30/index.html</t>
         </is>
       </c>
       <c r="F972" t="inlineStr">
@@ -25711,7 +25711,7 @@
       </c>
       <c r="E973" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/listen-to-me-fusion-1_29/index.html</t>
+          <t>https://books.toscrape.com/catalogue/listen-to-me-fusion-1_29/index.html</t>
         </is>
       </c>
       <c r="F973" t="inlineStr">
@@ -25737,7 +25737,7 @@
       </c>
       <c r="E974" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/kitchens-of-the-great-midwest_28/index.html</t>
+          <t>https://books.toscrape.com/catalogue/kitchens-of-the-great-midwest_28/index.html</t>
         </is>
       </c>
       <c r="F974" t="inlineStr">
@@ -25763,7 +25763,7 @@
       </c>
       <c r="E975" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/jane-eyre_27/index.html</t>
+          <t>https://books.toscrape.com/catalogue/jane-eyre_27/index.html</t>
         </is>
       </c>
       <c r="F975" t="inlineStr">
@@ -25789,7 +25789,7 @@
       </c>
       <c r="E976" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/imperfect-harmony_26/index.html</t>
+          <t>https://books.toscrape.com/catalogue/imperfect-harmony_26/index.html</t>
         </is>
       </c>
       <c r="F976" t="inlineStr">
@@ -25815,7 +25815,7 @@
       </c>
       <c r="E977" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/icing-aces-hockey-2_25/index.html</t>
+          <t>https://books.toscrape.com/catalogue/icing-aces-hockey-2_25/index.html</t>
         </is>
       </c>
       <c r="F977" t="inlineStr">
@@ -25841,7 +25841,7 @@
       </c>
       <c r="E978" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/hawkeye-vol-1-my-life-as-a-weapon-hawkeye-1_24/index.html</t>
+          <t>https://books.toscrape.com/catalogue/hawkeye-vol-1-my-life-as-a-weapon-hawkeye-1_24/index.html</t>
         </is>
       </c>
       <c r="F978" t="inlineStr">
@@ -25867,7 +25867,7 @@
       </c>
       <c r="E979" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/having-the-barbarians-baby-ice-planet-barbarians-75_23/index.html</t>
+          <t>https://books.toscrape.com/catalogue/having-the-barbarians-baby-ice-planet-barbarians-75_23/index.html</t>
         </is>
       </c>
       <c r="F979" t="inlineStr">
@@ -25893,7 +25893,7 @@
       </c>
       <c r="E980" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/giant-days-vol-1-giant-days-1-4_22/index.html</t>
+          <t>https://books.toscrape.com/catalogue/giant-days-vol-1-giant-days-1-4_22/index.html</t>
         </is>
       </c>
       <c r="F980" t="inlineStr">
@@ -25919,7 +25919,7 @@
       </c>
       <c r="E981" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/fruits-basket-vol-1-fruits-basket-1_21/index.html</t>
+          <t>https://books.toscrape.com/catalogue/fruits-basket-vol-1-fruits-basket-1_21/index.html</t>
         </is>
       </c>
       <c r="F981" t="inlineStr">
@@ -25945,7 +25945,7 @@
       </c>
       <c r="E982" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/frankenstein_20/index.html</t>
+          <t>https://books.toscrape.com/catalogue/frankenstein_20/index.html</t>
         </is>
       </c>
       <c r="F982" t="inlineStr">
@@ -25971,7 +25971,7 @@
       </c>
       <c r="E983" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/forever-rockers-the-rocker-12_19/index.html</t>
+          <t>https://books.toscrape.com/catalogue/forever-rockers-the-rocker-12_19/index.html</t>
         </is>
       </c>
       <c r="F983" t="inlineStr">
@@ -25997,7 +25997,7 @@
       </c>
       <c r="E984" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/fighting-fate-fighting-6_18/index.html</t>
+          <t>https://books.toscrape.com/catalogue/fighting-fate-fighting-6_18/index.html</t>
         </is>
       </c>
       <c r="F984" t="inlineStr">
@@ -26023,7 +26023,7 @@
       </c>
       <c r="E985" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/emma_17/index.html</t>
+          <t>https://books.toscrape.com/catalogue/emma_17/index.html</t>
         </is>
       </c>
       <c r="F985" t="inlineStr">
@@ -26049,7 +26049,7 @@
       </c>
       <c r="E986" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/eat-pray-love_16/index.html</t>
+          <t>https://books.toscrape.com/catalogue/eat-pray-love_16/index.html</t>
         </is>
       </c>
       <c r="F986" t="inlineStr">
@@ -26075,7 +26075,7 @@
       </c>
       <c r="E987" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/deep-under-walker-security-1_15/index.html</t>
+          <t>https://books.toscrape.com/catalogue/deep-under-walker-security-1_15/index.html</t>
         </is>
       </c>
       <c r="F987" t="inlineStr">
@@ -26101,7 +26101,7 @@
       </c>
       <c r="E988" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/choosing-our-religion-the-spiritual-lives-of-americas-nones_14/index.html</t>
+          <t>https://books.toscrape.com/catalogue/choosing-our-religion-the-spiritual-lives-of-americas-nones_14/index.html</t>
         </is>
       </c>
       <c r="F988" t="inlineStr">
@@ -26127,7 +26127,7 @@
       </c>
       <c r="E989" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/charlie-and-the-chocolate-factory-charlie-bucket-1_13/index.html</t>
+          <t>https://books.toscrape.com/catalogue/charlie-and-the-chocolate-factory-charlie-bucket-1_13/index.html</t>
         </is>
       </c>
       <c r="F989" t="inlineStr">
@@ -26153,7 +26153,7 @@
       </c>
       <c r="E990" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/charitys-cross-charles-towne-belles-4_12/index.html</t>
+          <t>https://books.toscrape.com/catalogue/charitys-cross-charles-towne-belles-4_12/index.html</t>
         </is>
       </c>
       <c r="F990" t="inlineStr">
@@ -26179,7 +26179,7 @@
       </c>
       <c r="E991" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/bright-lines_11/index.html</t>
+          <t>https://books.toscrape.com/catalogue/bright-lines_11/index.html</t>
         </is>
       </c>
       <c r="F991" t="inlineStr">
@@ -26205,7 +26205,7 @@
       </c>
       <c r="E992" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/bridget-joness-diary-bridget-jones-1_10/index.html</t>
+          <t>https://books.toscrape.com/catalogue/bridget-joness-diary-bridget-jones-1_10/index.html</t>
         </is>
       </c>
       <c r="F992" t="inlineStr">
@@ -26231,7 +26231,7 @@
       </c>
       <c r="E993" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/bounty-colorado-mountain-7_9/index.html</t>
+          <t>https://books.toscrape.com/catalogue/bounty-colorado-mountain-7_9/index.html</t>
         </is>
       </c>
       <c r="F993" t="inlineStr">
@@ -26257,7 +26257,7 @@
       </c>
       <c r="E994" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/blood-defense-samantha-brinkman-1_8/index.html</t>
+          <t>https://books.toscrape.com/catalogue/blood-defense-samantha-brinkman-1_8/index.html</t>
         </is>
       </c>
       <c r="F994" t="inlineStr">
@@ -26283,7 +26283,7 @@
       </c>
       <c r="E995" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/bleach-vol-1-strawberry-and-the-soul-reapers-bleach-1_7/index.html</t>
+          <t>https://books.toscrape.com/catalogue/bleach-vol-1-strawberry-and-the-soul-reapers-bleach-1_7/index.html</t>
         </is>
       </c>
       <c r="F995" t="inlineStr">
@@ -26309,7 +26309,7 @@
       </c>
       <c r="E996" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/beyond-good-and-evil_6/index.html</t>
+          <t>https://books.toscrape.com/catalogue/beyond-good-and-evil_6/index.html</t>
         </is>
       </c>
       <c r="F996" t="inlineStr">
@@ -26335,7 +26335,7 @@
       </c>
       <c r="E997" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/alice-in-wonderland-alices-adventures-in-wonderland-1_5/index.html</t>
+          <t>https://books.toscrape.com/catalogue/alice-in-wonderland-alices-adventures-in-wonderland-1_5/index.html</t>
         </is>
       </c>
       <c r="F997" t="inlineStr">
@@ -26361,7 +26361,7 @@
       </c>
       <c r="E998" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/ajin-demi-human-volume-1-ajin-demi-human-1_4/index.html</t>
+          <t>https://books.toscrape.com/catalogue/ajin-demi-human-volume-1-ajin-demi-human-1_4/index.html</t>
         </is>
       </c>
       <c r="F998" t="inlineStr">
@@ -26387,7 +26387,7 @@
       </c>
       <c r="E999" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/a-spys-devotion-the-regency-spies-of-london-1_3/index.html</t>
+          <t>https://books.toscrape.com/catalogue/a-spys-devotion-the-regency-spies-of-london-1_3/index.html</t>
         </is>
       </c>
       <c r="F999" t="inlineStr">
@@ -26413,7 +26413,7 @@
       </c>
       <c r="E1000" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/1st-to-die-womens-murder-club-1_2/index.html</t>
+          <t>https://books.toscrape.com/catalogue/1st-to-die-womens-murder-club-1_2/index.html</t>
         </is>
       </c>
       <c r="F1000" t="inlineStr">
@@ -26439,7 +26439,7 @@
       </c>
       <c r="E1001" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/1000-places-to-see-before-you-die_1/index.html</t>
+          <t>https://books.toscrape.com/catalogue/1000-places-to-see-before-you-die_1/index.html</t>
         </is>
       </c>
       <c r="F1001" t="inlineStr">
